--- a/SEPIA/SEPIA_config.xlsx
+++ b/SEPIA/SEPIA_config.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" state="visible" r:id="rId3"/>
@@ -1955,1114 +1955,1114 @@
     <t xml:space="preserve">Production of ammonia from hydrogen</t>
   </si>
   <si>
+    <t xml:space="preserve">prohydclammt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production of H2 via steam methane reforming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prohydgaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmsmr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smrc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production of H2 via steam methane reforming CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prohydgazcc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steam Methane reforming H2 production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prohydfesmr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probmliqu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biomass to liquid CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probmliqucc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biomass to liquid losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probmliqlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biomass to liquid CC losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probmliqloscc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battery charger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probattchg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battery charger losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probattchlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battery discharger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probattdhg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battery discharger losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probattdhlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fischer-Tropsch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profischer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fischer-Tropsch heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profischerh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fischer-Tropsch losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profischerlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from coal-fired CHP plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchpcms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmvapchpcms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coal cogeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from oil-fired CHP plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchppet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmvapchppet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oil cogeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from methane-fired CHP plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchpgass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmvapchpgaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gas network cogeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from methane-fired CHP CC plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchpccgaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from biogas-fired CHP plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchpbgl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmvapchpbgl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biogas cogeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from solid biomass CHP plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchpboi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmvapchpboi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solid biomass cogeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat out put solid biomass CHP CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbelccbmcch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from waste-to-energy CHP CC plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prewstvapcc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmvapchpwst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waste cogeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from waste-to-energy CHP plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchpwst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from geothermal CHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchpgeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmvapchpgeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geothermal heat cogeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from hydrogen CHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbvapchphyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmvapchphyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrogen cogeneration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from heat recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchfat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from household waste incineration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchinc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmrchinc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prcc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from geothermal energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchgeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geothermal heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from solid biomass boilers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchboi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmrchboi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from gas-fired boilers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchgaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmrchgaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gas network</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gas-fired boilers losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchgazzloss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from oil-fired boilers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchpet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmrchpet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from centralised electric boilers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbchresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centralised electric boilers losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbchreshh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Losses from centralised electric boilers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">losselchh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from coal-fired boilers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchcms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmrchcms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from centralised solar thermal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchsth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centralised solar thermal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from centralised heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchpac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmrchpac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centralised heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchpacc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from centralised electric heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchpee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchpeee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchpeeee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat energy output from hydrogen boilers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbrchhyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rdmrchhyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (nuclear powerplants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossnuc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (coal-fired powerplants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">losscoal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (coal-fired powerplants) lignite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">losslig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (oil-fired powerplants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (gas-fired powerplants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossgas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (solid biomass powerplants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (waste-fired powerplants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">llll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iuygg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (hydrogen powerplants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fftfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (coal-fired CHP plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scvqs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (oil-fired CHP plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">csqz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (methane-fired CHP plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dqzf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (methane-fired CHP CC plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossgazchpcc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (biogas-fired CHP plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sfqf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (solid biomass CHP plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossbchp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">losses solid biomass chp CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prbelccbmccl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (waste-to-energy CHP plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (waste-to-energy CHP CC plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dzzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zfazfa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fzza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (geothermal CHP plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fzeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses methanolisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossmet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (hydrogen CHP plants)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">afzf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (electrolysis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">losshely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (steam methane reforming)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossmr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossmrr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (heat recovery)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">efzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (household waste incineration)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fzfaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (geothermal energy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fqzfzef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses rural biomass boilers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses urban decentral biomass boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossbbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (solid biomass residential urban boilers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">losssb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (solid biomass tertiary urban boilers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">losssbbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (gas-fired residential rural boilers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossgb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (gas-fired tertiary rural boilers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossgbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses rural gas boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossgbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses urban decentral gas boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossgbss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses rural oil boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses urban decentral oil boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossobb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (oil-fired residential urban boilers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (oil-fired tertiary urban boilers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossobss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (coal-fired boilers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">efzef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (centralised solar thermal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (centralised heat pumps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">losshp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (hydrogen boilers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zfzf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses rural resistive heater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses urban decentral resistive heater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (resistive heaters residential urban)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (resistive heaters tertiary urban)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (resistive heaters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhshs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhshsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhshss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossrhyy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gas grid distribution &amp; storage losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fzzaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat network distribution losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrogen distribution &amp; storage losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fazfa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (methanation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presabaloss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses (biomass liquefaction)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fzafz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses biomass for industry CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossbmind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformation losses gas for industry CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lossgasind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prescmscfres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rural biomass boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presenccfres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urban decentral biomass boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presenccfb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential and tertiary biomass for heating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presenccfbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presenccfbbb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rural oil boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespetcfres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urban decentral oil boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespetcfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential and tertiary oil for heating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespetcfoo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespetcfooo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential and tertiary gas for heating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presgazcfres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urban decentral gas boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presgazcfg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rural gas boiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presgazcfgg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presgazcfggg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electricity demand of residential and tertairy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preselccfres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preselccfterr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential rural heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehhp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehhpp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential urban heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehhh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehhhh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertairy rural heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehpp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehppp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertairy urban heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehplm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertairy urban heatpumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehplmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential rural electric heaters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehpln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehplnn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urban decentral resistive heater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehplx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential urban electric heaters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehplxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertairy rural electric heaters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rural resistive heaters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehplyy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertairy urban electric heaters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehplyyy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehplz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential and tertairy heat from electric heaters and pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehpx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehpxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehpy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preehpyy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electricity demand for rail network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preserail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential and tertiary DH demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presvapcfdhs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential  ambient rural  heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccfres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccfra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential  ambient urban heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccfraa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccfaaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rural ground heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccfta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccftaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urban decentral air heat pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccfftt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccffff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pressthcfres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prescmscfter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presenccfter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespetcfter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presgazcfter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preselccfter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presvapcfter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccfter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pressthcfter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oil to transport demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preslqfcftra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presgazcftra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">land transport hydrogen demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preshydcftra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">land transport EV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preselccftra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aviation oil demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preslqfcfavi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shipping oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preslqfcffrewati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shipping methanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presngvcffrewati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shipping hydrogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preshydwati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prescmscfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solid biomass for Industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presenccfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solid biomass for Industry CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presenccfindd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oil for industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespetcfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gas for industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presgazcfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gas for industry CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presgazcfindd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">electricity for industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preselccfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pressthcfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low-temperature heat for industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presvapcfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prespaccfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydrogen for industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preshydcfind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ammonia for industry</t>
+  </si>
+  <si>
     <t xml:space="preserve">prohydclamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production of H2 via steam methane reforming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prohydgaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmsmr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smrc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production of H2 via steam methane reforming CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prohydgazcc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ddd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steam Methane reforming H2 production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prohydfesmr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probmliqu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">biomass to liquid CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probmliqucc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">biomass to liquid losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probmliqlos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">biomass to liquid CC losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probmliqloscc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battery charger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probattchg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battery charger losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probattchlos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battery discharger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probattdhg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battery discharger losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">probattdhlos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fischer-Tropsch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">profischer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fischer-Tropsch heat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">profischerh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fischer-Tropsch losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">profischerlo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from coal-fired CHP plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchpcms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmvapchpcms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coal cogeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from oil-fired CHP plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchppet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmvapchppet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oil cogeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from methane-fired CHP plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchpgass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmvapchpgaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gas network cogeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from methane-fired CHP CC plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchpccgaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from biogas-fired CHP plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchpbgl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmvapchpbgl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biogas cogeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from solid biomass CHP plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchpboi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmvapchpboi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solid biomass cogeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat out put solid biomass CHP CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbelccbmcch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from waste-to-energy CHP CC plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prewstvapcc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmvapchpwst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waste cogeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from waste-to-energy CHP plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchpwst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from geothermal CHP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchpgeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmvapchpgeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geothermal heat cogeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from hydrogen CHP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbvapchphyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmvapchphyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrogen cogeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from heat recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchfat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from household waste incineration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchinc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmrchinc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prcc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from geothermal energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchgeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geothermal heat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from solid biomass boilers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchboi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmrchboi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from gas-fired boilers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchgaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmrchgaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gas network</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gas-fired boilers losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchgazzloss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from oil-fired boilers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchpet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmrchpet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from centralised electric boilers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbchresh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centralised electric boilers losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbchreshh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Losses from centralised electric boilers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">losselchh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from coal-fired boilers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchcms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmrchcms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from centralised solar thermal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchsth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centralised solar thermal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from centralised heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchpac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmrchpac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centralised heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchpacc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from centralised electric heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchpee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchpeee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchpeeee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat energy output from hydrogen boilers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbrchhyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdmrchhyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (nuclear powerplants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossnuc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (coal-fired powerplants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">losscoal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (coal-fired powerplants) lignite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">losslig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (oil-fired powerplants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (gas-fired powerplants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossgas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (solid biomass powerplants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (waste-fired powerplants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">llll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iuygg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (hydrogen powerplants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fftfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (coal-fired CHP plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scvqs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (oil-fired CHP plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">csqz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (methane-fired CHP plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dqzf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (methane-fired CHP CC plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossgazchpcc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (biogas-fired CHP plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sfqf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (solid biomass CHP plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossbchp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">losses solid biomass chp CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prbelccbmccl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (waste-to-energy CHP plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (waste-to-energy CHP CC plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dzzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zfazfa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fzza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (geothermal CHP plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fzeg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses methanolisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossmet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (hydrogen CHP plants)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afzf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (electrolysis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">losshely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (steam methane reforming)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossmr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossmrr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (heat recovery)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">efzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (household waste incineration)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fzfaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (geothermal energy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fqzfzef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses rural biomass boilers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossbb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses urban decentral biomass boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossbbb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (solid biomass residential urban boilers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">losssb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (solid biomass tertiary urban boilers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">losssbbb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (gas-fired residential rural boilers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossgb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (gas-fired tertiary rural boilers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossgbb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses rural gas boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossgbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses urban decentral gas boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossgbss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses rural oil boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses urban decentral oil boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossobb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (oil-fired residential urban boilers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (oil-fired tertiary urban boilers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossobss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (coal-fired boilers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">efzef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (centralised solar thermal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (centralised heat pumps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">losshp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (hydrogen boilers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zfzf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses rural resistive heater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses urban decentral resistive heater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (resistive heaters residential urban)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (resistive heaters tertiary urban)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (resistive heaters)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhshs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhshsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhshss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhxx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossrhyy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gas grid distribution &amp; storage losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fzzaf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heat network distribution losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrogen distribution &amp; storage losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fazfa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (methanation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presabaloss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses (biomass liquefaction)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fzafz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses biomass for industry CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossbmind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformation losses gas for industry CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lossgasind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prescmscfres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rural biomass boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presenccfres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">urban decentral biomass boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presenccfb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential and tertiary biomass for heating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presenccfbb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presenccfbbb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rural oil boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespetcfres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">urban decentral oil boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespetcfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential and tertiary oil for heating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespetcfoo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespetcfooo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential and tertiary gas for heating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presgazcfres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">urban decentral gas boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presgazcfg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rural gas boiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presgazcfgg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presgazcfggg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">electricity demand of residential and tertairy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preselccfres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preselccfterr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential rural heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehhp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehhpp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential urban heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehhh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehhhh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tertairy rural heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehpp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehppp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tertairy urban heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehplm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tertairy urban heatpumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehplmm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential rural electric heaters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehpln</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehplnn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">urban decentral resistive heater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehplx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential urban electric heaters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehplxx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tertairy rural electric heaters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rural resistive heaters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehplyy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tertairy urban electric heaters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehplyyy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehplz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential and tertairy heat from electric heaters and pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehpx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehpxx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehpy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preehpyy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">electricity demand for rail network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preserail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential and tertiary DH demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presvapcfdhs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential  ambient rural  heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential  ambient urban heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfraa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfaaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rural ground heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccftaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">urban decentral air heat pump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfftt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccffff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pressthcfres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prescmscfter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presenccfter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespetcfter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presgazcfter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preselccfter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presvapcfter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pressthcfter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oil to transport demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preslqfcftra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presgazcftra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">land transport hydrogen demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preshydcftra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">land transport EV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preselccftra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aviation oil demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preslqfcfavi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shipping oil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preslqfcffrewati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shipping methanol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presngvcffrewati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shipping hydrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preshydwati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prescmscfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solid biomass for Industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presenccfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solid biomass for Industry CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presenccfindd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oil for industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespetcfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gas for industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presgazcfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gas for industry CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presgazcfindd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">electricity for industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preselccfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pressthcfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">low-temperature heat for industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presvapcfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hydrogen for industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preshydcfind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ammonia for industry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preammind</t>
   </si>
   <si>
     <t xml:space="preserve">prescmscfneind</t>

--- a/SEPIA/SEPIA_config.xlsx
+++ b/SEPIA/SEPIA_config.xlsx
@@ -396,7 +396,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="1446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2819" uniqueCount="1454">
   <si>
     <t xml:space="preserve">Sheet</t>
   </si>
@@ -3521,9 +3521,6 @@
     <t xml:space="preserve">proeoffdch</t>
   </si>
   <si>
-    <t xml:space="preserve">electro_sehyd_se</t>
-  </si>
-  <si>
     <t xml:space="preserve">VRE connected electrolysers</t>
   </si>
   <si>
@@ -3554,6 +3551,24 @@
     <t xml:space="preserve">prehvvapflc</t>
   </si>
   <si>
+    <t xml:space="preserve">biomass-to-methanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prebmmeth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biomass-to-methanol losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prebmmethlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ammonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prebmannfe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Process emissions from industry</t>
   </si>
   <si>
@@ -4005,6 +4020,15 @@
   </si>
   <si>
     <t xml:space="preserve">emmoilref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biomass to methanol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emmbmmet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emmbmmetatm</t>
   </si>
   <si>
     <t xml:space="preserve">OCGT emissions</t>
@@ -4958,7 +4982,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5037,12 +5061,6 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -5358,7 +5376,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5543,7 +5561,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5551,11 +5569,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5563,7 +5577,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5579,11 +5593,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5591,7 +5605,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -5615,11 +5629,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -6748,7 +6762,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="B1" s="1" t="n">
         <v>2025</v>
@@ -6771,7 +6785,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>10</v>
@@ -6792,12 +6806,12 @@
         <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0</v>
@@ -6818,12 +6832,12 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.6</v>
@@ -6844,12 +6858,12 @@
         <v>0.6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -6870,12 +6884,12 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1.28</v>
@@ -6896,12 +6910,12 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>47</v>
@@ -6922,12 +6936,12 @@
         <v>40</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>20</v>
@@ -6948,12 +6962,12 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -6974,12 +6988,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1379</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0</v>
@@ -7000,12 +7014,12 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0</v>
@@ -7026,12 +7040,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -7052,12 +7066,12 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>0</v>
@@ -7078,12 +7092,12 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
@@ -7104,12 +7118,12 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>16</v>
@@ -7130,12 +7144,12 @@
         <v>16</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>19</v>
@@ -7156,12 +7170,12 @@
         <v>19</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>31</v>
@@ -7182,12 +7196,12 @@
         <v>20</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -7208,12 +7222,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -7234,12 +7248,12 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -7260,12 +7274,12 @@
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>107</v>
@@ -7286,12 +7300,12 @@
         <v>107</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1000</v>
@@ -7312,12 +7326,12 @@
         <v>1000</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>43</v>
@@ -7338,12 +7352,12 @@
         <v>43</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -7364,12 +7378,12 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1409</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>68</v>
@@ -7390,12 +7404,12 @@
         <v>68</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -7416,12 +7430,12 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -7442,12 +7456,12 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>0</v>
@@ -7468,12 +7482,12 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>351</v>
@@ -7494,7 +7508,7 @@
         <v>341</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7546,7 +7560,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="B1" s="1" t="n">
         <v>2025</v>
@@ -7569,7 +7583,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>6.5</v>
@@ -7590,12 +7604,12 @@
         <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1418</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0</v>
@@ -7616,12 +7630,12 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1419</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0</v>
@@ -7642,12 +7656,12 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1420</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -7668,12 +7682,12 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1421</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1.36</v>
@@ -7694,12 +7708,12 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1422</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>38</v>
@@ -7720,12 +7734,12 @@
         <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1423</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>42</v>
@@ -7746,12 +7760,12 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -7772,12 +7786,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1425</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
@@ -7798,12 +7812,12 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1426</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0</v>
@@ -7824,12 +7838,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1427</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -7850,12 +7864,12 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1428</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>9</v>
@@ -7876,12 +7890,12 @@
         <v>8</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
@@ -7902,12 +7916,12 @@
         <v>8</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>13</v>
@@ -7928,12 +7942,12 @@
         <v>13</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1431</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>0</v>
@@ -7954,12 +7968,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1432</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>60</v>
@@ -7980,12 +7994,12 @@
         <v>60</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1433</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -8006,12 +8020,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1434</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -8032,12 +8046,12 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -8058,12 +8072,12 @@
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1436</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>12</v>
@@ -8084,12 +8098,12 @@
         <v>12</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1076</v>
@@ -8110,12 +8124,12 @@
         <v>1000</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>11</v>
@@ -8136,12 +8150,12 @@
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -8162,12 +8176,12 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1440</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>40</v>
@@ -8188,12 +8202,12 @@
         <v>40</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1441</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -8214,12 +8228,12 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1442</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -8240,12 +8254,12 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1443</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>2.4</v>
@@ -8266,12 +8280,12 @@
         <v>2.4</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1444</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>616</v>
@@ -8292,7 +8306,7 @@
         <v>600</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1445</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -17528,14 +17542,17 @@
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A336" s="46" t="s">
+      <c r="A336" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D336" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="D336" s="1" t="s">
+      <c r="E336" s="1" t="s">
         <v>1042</v>
-      </c>
-      <c r="E336" s="1" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17546,10 +17563,10 @@
         <v>282</v>
       </c>
       <c r="D337" s="25" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E337" s="1" t="s">
         <v>1044</v>
-      </c>
-      <c r="E337" s="1" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17560,10 +17577,10 @@
         <v>196</v>
       </c>
       <c r="D338" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E338" s="1" t="s">
         <v>1046</v>
-      </c>
-      <c r="E338" s="1" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17574,10 +17591,10 @@
         <v>282</v>
       </c>
       <c r="D339" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E339" s="1" t="s">
         <v>1048</v>
-      </c>
-      <c r="E339" s="1" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17588,10 +17605,52 @@
         <v>201</v>
       </c>
       <c r="D340" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E340" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="E340" s="1" t="s">
+    </row>
+    <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A341" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>1051</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A342" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A343" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>1056</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -17618,7 +17677,7 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="47" width="8.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="8.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="62.18"/>
@@ -17628,7 +17687,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -17651,7 +17710,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>342</v>
       </c>
       <c r="B2" s="26" t="s">
@@ -17659,16 +17718,16 @@
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="43" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="F2" s="43"/>
       <c r="G2" s="43"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="48" t="s">
         <v>342</v>
       </c>
       <c r="B3" s="26" t="s">
@@ -17676,16 +17735,16 @@
       </c>
       <c r="C3" s="43"/>
       <c r="D3" s="44" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="F3" s="43"/>
       <c r="G3" s="43"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="48" t="s">
         <v>342</v>
       </c>
       <c r="B4" s="26" t="s">
@@ -17693,16 +17752,16 @@
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="44" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B5" s="26" t="s">
@@ -17710,16 +17769,16 @@
       </c>
       <c r="C5" s="43"/>
       <c r="D5" s="44" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="F5" s="43"/>
       <c r="G5" s="43"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B6" s="26" t="s">
@@ -17727,16 +17786,16 @@
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="44" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="43"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="48" t="s">
         <v>346</v>
       </c>
       <c r="B7" s="26" t="s">
@@ -17744,16 +17803,16 @@
       </c>
       <c r="C7" s="43"/>
       <c r="D7" s="44" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="F7" s="43"/>
       <c r="G7" s="43"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B8" s="26" t="s">
@@ -17761,16 +17820,16 @@
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="44" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="F8" s="43"/>
       <c r="G8" s="43"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B9" s="26" t="s">
@@ -17778,16 +17837,16 @@
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="44" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B10" s="26" t="s">
@@ -17795,16 +17854,16 @@
       </c>
       <c r="C10" s="43"/>
       <c r="D10" s="44" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="F10" s="43"/>
       <c r="G10" s="43"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B11" s="26" t="s">
@@ -17815,13 +17874,13 @@
         <v>782</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="F11" s="43"/>
       <c r="G11" s="43"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="26" t="s">
@@ -17832,13 +17891,13 @@
         <v>780</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B13" s="26" t="s">
@@ -17846,16 +17905,16 @@
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="44" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="F13" s="43"/>
       <c r="G13" s="43"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B14" s="26" t="s">
@@ -17863,54 +17922,54 @@
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="44" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="F14" s="43"/>
       <c r="G14" s="43"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="D15" s="44" t="s">
         <v>771</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>773</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="F16" s="43"/>
       <c r="G16" s="43"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B17" s="26" t="s">
@@ -17918,16 +17977,16 @@
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="44" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="F17" s="43"/>
       <c r="G17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B18" s="26" t="s">
@@ -17935,16 +17994,16 @@
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="44" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="F18" s="43"/>
       <c r="G18" s="43"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="48" t="s">
         <v>340</v>
       </c>
       <c r="B19" s="26" t="s">
@@ -17952,16 +18011,16 @@
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="44" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="F19" s="43"/>
       <c r="G19" s="43"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B20" s="26" t="s">
@@ -17972,13 +18031,13 @@
         <v>877</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="F20" s="43"/>
       <c r="G20" s="43"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B21" s="26" t="s">
@@ -17988,14 +18047,14 @@
       <c r="D21" s="44" t="s">
         <v>766</v>
       </c>
-      <c r="E21" s="50" t="s">
-        <v>1084</v>
+      <c r="E21" s="49" t="s">
+        <v>1089</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B22" s="26" t="s">
@@ -18006,13 +18065,13 @@
         <v>766</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="F22" s="43"/>
       <c r="G22" s="43"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B23" s="26" t="s">
@@ -18023,13 +18082,13 @@
         <v>764</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="F23" s="43"/>
       <c r="G23" s="43"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B24" s="26" t="s">
@@ -18040,32 +18099,32 @@
         <v>764</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="F24" s="43"/>
       <c r="G24" s="43"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="48" t="s">
         <v>348</v>
       </c>
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="48" t="s">
         <v>389</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="F25" s="43"/>
       <c r="G25" s="43"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B26" s="26" t="s">
@@ -18075,16 +18134,16 @@
         <v>126</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="F26" s="43"/>
       <c r="G26" s="43"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B27" s="26" t="s">
@@ -18094,16 +18153,16 @@
         <v>133</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B28" s="26" t="s">
@@ -18113,54 +18172,54 @@
         <v>119</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="F28" s="43"/>
       <c r="G28" s="43"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="F29" s="43"/>
       <c r="G29" s="43"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49" t="s">
+      <c r="A30" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="F30" s="43"/>
       <c r="G30" s="43"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="48" t="s">
         <v>354</v>
       </c>
       <c r="B31" s="26" t="s">
@@ -18168,16 +18227,16 @@
       </c>
       <c r="C31" s="43"/>
       <c r="D31" s="44" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="F31" s="43"/>
       <c r="G31" s="43"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B32" s="26" t="s">
@@ -18188,13 +18247,13 @@
         <v>357</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="F32" s="43"/>
       <c r="G32" s="43"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
+      <c r="A33" s="48" t="s">
         <v>358</v>
       </c>
       <c r="B33" s="26" t="s">
@@ -18202,16 +18261,16 @@
       </c>
       <c r="C33" s="43"/>
       <c r="D33" s="44" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="F33" s="43"/>
       <c r="G33" s="43"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="48" t="s">
         <v>360</v>
       </c>
       <c r="B34" s="26" t="s">
@@ -18222,32 +18281,32 @@
         <v>934</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>362</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="F35" s="43"/>
       <c r="G35" s="43"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B36" s="26" t="s">
@@ -18255,16 +18314,16 @@
       </c>
       <c r="C36" s="43"/>
       <c r="D36" s="44" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F36" s="43"/>
       <c r="G36" s="43"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B37" s="26" t="s">
@@ -18274,16 +18333,16 @@
         <v>129</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="F37" s="43"/>
       <c r="G37" s="43"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="49" t="s">
+      <c r="A38" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B38" s="26" t="s">
@@ -18291,16 +18350,16 @@
       </c>
       <c r="C38" s="43"/>
       <c r="D38" s="44" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="F38" s="43"/>
       <c r="G38" s="43"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="s">
+      <c r="A39" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B39" s="26" t="s">
@@ -18308,16 +18367,16 @@
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49" t="s">
+      <c r="A40" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B40" s="26" t="s">
@@ -18325,16 +18384,16 @@
       </c>
       <c r="C40" s="43"/>
       <c r="D40" s="44" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="F40" s="43"/>
       <c r="G40" s="43"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="49" t="s">
+      <c r="A41" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B41" s="26" t="s">
@@ -18342,16 +18401,16 @@
       </c>
       <c r="C41" s="43"/>
       <c r="D41" s="44" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="F41" s="43"/>
       <c r="G41" s="43"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="49" t="s">
+      <c r="A42" s="48" t="s">
         <v>346</v>
       </c>
       <c r="B42" s="26" t="s">
@@ -18359,16 +18418,16 @@
       </c>
       <c r="C42" s="43"/>
       <c r="D42" s="44" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="F42" s="43"/>
       <c r="G42" s="43"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="49" t="s">
+      <c r="A43" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B43" s="26" t="s">
@@ -18376,16 +18435,16 @@
       </c>
       <c r="C43" s="43"/>
       <c r="D43" s="44" t="s">
-        <v>1124</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>1125</v>
+        <v>1129</v>
+      </c>
+      <c r="E43" s="50" t="s">
+        <v>1130</v>
       </c>
       <c r="F43" s="43"/>
       <c r="G43" s="43"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B44" s="26" t="s">
@@ -18393,16 +18452,16 @@
       </c>
       <c r="C44" s="43"/>
       <c r="D44" s="44" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E44" s="51" t="s">
-        <v>1127</v>
+        <v>1131</v>
+      </c>
+      <c r="E44" s="50" t="s">
+        <v>1132</v>
       </c>
       <c r="F44" s="43"/>
       <c r="G44" s="43"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B45" s="26" t="s">
@@ -18410,16 +18469,16 @@
       </c>
       <c r="C45" s="43"/>
       <c r="D45" s="44" t="s">
-        <v>1124</v>
-      </c>
-      <c r="E45" s="51" t="s">
-        <v>1128</v>
+        <v>1129</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>1133</v>
       </c>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B46" s="26" t="s">
@@ -18429,16 +18488,16 @@
         <v>411</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E46" s="51" t="s">
-        <v>1129</v>
+        <v>1131</v>
+      </c>
+      <c r="E46" s="50" t="s">
+        <v>1134</v>
       </c>
       <c r="F46" s="43"/>
       <c r="G46" s="43"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="48" t="s">
         <v>366</v>
       </c>
       <c r="B47" s="26" t="s">
@@ -18446,16 +18505,16 @@
       </c>
       <c r="C47" s="43"/>
       <c r="D47" s="44" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E47" s="51" t="s">
-        <v>1131</v>
+        <v>1135</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>1136</v>
       </c>
       <c r="F47" s="43"/>
       <c r="G47" s="43"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B48" s="26" t="s">
@@ -18463,16 +18522,16 @@
       </c>
       <c r="C48" s="43"/>
       <c r="D48" s="44" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E48" s="51" t="s">
-        <v>1132</v>
+        <v>1135</v>
+      </c>
+      <c r="E48" s="50" t="s">
+        <v>1137</v>
       </c>
       <c r="F48" s="43"/>
       <c r="G48" s="43"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="49" t="s">
+      <c r="A49" s="48" t="s">
         <v>366</v>
       </c>
       <c r="B49" s="26" t="s">
@@ -18482,16 +18541,16 @@
         <v>411</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E49" s="51" t="s">
-        <v>1134</v>
+        <v>1138</v>
+      </c>
+      <c r="E49" s="50" t="s">
+        <v>1139</v>
       </c>
       <c r="F49" s="43"/>
       <c r="G49" s="43"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="49" t="s">
+      <c r="A50" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B50" s="26" t="s">
@@ -18501,16 +18560,16 @@
         <v>411</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E50" s="51" t="s">
-        <v>1135</v>
+        <v>1138</v>
+      </c>
+      <c r="E50" s="50" t="s">
+        <v>1140</v>
       </c>
       <c r="F50" s="43"/>
       <c r="G50" s="43"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="48" t="s">
         <v>366</v>
       </c>
       <c r="B51" s="26" t="s">
@@ -18518,16 +18577,16 @@
       </c>
       <c r="C51" s="43"/>
       <c r="D51" s="44" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E51" s="51" t="s">
-        <v>1136</v>
+        <v>1138</v>
+      </c>
+      <c r="E51" s="50" t="s">
+        <v>1141</v>
       </c>
       <c r="F51" s="43"/>
       <c r="G51" s="43"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49" t="s">
+      <c r="A52" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B52" s="26" t="s">
@@ -18535,16 +18594,16 @@
       </c>
       <c r="C52" s="43"/>
       <c r="D52" s="44" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E52" s="51" t="s">
-        <v>1138</v>
+        <v>1142</v>
+      </c>
+      <c r="E52" s="50" t="s">
+        <v>1143</v>
       </c>
       <c r="F52" s="43"/>
       <c r="G52" s="43"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="49" t="s">
+      <c r="A53" s="48" t="s">
         <v>340</v>
       </c>
       <c r="B53" s="26" t="s">
@@ -18554,14 +18613,14 @@
       <c r="D53" s="44" t="s">
         <v>547</v>
       </c>
-      <c r="E53" s="51" t="s">
-        <v>1139</v>
+      <c r="E53" s="50" t="s">
+        <v>1144</v>
       </c>
       <c r="F53" s="43"/>
       <c r="G53" s="43"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="49" t="s">
+      <c r="A54" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B54" s="26" t="s">
@@ -18569,16 +18628,16 @@
       </c>
       <c r="C54" s="43"/>
       <c r="D54" s="44" t="s">
-        <v>1140</v>
-      </c>
-      <c r="E54" s="51" t="s">
-        <v>1141</v>
+        <v>1145</v>
+      </c>
+      <c r="E54" s="50" t="s">
+        <v>1146</v>
       </c>
       <c r="F54" s="43"/>
       <c r="G54" s="43"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="49" t="s">
+      <c r="A55" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B55" s="26" t="s">
@@ -18586,16 +18645,16 @@
       </c>
       <c r="C55" s="43"/>
       <c r="D55" s="44" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E55" s="51" t="s">
-        <v>1142</v>
+        <v>1122</v>
+      </c>
+      <c r="E55" s="50" t="s">
+        <v>1147</v>
       </c>
       <c r="F55" s="43"/>
       <c r="G55" s="43"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="49" t="s">
+      <c r="A56" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B56" s="26" t="s">
@@ -18605,14 +18664,14 @@
       <c r="D56" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="E56" s="51" t="s">
-        <v>1143</v>
+      <c r="E56" s="50" t="s">
+        <v>1148</v>
       </c>
       <c r="F56" s="43"/>
       <c r="G56" s="43"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
+      <c r="A57" s="48" t="s">
         <v>340</v>
       </c>
       <c r="B57" s="26" t="s">
@@ -18622,14 +18681,14 @@
       <c r="D57" s="44" t="s">
         <v>375</v>
       </c>
-      <c r="E57" s="51" t="s">
-        <v>1144</v>
+      <c r="E57" s="50" t="s">
+        <v>1149</v>
       </c>
       <c r="F57" s="43"/>
       <c r="G57" s="43"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
+      <c r="A58" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B58" s="26" t="s">
@@ -18637,16 +18696,16 @@
       </c>
       <c r="C58" s="43"/>
       <c r="D58" s="44" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="F58" s="43"/>
       <c r="G58" s="43"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="49" t="s">
+      <c r="A59" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B59" s="26" t="s">
@@ -18654,16 +18713,16 @@
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="F59" s="43"/>
       <c r="G59" s="43"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="49" t="s">
+      <c r="A60" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B60" s="26" t="s">
@@ -18673,16 +18732,16 @@
         <v>411</v>
       </c>
       <c r="D60" s="44" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="F60" s="43"/>
       <c r="G60" s="43"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
+      <c r="A61" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B61" s="26" t="s">
@@ -18690,16 +18749,16 @@
       </c>
       <c r="C61" s="43"/>
       <c r="D61" s="44" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="F61" s="43"/>
       <c r="G61" s="43"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
+      <c r="A62" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B62" s="26" t="s">
@@ -18707,16 +18766,16 @@
       </c>
       <c r="C62" s="43"/>
       <c r="D62" s="44" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="F62" s="43"/>
       <c r="G62" s="43"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="49" t="s">
+      <c r="A63" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B63" s="26" t="s">
@@ -18724,16 +18783,16 @@
       </c>
       <c r="C63" s="43"/>
       <c r="D63" s="44" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="F63" s="43"/>
       <c r="G63" s="43"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="49" t="s">
+      <c r="A64" s="48" t="s">
         <v>340</v>
       </c>
       <c r="B64" s="26" t="s">
@@ -18741,16 +18800,16 @@
       </c>
       <c r="C64" s="43"/>
       <c r="D64" s="44" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="F64" s="43"/>
       <c r="G64" s="43"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="49" t="s">
+      <c r="A65" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B65" s="26" t="s">
@@ -18758,16 +18817,16 @@
       </c>
       <c r="C65" s="43"/>
       <c r="D65" s="44" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="F65" s="43"/>
       <c r="G65" s="43"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="49" t="s">
+      <c r="A66" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B66" s="26" t="s">
@@ -18775,16 +18834,16 @@
       </c>
       <c r="C66" s="43"/>
       <c r="D66" s="44" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="F66" s="43"/>
       <c r="G66" s="43"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
+      <c r="A67" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B67" s="26" t="s">
@@ -18792,16 +18851,16 @@
       </c>
       <c r="C67" s="43"/>
       <c r="D67" s="44" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="F67" s="43"/>
       <c r="G67" s="43"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="49" t="s">
+      <c r="A68" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B68" s="26" t="s">
@@ -18809,16 +18868,16 @@
       </c>
       <c r="C68" s="43"/>
       <c r="D68" s="44" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="F68" s="43"/>
       <c r="G68" s="43"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="49" t="s">
+      <c r="A69" s="48" t="s">
         <v>354</v>
       </c>
       <c r="B69" s="26" t="s">
@@ -18828,201 +18887,201 @@
       <c r="D69" s="44" t="s">
         <v>383</v>
       </c>
-      <c r="E69" s="50" t="s">
-        <v>1162</v>
+      <c r="E69" s="49" t="s">
+        <v>1167</v>
       </c>
       <c r="F69" s="43"/>
       <c r="G69" s="43"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="49" t="s">
+      <c r="A70" s="48" t="s">
         <v>380</v>
       </c>
       <c r="B70" s="26" t="s">
         <v>354</v>
       </c>
       <c r="C70" s="43"/>
-      <c r="D70" s="50" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E70" s="50" t="s">
-        <v>1164</v>
+      <c r="D70" s="49" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E70" s="49" t="s">
+        <v>1169</v>
       </c>
       <c r="F70" s="43"/>
       <c r="G70" s="43"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="49" t="s">
+      <c r="A71" s="48" t="s">
         <v>384</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C71" s="43"/>
-      <c r="D71" s="50" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E71" s="50" t="s">
-        <v>1166</v>
+      <c r="D71" s="49" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E71" s="49" t="s">
+        <v>1171</v>
       </c>
       <c r="F71" s="43"/>
       <c r="G71" s="43"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="49" t="s">
+      <c r="A72" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C72" s="43"/>
-      <c r="D72" s="50" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E72" s="50" t="s">
-        <v>1168</v>
+      <c r="D72" s="49" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E72" s="49" t="s">
+        <v>1173</v>
       </c>
       <c r="F72" s="43"/>
       <c r="G72" s="43"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="49" t="s">
+      <c r="A73" s="48" t="s">
         <v>344</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C73" s="43"/>
-      <c r="D73" s="50" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E73" s="50" t="s">
-        <v>1170</v>
+      <c r="D73" s="49" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E73" s="49" t="s">
+        <v>1175</v>
       </c>
       <c r="F73" s="43"/>
       <c r="G73" s="43"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="49" t="s">
+      <c r="A74" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C74" s="43"/>
-      <c r="D74" s="50" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E74" s="50" t="s">
-        <v>1172</v>
+      <c r="D74" s="49" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E74" s="49" t="s">
+        <v>1177</v>
       </c>
       <c r="F74" s="43"/>
       <c r="G74" s="43"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="49" t="s">
+      <c r="A75" s="48" t="s">
         <v>350</v>
       </c>
       <c r="B75" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C75" s="43"/>
-      <c r="D75" s="50" t="s">
-        <v>1173</v>
-      </c>
-      <c r="E75" s="50" t="s">
-        <v>1174</v>
+      <c r="D75" s="49" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E75" s="49" t="s">
+        <v>1179</v>
       </c>
       <c r="F75" s="43"/>
       <c r="G75" s="43"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="49" t="s">
+      <c r="A76" s="48" t="s">
         <v>338</v>
       </c>
       <c r="B76" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C76" s="43"/>
-      <c r="D76" s="50" t="s">
-        <v>1173</v>
-      </c>
-      <c r="E76" s="50" t="s">
-        <v>1175</v>
+      <c r="D76" s="49" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E76" s="49" t="s">
+        <v>1180</v>
       </c>
       <c r="F76" s="43"/>
       <c r="G76" s="43"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="49" t="s">
+      <c r="A77" s="48" t="s">
         <v>346</v>
       </c>
       <c r="B77" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C77" s="43"/>
-      <c r="D77" s="50" t="s">
+      <c r="D77" s="49" t="s">
         <v>446</v>
       </c>
-      <c r="E77" s="50" t="s">
-        <v>1176</v>
+      <c r="E77" s="49" t="s">
+        <v>1181</v>
       </c>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="49" t="s">
+      <c r="A78" s="48" t="s">
         <v>346</v>
       </c>
       <c r="B78" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C78" s="43"/>
-      <c r="D78" s="50" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E78" s="50" t="s">
-        <v>1178</v>
+      <c r="D78" s="49" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E78" s="49" t="s">
+        <v>1183</v>
       </c>
       <c r="F78" s="43"/>
       <c r="G78" s="43"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="49" t="s">
+      <c r="A79" s="48" t="s">
         <v>346</v>
       </c>
       <c r="B79" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C79" s="43"/>
-      <c r="D79" s="50" t="s">
-        <v>1179</v>
-      </c>
-      <c r="E79" s="50" t="s">
-        <v>1180</v>
+      <c r="D79" s="49" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E79" s="49" t="s">
+        <v>1185</v>
       </c>
       <c r="F79" s="43"/>
       <c r="G79" s="43"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="49" t="s">
+      <c r="A80" s="48" t="s">
         <v>348</v>
       </c>
       <c r="B80" s="26" t="s">
         <v>338</v>
       </c>
       <c r="C80" s="43"/>
-      <c r="D80" s="50" t="s">
-        <v>1181</v>
-      </c>
-      <c r="E80" s="50" t="s">
-        <v>1182</v>
+      <c r="D80" s="49" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E80" s="49" t="s">
+        <v>1187</v>
       </c>
       <c r="F80" s="43"/>
       <c r="G80" s="43"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="47" t="s">
+      <c r="A81" s="46" t="s">
         <v>350</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -19032,139 +19091,167 @@
         <v>1005</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="47" t="s">
+      <c r="A82" s="46" t="s">
         <v>338</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>350</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="47" t="s">
+      <c r="A83" s="46" t="s">
         <v>348</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>338</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="47" t="s">
+      <c r="A84" s="46" t="s">
         <v>387</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>338</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="47" t="s">
+      <c r="A85" s="46" t="s">
         <v>387</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>340</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="47" t="s">
+      <c r="A86" s="46" t="s">
         <v>387</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>338</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="47" t="s">
+      <c r="A87" s="46" t="s">
         <v>348</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>338</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="47" t="s">
+      <c r="A88" s="46" t="s">
         <v>354</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>338</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="47" t="s">
+      <c r="A89" s="46" t="s">
         <v>348</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>338</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="47" t="s">
+      <c r="A90" s="46" t="s">
         <v>348</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>338</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1202</v>
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="46" t="s">
+        <v>350</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>1210</v>
       </c>
     </row>
     <row r="1048377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -19389,7 +19476,7 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="47" width="12.78"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="12.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="62.18"/>
@@ -19399,7 +19486,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -19422,7 +19509,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>320</v>
       </c>
       <c r="B2" s="26" t="s">
@@ -19430,16 +19517,16 @@
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="43" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="F2" s="43"/>
       <c r="G2" s="43"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="48" t="s">
         <v>320</v>
       </c>
       <c r="B3" s="26" t="s">
@@ -19447,16 +19534,16 @@
       </c>
       <c r="C3" s="43"/>
       <c r="D3" s="44" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="F3" s="43"/>
       <c r="G3" s="43"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B4" s="26" t="s">
@@ -19464,16 +19551,16 @@
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="44" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B5" s="26" t="s">
@@ -19481,16 +19568,16 @@
       </c>
       <c r="C5" s="43"/>
       <c r="D5" s="44" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="F5" s="43"/>
       <c r="G5" s="43"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B6" s="26" t="s">
@@ -19498,16 +19585,16 @@
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="44" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="43"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B7" s="26" t="s">
@@ -19515,16 +19602,16 @@
       </c>
       <c r="C7" s="43"/>
       <c r="D7" s="44" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>1172</v>
+        <v>1176</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>1177</v>
       </c>
       <c r="F7" s="43"/>
       <c r="G7" s="43"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B8" s="26" t="s">
@@ -19532,16 +19619,16 @@
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="44" t="s">
-        <v>1173</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>1174</v>
+        <v>1178</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>1179</v>
       </c>
       <c r="F8" s="43"/>
       <c r="G8" s="43"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B9" s="26" t="s">
@@ -19549,16 +19636,16 @@
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="44" t="s">
-        <v>1204</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>1176</v>
+        <v>1212</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>1181</v>
       </c>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B10" s="26" t="s">
@@ -19566,16 +19653,16 @@
       </c>
       <c r="C10" s="43"/>
       <c r="D10" s="44" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E10" s="50" t="s">
-        <v>1178</v>
+        <v>1213</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>1183</v>
       </c>
       <c r="F10" s="43"/>
       <c r="G10" s="43"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B11" s="26" t="s">
@@ -19583,118 +19670,118 @@
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="44" t="s">
-        <v>1206</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>1175</v>
+        <v>1214</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>1180</v>
       </c>
       <c r="F11" s="43"/>
       <c r="G11" s="43"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="s">
-        <v>1207</v>
+      <c r="A12" s="48" t="s">
+        <v>1215</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="44" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="s">
-        <v>1207</v>
+      <c r="A13" s="48" t="s">
+        <v>1215</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="44" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="F13" s="43"/>
       <c r="G13" s="43"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="s">
-        <v>1208</v>
+      <c r="A14" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="44" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="F14" s="43"/>
       <c r="G14" s="43"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="s">
-        <v>1208</v>
+      <c r="A15" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="44" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49" t="s">
-        <v>1208</v>
+      <c r="A16" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="44" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="F16" s="43"/>
       <c r="G16" s="43"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
-        <v>1208</v>
+      <c r="A17" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="44" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="F17" s="43"/>
       <c r="G17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B18" s="26" t="s">
@@ -19702,85 +19789,85 @@
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="44" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="F18" s="43"/>
       <c r="G18" s="43"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>1208</v>
+      <c r="A19" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="44" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="F19" s="43"/>
       <c r="G19" s="43"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49" t="s">
-        <v>1208</v>
+      <c r="A20" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="F20" s="43"/>
       <c r="G20" s="43"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="s">
-        <v>1208</v>
+      <c r="A21" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="44" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="s">
-        <v>1208</v>
+      <c r="A22" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="44" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="F22" s="43"/>
       <c r="G22" s="43"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="s">
-        <v>1222</v>
+      <c r="A23" s="48" t="s">
+        <v>1230</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>236</v>
@@ -19790,14 +19877,14 @@
         <v>877</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="F23" s="43"/>
       <c r="G23" s="43"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49" t="s">
-        <v>1223</v>
+      <c r="A24" s="48" t="s">
+        <v>1231</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>234</v>
@@ -19806,17 +19893,17 @@
         <v>126</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="F24" s="43"/>
       <c r="G24" s="43"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49" t="s">
-        <v>1224</v>
+      <c r="A25" s="48" t="s">
+        <v>1232</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>234</v>
@@ -19825,34 +19912,34 @@
         <v>133</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="F25" s="43"/>
       <c r="G25" s="43"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49" t="s">
-        <v>1224</v>
+      <c r="A26" s="48" t="s">
+        <v>1232</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C26" s="43"/>
       <c r="D26" s="44" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>1170</v>
+        <v>1174</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>1175</v>
       </c>
       <c r="F26" s="43"/>
       <c r="G26" s="43"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49" t="s">
-        <v>1225</v>
+      <c r="A27" s="48" t="s">
+        <v>1233</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>234</v>
@@ -19861,70 +19948,70 @@
         <v>119</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49" t="s">
-        <v>1225</v>
+      <c r="A28" s="48" t="s">
+        <v>1233</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C28" s="43"/>
       <c r="D28" s="44" t="s">
-        <v>1226</v>
-      </c>
-      <c r="E28" s="50" t="s">
-        <v>1168</v>
+        <v>1234</v>
+      </c>
+      <c r="E28" s="49" t="s">
+        <v>1173</v>
       </c>
       <c r="F28" s="43"/>
       <c r="G28" s="43"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="s">
-        <v>1227</v>
+      <c r="A29" s="48" t="s">
+        <v>1235</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="F29" s="43"/>
       <c r="G29" s="43"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49" t="s">
-        <v>1227</v>
+      <c r="A30" s="48" t="s">
+        <v>1235</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>243</v>
       </c>
       <c r="C30" s="43"/>
       <c r="D30" s="44" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="F30" s="43"/>
       <c r="G30" s="43"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="s">
-        <v>1222</v>
+      <c r="A31" s="48" t="s">
+        <v>1230</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>243</v>
@@ -19932,13 +20019,13 @@
       <c r="C31" s="43"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="F31" s="43"/>
       <c r="G31" s="43"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="48" t="s">
         <v>334</v>
       </c>
       <c r="B32" s="26" t="s">
@@ -19949,47 +20036,47 @@
         <v>357</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="F32" s="43"/>
       <c r="G32" s="43"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>1222</v>
+      <c r="A33" s="48" t="s">
+        <v>1230</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C33" s="43"/>
       <c r="D33" s="44" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="F33" s="43"/>
       <c r="G33" s="43"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>1222</v>
+      <c r="A34" s="48" t="s">
+        <v>1230</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C34" s="43"/>
       <c r="D34" s="44" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B35" s="26" t="s">
@@ -19997,16 +20084,16 @@
       </c>
       <c r="C35" s="43"/>
       <c r="D35" s="44" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="F35" s="43"/>
       <c r="G35" s="43"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B36" s="26" t="s">
@@ -20014,16 +20101,16 @@
       </c>
       <c r="C36" s="43"/>
       <c r="D36" s="44" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="F36" s="43"/>
       <c r="G36" s="43"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B37" s="26" t="s">
@@ -20031,16 +20118,16 @@
       </c>
       <c r="C37" s="43"/>
       <c r="D37" s="44" t="s">
-        <v>1228</v>
-      </c>
-      <c r="E37" s="50" t="s">
-        <v>1180</v>
+        <v>1236</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>1185</v>
       </c>
       <c r="F37" s="43"/>
       <c r="G37" s="43"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="49" t="s">
+      <c r="A38" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B38" s="26" t="s">
@@ -20048,16 +20135,16 @@
       </c>
       <c r="C38" s="43"/>
       <c r="D38" s="44" t="s">
-        <v>1229</v>
-      </c>
-      <c r="E38" s="50" t="s">
-        <v>1182</v>
+        <v>1237</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>1187</v>
       </c>
       <c r="F38" s="43"/>
       <c r="G38" s="43"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="s">
+      <c r="A39" s="48" t="s">
         <v>366</v>
       </c>
       <c r="B39" s="26" t="s">
@@ -20065,16 +20152,16 @@
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E39" s="51" t="s">
-        <v>1131</v>
+        <v>1135</v>
+      </c>
+      <c r="E39" s="50" t="s">
+        <v>1136</v>
       </c>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49" t="s">
+      <c r="A40" s="48" t="s">
         <v>366</v>
       </c>
       <c r="B40" s="26" t="s">
@@ -20082,50 +20169,50 @@
       </c>
       <c r="C40" s="43"/>
       <c r="D40" s="44" t="s">
-        <v>1230</v>
-      </c>
-      <c r="E40" s="51" t="s">
-        <v>1135</v>
+        <v>1238</v>
+      </c>
+      <c r="E40" s="50" t="s">
+        <v>1140</v>
       </c>
       <c r="F40" s="43"/>
       <c r="G40" s="43"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="52" t="s">
+      <c r="A41" s="51" t="s">
         <v>372</v>
       </c>
-      <c r="B41" s="52" t="s">
+      <c r="B41" s="51" t="s">
         <v>372</v>
       </c>
       <c r="C41" s="43"/>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="49" t="s">
         <v>373</v>
       </c>
-      <c r="E41" s="51" t="s">
-        <v>1143</v>
+      <c r="E41" s="50" t="s">
+        <v>1148</v>
       </c>
       <c r="F41" s="43"/>
       <c r="G41" s="43"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="52" t="s">
+      <c r="A42" s="51" t="s">
         <v>352</v>
       </c>
-      <c r="B42" s="52" t="s">
+      <c r="B42" s="51" t="s">
         <v>352</v>
       </c>
       <c r="C42" s="43"/>
-      <c r="D42" s="50" t="s">
-        <v>1115</v>
+      <c r="D42" s="49" t="s">
+        <v>1120</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="F42" s="43"/>
       <c r="G42" s="43"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="49" t="s">
+      <c r="A43" s="48" t="s">
         <v>368</v>
       </c>
       <c r="B43" s="26" t="s">
@@ -20133,16 +20220,16 @@
       </c>
       <c r="C43" s="43"/>
       <c r="D43" s="44" t="s">
-        <v>1124</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>1128</v>
+        <v>1129</v>
+      </c>
+      <c r="E43" s="50" t="s">
+        <v>1133</v>
       </c>
       <c r="F43" s="43"/>
       <c r="G43" s="43"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="48" t="s">
         <v>368</v>
       </c>
       <c r="B44" s="26" t="s">
@@ -20150,16 +20237,16 @@
       </c>
       <c r="C44" s="43"/>
       <c r="D44" s="44" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E44" s="51" t="s">
-        <v>1129</v>
+        <v>1131</v>
+      </c>
+      <c r="E44" s="50" t="s">
+        <v>1134</v>
       </c>
       <c r="F44" s="43"/>
       <c r="G44" s="43"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B45" s="26" t="s">
@@ -20167,16 +20254,16 @@
       </c>
       <c r="C45" s="43"/>
       <c r="D45" s="44" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B46" s="26" t="s">
@@ -20184,16 +20271,16 @@
       </c>
       <c r="C46" s="43"/>
       <c r="D46" s="44" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E46" s="51" t="s">
-        <v>1142</v>
+        <v>1239</v>
+      </c>
+      <c r="E46" s="50" t="s">
+        <v>1147</v>
       </c>
       <c r="F46" s="43"/>
       <c r="G46" s="43"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B47" s="26" t="s">
@@ -20201,16 +20288,16 @@
       </c>
       <c r="C47" s="43"/>
       <c r="D47" s="44" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="F47" s="43"/>
       <c r="G47" s="43"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B48" s="26" t="s">
@@ -20218,33 +20305,33 @@
       </c>
       <c r="C48" s="43"/>
       <c r="D48" s="44" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="F48" s="43"/>
       <c r="G48" s="43"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="49" t="s">
-        <v>1222</v>
+      <c r="A49" s="48" t="s">
+        <v>1230</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C49" s="43"/>
       <c r="D49" s="44" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="F49" s="43"/>
       <c r="G49" s="43"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="49" t="s">
+      <c r="A50" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B50" s="26" t="s">
@@ -20252,33 +20339,33 @@
       </c>
       <c r="C50" s="43"/>
       <c r="D50" s="44" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="F50" s="43"/>
       <c r="G50" s="43"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49" t="s">
-        <v>1208</v>
+      <c r="A51" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C51" s="43"/>
       <c r="D51" s="44" t="s">
-        <v>1233</v>
-      </c>
-      <c r="E51" s="50" t="s">
-        <v>1084</v>
+        <v>1241</v>
+      </c>
+      <c r="E51" s="49" t="s">
+        <v>1089</v>
       </c>
       <c r="F51" s="43"/>
       <c r="G51" s="43"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49" t="s">
+      <c r="A52" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B52" s="26" t="s">
@@ -20286,33 +20373,33 @@
       </c>
       <c r="C52" s="43"/>
       <c r="D52" s="44" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="F52" s="43"/>
       <c r="G52" s="43"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="49" t="s">
-        <v>1208</v>
+      <c r="A53" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C53" s="43"/>
       <c r="D53" s="44" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="F53" s="43"/>
       <c r="G53" s="43"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="49" t="s">
+      <c r="A54" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B54" s="26" t="s">
@@ -20320,33 +20407,33 @@
       </c>
       <c r="C54" s="43"/>
       <c r="D54" s="44" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="F54" s="43"/>
       <c r="G54" s="43"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="49" t="s">
-        <v>1208</v>
+      <c r="A55" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C55" s="43"/>
       <c r="D55" s="44" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="F55" s="43"/>
       <c r="G55" s="43"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="49" t="s">
+      <c r="A56" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B56" s="26" t="s">
@@ -20354,33 +20441,33 @@
       </c>
       <c r="C56" s="43"/>
       <c r="D56" s="44" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="F56" s="43"/>
       <c r="G56" s="43"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
-        <v>1208</v>
+      <c r="A57" s="48" t="s">
+        <v>1216</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C57" s="43"/>
       <c r="D57" s="44" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="F57" s="43"/>
       <c r="G57" s="43"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
+      <c r="A58" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B58" s="26" t="s">
@@ -20388,33 +20475,33 @@
       </c>
       <c r="C58" s="43"/>
       <c r="D58" s="44" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="F58" s="43"/>
       <c r="G58" s="43"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="49" t="s">
-        <v>1207</v>
+      <c r="A59" s="48" t="s">
+        <v>1215</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="F59" s="43"/>
       <c r="G59" s="43"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="49" t="s">
+      <c r="A60" s="48" t="s">
         <v>352</v>
       </c>
       <c r="B60" s="26" t="s">
@@ -20422,16 +20509,16 @@
       </c>
       <c r="C60" s="43"/>
       <c r="D60" s="44" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="F60" s="43"/>
       <c r="G60" s="43"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
+      <c r="A61" s="48" t="s">
         <v>297</v>
       </c>
       <c r="B61" s="26" t="s">
@@ -20439,16 +20526,16 @@
       </c>
       <c r="C61" s="43"/>
       <c r="D61" s="44" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="F61" s="43"/>
       <c r="G61" s="43"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
+      <c r="A62" s="48" t="s">
         <v>384</v>
       </c>
       <c r="B62" s="26" t="s">
@@ -20456,110 +20543,124 @@
       </c>
       <c r="C62" s="43"/>
       <c r="D62" s="44" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E62" s="50" t="s">
-        <v>1166</v>
+        <v>1170</v>
+      </c>
+      <c r="E62" s="49" t="s">
+        <v>1171</v>
       </c>
       <c r="F62" s="43"/>
       <c r="G62" s="43"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="47" t="s">
+      <c r="A63" s="46" t="s">
         <v>366</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>366</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="E63" s="25" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="47" t="s">
-        <v>1207</v>
+      <c r="A64" s="46" t="s">
+        <v>1215</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="47" t="s">
-        <v>1207</v>
+      <c r="A65" s="46" t="s">
+        <v>1215</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>234</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="47" t="s">
+      <c r="A66" s="46" t="s">
         <v>297</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>234</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="47" t="s">
+      <c r="A67" s="46" t="s">
         <v>297</v>
       </c>
       <c r="B67" s="25" t="s">
         <v>387</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="47" t="s">
+      <c r="A68" s="46" t="s">
         <v>297</v>
       </c>
       <c r="B68" s="25" t="s">
         <v>387</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="49" t="s">
-        <v>1222</v>
-      </c>
-      <c r="B69" s="53" t="s">
+      <c r="A69" s="48" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B69" s="52" t="s">
         <v>234</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>1202</v>
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="46" t="s">
+        <v>352</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>1209</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -20611,563 +20712,563 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B2" s="54" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C2" s="55" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>1243</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>1246</v>
+        <v>1251</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="B3" s="54" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C3" s="55" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>1246</v>
+        <v>1255</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>1246</v>
+        <v>1258</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E4" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>1252</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>1246</v>
+        <v>1260</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E6" s="56" t="s">
         <v>1254</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C6" s="58" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>1254</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1256</v>
-      </c>
-      <c r="B7" s="54" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C7" s="57" t="s">
         <v>1257</v>
       </c>
-      <c r="C7" s="58" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E7" s="57" t="s">
-        <v>1246</v>
+      <c r="D7" s="55" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>1258</v>
-      </c>
-      <c r="E8" s="57" t="s">
-        <v>1246</v>
+        <v>1266</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E8" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E9" s="57" t="s">
-        <v>1246</v>
+        <v>1268</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>1262</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>1246</v>
+        <v>1270</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>1264</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>1246</v>
+        <v>1272</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C12" s="55" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>1266</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>1246</v>
+        <v>1274</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E12" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>1269</v>
-      </c>
-      <c r="C13" s="58" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>1268</v>
-      </c>
-      <c r="E13" s="59" t="s">
-        <v>1270</v>
+        <v>1276</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1271</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C14" s="58" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>1271</v>
-      </c>
-      <c r="E14" s="59" t="s">
-        <v>1270</v>
+        <v>1279</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B15" s="54" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C15" s="58" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>1275</v>
-      </c>
-      <c r="E15" s="59" t="s">
-        <v>1270</v>
+        <v>1281</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1276</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C16" s="58" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D16" s="56" t="s">
-        <v>1276</v>
-      </c>
-      <c r="E16" s="59" t="s">
-        <v>1270</v>
+        <v>1284</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="B17" s="54" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C17" s="58" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E17" s="57" t="s">
-        <v>1246</v>
+        <v>1286</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D17" s="55" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E17" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>1280</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>1246</v>
+        <v>1288</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E18" s="56" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1282</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C19" s="58" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D19" s="56" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E19" s="59" t="s">
-        <v>1270</v>
+        <v>1290</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C20" s="55" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D20" s="56" t="s">
-        <v>1285</v>
-      </c>
-      <c r="E20" s="59" t="s">
-        <v>1270</v>
+        <v>1293</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B21" s="61" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>1287</v>
-      </c>
-      <c r="E21" s="57" t="s">
-        <v>1290</v>
+        <v>1295</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E21" s="56" t="s">
+        <v>1298</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B22" s="62" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E22" s="59" t="s">
-        <v>1270</v>
+        <v>1299</v>
+      </c>
+      <c r="B22" s="61" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D22" s="55" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E22" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B23" s="54" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D23" s="56" t="s">
-        <v>1294</v>
-      </c>
-      <c r="E23" s="59" t="s">
-        <v>1270</v>
+        <v>1302</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D23" s="55" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E23" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1296</v>
-      </c>
-      <c r="B24" s="54" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C24" s="54" t="s">
         <v>1297</v>
       </c>
-      <c r="C24" s="55" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D24" s="56" t="s">
-        <v>1296</v>
-      </c>
-      <c r="E24" s="59" t="s">
-        <v>1270</v>
+      <c r="D24" s="55" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E24" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B25" s="54" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D25" s="56" t="s">
-        <v>1298</v>
-      </c>
-      <c r="E25" s="59" t="s">
-        <v>1270</v>
+        <v>1306</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E25" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1301</v>
-      </c>
-      <c r="B26" s="63" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C26" s="55" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D26" s="64" t="s">
-        <v>1303</v>
-      </c>
-      <c r="E26" s="59" t="s">
-        <v>1270</v>
+        <v>1309</v>
+      </c>
+      <c r="B26" s="62" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E26" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B27" s="63" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C27" s="65" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D27" s="64" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E27" s="59" t="s">
-        <v>1270</v>
+        <v>1312</v>
+      </c>
+      <c r="B27" s="62" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C27" s="64" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B28" s="63" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C28" s="65" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D28" s="64" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E28" s="59" t="s">
-        <v>1270</v>
+        <v>1315</v>
+      </c>
+      <c r="B28" s="62" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C28" s="64" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E28" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B29" s="63" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C29" s="65" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D29" s="64" t="s">
-        <v>1312</v>
-      </c>
-      <c r="E29" s="59" t="s">
-        <v>1270</v>
+        <v>1318</v>
+      </c>
+      <c r="B29" s="62" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C29" s="64" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E29" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1313</v>
-      </c>
-      <c r="B30" s="63" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C30" s="55" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E30" s="59" t="s">
-        <v>1270</v>
+        <v>1321</v>
+      </c>
+      <c r="B30" s="62" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E30" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1316</v>
-      </c>
-      <c r="B31" s="63" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C31" s="65" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D31" s="64" t="s">
-        <v>1318</v>
-      </c>
-      <c r="E31" s="59" t="s">
-        <v>1270</v>
+        <v>1324</v>
+      </c>
+      <c r="B31" s="62" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C31" s="64" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E31" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1319</v>
-      </c>
-      <c r="B32" s="54" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C32" s="55" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D32" s="56" t="s">
-        <v>1319</v>
-      </c>
-      <c r="E32" s="59" t="s">
-        <v>1270</v>
+        <v>1327</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D32" s="55" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="B33" s="60" t="s">
-        <v>1322</v>
-      </c>
-      <c r="C33" s="58" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D33" s="64" t="s">
-        <v>1321</v>
-      </c>
-      <c r="E33" s="59" t="s">
-        <v>1270</v>
+        <v>1329</v>
+      </c>
+      <c r="B33" s="59" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C33" s="57" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1324</v>
-      </c>
-      <c r="B34" s="60" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C34" s="58" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D34" s="56" t="s">
-        <v>1324</v>
-      </c>
-      <c r="E34" s="59" t="s">
-        <v>1270</v>
+        <v>1332</v>
+      </c>
+      <c r="B34" s="59" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C34" s="57" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E34" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
   </sheetData>
@@ -21221,274 +21322,274 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1326</v>
-      </c>
-      <c r="B2" s="54" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="56" t="s">
-        <v>1326</v>
-      </c>
-      <c r="E2" s="66" t="s">
-        <v>1290</v>
+        <v>1334</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>1298</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1328</v>
-      </c>
-      <c r="B3" s="54" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C3" s="55" t="s">
-        <v>1330</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>1328</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>1270</v>
+        <v>1336</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E3" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="56" t="s">
-        <v>1331</v>
-      </c>
-      <c r="E4" s="59" t="s">
-        <v>1270</v>
+        <v>1339</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="55" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="56" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E5" s="59" t="s">
-        <v>1270</v>
+        <v>1341</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C5" s="54"/>
+      <c r="D5" s="55" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1335</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="56" t="s">
-        <v>1335</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>1270</v>
+        <v>1343</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C6" s="54"/>
+      <c r="D6" s="55" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E6" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1337</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="56" t="s">
-        <v>1337</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>1270</v>
+        <v>1345</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C7" s="54"/>
+      <c r="D7" s="55" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E7" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>1340</v>
-      </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="56" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E8" s="59" t="s">
-        <v>1270</v>
+        <v>1347</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E8" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1341</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="56" t="s">
-        <v>1341</v>
-      </c>
-      <c r="E9" s="59" t="s">
-        <v>1270</v>
+        <v>1349</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="55" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E9" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1343</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="56" t="s">
-        <v>1343</v>
-      </c>
-      <c r="E10" s="59" t="s">
-        <v>1270</v>
+        <v>1351</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="55" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E10" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1345</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="56" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E11" s="59" t="s">
-        <v>1270</v>
+        <v>1353</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C11" s="54"/>
+      <c r="D11" s="55" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E11" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1347</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="56" t="s">
-        <v>1347</v>
-      </c>
-      <c r="E12" s="59" t="s">
-        <v>1270</v>
+        <v>1355</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C12" s="54"/>
+      <c r="D12" s="55" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E12" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1349</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E13" s="59" t="s">
-        <v>1270</v>
+        <v>1357</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C13" s="54"/>
+      <c r="D13" s="55" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1351</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="56" t="s">
-        <v>1351</v>
-      </c>
-      <c r="E14" s="59" t="s">
-        <v>1270</v>
+        <v>1359</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C14" s="54"/>
+      <c r="D14" s="55" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1353</v>
-      </c>
-      <c r="B15" s="54" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="56" t="s">
-        <v>1353</v>
-      </c>
-      <c r="E15" s="59" t="s">
-        <v>1270</v>
+        <v>1361</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C15" s="54"/>
+      <c r="D15" s="55" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1355</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="56" t="s">
-        <v>1355</v>
-      </c>
-      <c r="E16" s="59" t="s">
-        <v>1270</v>
+        <v>1363</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C16" s="54"/>
+      <c r="D16" s="55" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1357</v>
-      </c>
-      <c r="B17" s="54" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56" t="s">
-        <v>1357</v>
-      </c>
-      <c r="E17" s="59" t="s">
-        <v>1270</v>
+        <v>1365</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C17" s="54"/>
+      <c r="D17" s="55" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1359</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="56" t="s">
-        <v>1359</v>
-      </c>
-      <c r="E18" s="59" t="s">
-        <v>1270</v>
+        <v>1367</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C18" s="54"/>
+      <c r="D18" s="55" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E18" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1361</v>
-      </c>
-      <c r="B19" s="54" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="56" t="s">
-        <v>1361</v>
-      </c>
-      <c r="E19" s="59" t="s">
-        <v>1270</v>
+        <v>1369</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C19" s="54"/>
+      <c r="D19" s="55" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>1278</v>
       </c>
     </row>
   </sheetData>
@@ -21678,44 +21779,44 @@
         <f aca="false">NODES!$A$65</f>
         <v>fos</v>
       </c>
-      <c r="C2" s="67" t="n">
+      <c r="C2" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="67"/>
-      <c r="AG2" s="67"/>
-      <c r="AH2" s="67"/>
-      <c r="AI2" s="67"/>
-      <c r="AJ2" s="67"/>
-      <c r="AK2" s="67"/>
-      <c r="AL2" s="68" t="n">
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
+      <c r="W2" s="66"/>
+      <c r="X2" s="66"/>
+      <c r="Y2" s="66"/>
+      <c r="Z2" s="66"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
+      <c r="AC2" s="66"/>
+      <c r="AD2" s="66"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="67" t="n">
         <f aca="false">C2</f>
         <v>1</v>
       </c>
@@ -21729,45 +21830,45 @@
         <f aca="false">NODES!$A$64</f>
         <v>ren</v>
       </c>
-      <c r="C3" s="69" t="n">
+      <c r="C3" s="68" t="n">
         <f aca="false">1-C2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="69"/>
-      <c r="U3" s="69"/>
-      <c r="V3" s="69"/>
-      <c r="W3" s="69"/>
-      <c r="X3" s="69"/>
-      <c r="Y3" s="69"/>
-      <c r="Z3" s="69"/>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="69"/>
-      <c r="AC3" s="69"/>
-      <c r="AD3" s="69"/>
-      <c r="AE3" s="69"/>
-      <c r="AF3" s="69"/>
-      <c r="AG3" s="69"/>
-      <c r="AH3" s="69"/>
-      <c r="AI3" s="69"/>
-      <c r="AJ3" s="69"/>
-      <c r="AK3" s="69"/>
-      <c r="AL3" s="69" t="n">
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
+      <c r="V3" s="68"/>
+      <c r="W3" s="68"/>
+      <c r="X3" s="68"/>
+      <c r="Y3" s="68"/>
+      <c r="Z3" s="68"/>
+      <c r="AA3" s="68"/>
+      <c r="AB3" s="68"/>
+      <c r="AC3" s="68"/>
+      <c r="AD3" s="68"/>
+      <c r="AE3" s="68"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68" t="n">
         <f aca="false">1-AL2</f>
         <v>0</v>
       </c>
@@ -21781,44 +21882,44 @@
         <f aca="false">NODES!$A$66</f>
         <v>nuk</v>
       </c>
-      <c r="C4" s="67" t="n">
+      <c r="C4" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="68" t="n">
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="66"/>
+      <c r="Y4" s="66"/>
+      <c r="Z4" s="66"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="67" t="n">
         <f aca="false">C4</f>
         <v>0</v>
       </c>
@@ -21832,44 +21933,44 @@
         <f aca="false">NODES!$A$65</f>
         <v>fos</v>
       </c>
-      <c r="C5" s="67" t="n">
+      <c r="C5" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="67"/>
-      <c r="AG5" s="67"/>
-      <c r="AH5" s="67"/>
-      <c r="AI5" s="67"/>
-      <c r="AJ5" s="67"/>
-      <c r="AK5" s="67"/>
-      <c r="AL5" s="68" t="n">
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="66"/>
+      <c r="U5" s="66"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="66"/>
+      <c r="X5" s="66"/>
+      <c r="Y5" s="66"/>
+      <c r="Z5" s="66"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="67" t="n">
         <f aca="false">C5</f>
         <v>1</v>
       </c>
@@ -21883,45 +21984,45 @@
         <f aca="false">NODES!$A$64</f>
         <v>ren</v>
       </c>
-      <c r="C6" s="69" t="n">
+      <c r="C6" s="68" t="n">
         <f aca="false">1-C5-C4</f>
         <v>0</v>
       </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="69"/>
-      <c r="Y6" s="69"/>
-      <c r="Z6" s="69"/>
-      <c r="AA6" s="69"/>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="69"/>
-      <c r="AD6" s="69"/>
-      <c r="AE6" s="69"/>
-      <c r="AF6" s="69"/>
-      <c r="AG6" s="69"/>
-      <c r="AH6" s="69"/>
-      <c r="AI6" s="69"/>
-      <c r="AJ6" s="69"/>
-      <c r="AK6" s="69"/>
-      <c r="AL6" s="69" t="n">
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
+      <c r="U6" s="68"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="68"/>
+      <c r="Z6" s="68"/>
+      <c r="AA6" s="68"/>
+      <c r="AB6" s="68"/>
+      <c r="AC6" s="68"/>
+      <c r="AD6" s="68"/>
+      <c r="AE6" s="68"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68" t="n">
         <f aca="false">1-AL5-AL4</f>
         <v>0</v>
       </c>
@@ -21935,44 +22036,44 @@
         <f aca="false">NODES!$A$65</f>
         <v>fos</v>
       </c>
-      <c r="C7" s="67" t="n">
+      <c r="C7" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="67"/>
-      <c r="P7" s="67"/>
-      <c r="Q7" s="67"/>
-      <c r="R7" s="67"/>
-      <c r="S7" s="67"/>
-      <c r="T7" s="67"/>
-      <c r="U7" s="67"/>
-      <c r="V7" s="67"/>
-      <c r="W7" s="67"/>
-      <c r="X7" s="67"/>
-      <c r="Y7" s="67"/>
-      <c r="Z7" s="67"/>
-      <c r="AA7" s="67"/>
-      <c r="AB7" s="67"/>
-      <c r="AC7" s="67"/>
-      <c r="AD7" s="67"/>
-      <c r="AE7" s="67"/>
-      <c r="AF7" s="67"/>
-      <c r="AG7" s="67"/>
-      <c r="AH7" s="67"/>
-      <c r="AI7" s="67"/>
-      <c r="AJ7" s="67"/>
-      <c r="AK7" s="67"/>
-      <c r="AL7" s="68" t="n">
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="66"/>
+      <c r="T7" s="66"/>
+      <c r="U7" s="66"/>
+      <c r="V7" s="66"/>
+      <c r="W7" s="66"/>
+      <c r="X7" s="66"/>
+      <c r="Y7" s="66"/>
+      <c r="Z7" s="66"/>
+      <c r="AA7" s="66"/>
+      <c r="AB7" s="66"/>
+      <c r="AC7" s="66"/>
+      <c r="AD7" s="66"/>
+      <c r="AE7" s="66"/>
+      <c r="AF7" s="66"/>
+      <c r="AG7" s="66"/>
+      <c r="AH7" s="66"/>
+      <c r="AI7" s="66"/>
+      <c r="AJ7" s="66"/>
+      <c r="AK7" s="66"/>
+      <c r="AL7" s="67" t="n">
         <f aca="false">C7</f>
         <v>0</v>
       </c>
@@ -21986,45 +22087,45 @@
         <f aca="false">NODES!$A$64</f>
         <v>ren</v>
       </c>
-      <c r="C8" s="69" t="n">
+      <c r="C8" s="68" t="n">
         <f aca="false">1-C7</f>
         <v>1</v>
       </c>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="69"/>
-      <c r="T8" s="69"/>
-      <c r="U8" s="69"/>
-      <c r="V8" s="69"/>
-      <c r="W8" s="69"/>
-      <c r="X8" s="69"/>
-      <c r="Y8" s="69"/>
-      <c r="Z8" s="69"/>
-      <c r="AA8" s="69"/>
-      <c r="AB8" s="69"/>
-      <c r="AC8" s="69"/>
-      <c r="AD8" s="69"/>
-      <c r="AE8" s="69"/>
-      <c r="AF8" s="69"/>
-      <c r="AG8" s="69"/>
-      <c r="AH8" s="69"/>
-      <c r="AI8" s="69"/>
-      <c r="AJ8" s="69"/>
-      <c r="AK8" s="69"/>
-      <c r="AL8" s="69" t="n">
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="68"/>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="68"/>
+      <c r="T8" s="68"/>
+      <c r="U8" s="68"/>
+      <c r="V8" s="68"/>
+      <c r="W8" s="68"/>
+      <c r="X8" s="68"/>
+      <c r="Y8" s="68"/>
+      <c r="Z8" s="68"/>
+      <c r="AA8" s="68"/>
+      <c r="AB8" s="68"/>
+      <c r="AC8" s="68"/>
+      <c r="AD8" s="68"/>
+      <c r="AE8" s="68"/>
+      <c r="AF8" s="68"/>
+      <c r="AG8" s="68"/>
+      <c r="AH8" s="68"/>
+      <c r="AI8" s="68"/>
+      <c r="AJ8" s="68"/>
+      <c r="AK8" s="68"/>
+      <c r="AL8" s="68" t="n">
         <f aca="false">1-AL7</f>
         <v>1</v>
       </c>
@@ -22038,44 +22139,44 @@
         <f aca="false">NODES!$A$65</f>
         <v>fos</v>
       </c>
-      <c r="C9" s="67" t="n">
+      <c r="C9" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="67"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="67"/>
-      <c r="P9" s="67"/>
-      <c r="Q9" s="67"/>
-      <c r="R9" s="67"/>
-      <c r="S9" s="67"/>
-      <c r="T9" s="67"/>
-      <c r="U9" s="67"/>
-      <c r="V9" s="67"/>
-      <c r="W9" s="67"/>
-      <c r="X9" s="67"/>
-      <c r="Y9" s="67"/>
-      <c r="Z9" s="67"/>
-      <c r="AA9" s="67"/>
-      <c r="AB9" s="67"/>
-      <c r="AC9" s="67"/>
-      <c r="AD9" s="67"/>
-      <c r="AE9" s="67"/>
-      <c r="AF9" s="67"/>
-      <c r="AG9" s="67"/>
-      <c r="AH9" s="67"/>
-      <c r="AI9" s="67"/>
-      <c r="AJ9" s="67"/>
-      <c r="AK9" s="67"/>
-      <c r="AL9" s="68" t="n">
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="66"/>
+      <c r="M9" s="66"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="66"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="66"/>
+      <c r="U9" s="66"/>
+      <c r="V9" s="66"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="66"/>
+      <c r="Y9" s="66"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="66"/>
+      <c r="AB9" s="66"/>
+      <c r="AC9" s="66"/>
+      <c r="AD9" s="66"/>
+      <c r="AE9" s="66"/>
+      <c r="AF9" s="66"/>
+      <c r="AG9" s="66"/>
+      <c r="AH9" s="66"/>
+      <c r="AI9" s="66"/>
+      <c r="AJ9" s="66"/>
+      <c r="AK9" s="66"/>
+      <c r="AL9" s="67" t="n">
         <f aca="false">C9</f>
         <v>1</v>
       </c>
@@ -22089,44 +22190,44 @@
         <f aca="false">NODES!$A$65</f>
         <v>fos</v>
       </c>
-      <c r="C10" s="67" t="n">
+      <c r="C10" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="67"/>
-      <c r="M10" s="67"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="67"/>
-      <c r="P10" s="67"/>
-      <c r="Q10" s="67"/>
-      <c r="R10" s="67"/>
-      <c r="S10" s="67"/>
-      <c r="T10" s="67"/>
-      <c r="U10" s="67"/>
-      <c r="V10" s="67"/>
-      <c r="W10" s="67"/>
-      <c r="X10" s="67"/>
-      <c r="Y10" s="67"/>
-      <c r="Z10" s="67"/>
-      <c r="AA10" s="67"/>
-      <c r="AB10" s="67"/>
-      <c r="AC10" s="67"/>
-      <c r="AD10" s="67"/>
-      <c r="AE10" s="67"/>
-      <c r="AF10" s="67"/>
-      <c r="AG10" s="67"/>
-      <c r="AH10" s="67"/>
-      <c r="AI10" s="67"/>
-      <c r="AJ10" s="67"/>
-      <c r="AK10" s="67"/>
-      <c r="AL10" s="68" t="n">
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66"/>
+      <c r="U10" s="66"/>
+      <c r="V10" s="66"/>
+      <c r="W10" s="66"/>
+      <c r="X10" s="66"/>
+      <c r="Y10" s="66"/>
+      <c r="Z10" s="66"/>
+      <c r="AA10" s="66"/>
+      <c r="AB10" s="66"/>
+      <c r="AC10" s="66"/>
+      <c r="AD10" s="66"/>
+      <c r="AE10" s="66"/>
+      <c r="AF10" s="66"/>
+      <c r="AG10" s="66"/>
+      <c r="AH10" s="66"/>
+      <c r="AI10" s="66"/>
+      <c r="AJ10" s="66"/>
+      <c r="AK10" s="66"/>
+      <c r="AL10" s="67" t="n">
         <f aca="false">C10</f>
         <v>1</v>
       </c>
@@ -22140,45 +22241,45 @@
         <f aca="false">NODES!$A$64</f>
         <v>ren</v>
       </c>
-      <c r="C11" s="69" t="n">
+      <c r="C11" s="68" t="n">
         <f aca="false">1-C10</f>
         <v>0</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="69"/>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="69"/>
-      <c r="U11" s="69"/>
-      <c r="V11" s="69"/>
-      <c r="W11" s="69"/>
-      <c r="X11" s="69"/>
-      <c r="Y11" s="69"/>
-      <c r="Z11" s="69"/>
-      <c r="AA11" s="69"/>
-      <c r="AB11" s="69"/>
-      <c r="AC11" s="69"/>
-      <c r="AD11" s="69"/>
-      <c r="AE11" s="69"/>
-      <c r="AF11" s="69"/>
-      <c r="AG11" s="69"/>
-      <c r="AH11" s="69"/>
-      <c r="AI11" s="69"/>
-      <c r="AJ11" s="69"/>
-      <c r="AK11" s="69"/>
-      <c r="AL11" s="69" t="n">
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="68"/>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
+      <c r="T11" s="68"/>
+      <c r="U11" s="68"/>
+      <c r="V11" s="68"/>
+      <c r="W11" s="68"/>
+      <c r="X11" s="68"/>
+      <c r="Y11" s="68"/>
+      <c r="Z11" s="68"/>
+      <c r="AA11" s="68"/>
+      <c r="AB11" s="68"/>
+      <c r="AC11" s="68"/>
+      <c r="AD11" s="68"/>
+      <c r="AE11" s="68"/>
+      <c r="AF11" s="68"/>
+      <c r="AG11" s="68"/>
+      <c r="AH11" s="68"/>
+      <c r="AI11" s="68"/>
+      <c r="AJ11" s="68"/>
+      <c r="AK11" s="68"/>
+      <c r="AL11" s="68" t="n">
         <f aca="false">1-AL10</f>
         <v>0</v>
       </c>

--- a/SEPIA/SEPIA_config.xlsx
+++ b/SEPIA/SEPIA_config.xlsx
@@ -3521,18 +3521,12 @@
     <t xml:space="preserve">proeoffdch</t>
   </si>
   <si>
-    <t xml:space="preserve">VRE connected electrolysers</t>
+    <t xml:space="preserve">hybrid electrolysers</t>
   </si>
   <si>
     <t xml:space="preserve">pregenvrehyd</t>
   </si>
   <si>
-    <t xml:space="preserve">Vre connected electrolysers losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proesolhlos</t>
-  </si>
-  <si>
     <t xml:space="preserve">FLC electrolysis</t>
   </si>
   <si>
@@ -4029,6 +4023,12 @@
   </si>
   <si>
     <t xml:space="preserve">emmbmmetatm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biomass to methanol CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emmbmmetstm</t>
   </si>
   <si>
     <t xml:space="preserve">OCGT emissions</t>
@@ -17490,7 +17490,7 @@
         <v>391</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>393</v>
+        <v>196</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>1033</v>
@@ -17504,7 +17504,7 @@
         <v>391</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>393</v>
+        <v>196</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>1035</v>
@@ -17518,7 +17518,7 @@
         <v>391</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>393</v>
+        <v>196</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>1037</v>
@@ -17532,7 +17532,7 @@
         <v>391</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>393</v>
+        <v>196</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>1039</v>
@@ -17543,7 +17543,7 @@
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="25" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>196</v>
@@ -17557,12 +17557,12 @@
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>393</v>
+        <v>194</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D337" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="D337" s="1" t="s">
         <v>1043</v>
       </c>
       <c r="E337" s="1" t="s">
@@ -17571,10 +17571,10 @@
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>196</v>
+        <v>282</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>1045</v>
@@ -17588,7 +17588,7 @@
         <v>196</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>282</v>
+        <v>201</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>1047</v>
@@ -17599,10 +17599,10 @@
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>1049</v>
@@ -17616,7 +17616,7 @@
         <v>238</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>186</v>
+        <v>282</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>1051</v>
@@ -17630,7 +17630,7 @@
         <v>238</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>282</v>
+        <v>189</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>1053</v>
@@ -17639,20 +17639,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A343" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B343" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E343" s="1" t="s">
-        <v>1056</v>
-      </c>
-    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -17718,10 +17705,10 @@
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="43" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F2" s="43"/>
       <c r="G2" s="43"/>
@@ -17735,10 +17722,10 @@
       </c>
       <c r="C3" s="43"/>
       <c r="D3" s="44" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="F3" s="43"/>
       <c r="G3" s="43"/>
@@ -17752,10 +17739,10 @@
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="44" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>1059</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>1061</v>
       </c>
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
@@ -17769,10 +17756,10 @@
       </c>
       <c r="C5" s="43"/>
       <c r="D5" s="44" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F5" s="43"/>
       <c r="G5" s="43"/>
@@ -17786,10 +17773,10 @@
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="44" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="43"/>
@@ -17803,10 +17790,10 @@
       </c>
       <c r="C7" s="43"/>
       <c r="D7" s="44" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F7" s="43"/>
       <c r="G7" s="43"/>
@@ -17820,10 +17807,10 @@
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="44" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F8" s="43"/>
       <c r="G8" s="43"/>
@@ -17837,10 +17824,10 @@
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="44" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
@@ -17854,10 +17841,10 @@
       </c>
       <c r="C10" s="43"/>
       <c r="D10" s="44" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="F10" s="43"/>
       <c r="G10" s="43"/>
@@ -17874,7 +17861,7 @@
         <v>782</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F11" s="43"/>
       <c r="G11" s="43"/>
@@ -17891,7 +17878,7 @@
         <v>780</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
@@ -17905,10 +17892,10 @@
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="44" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F13" s="43"/>
       <c r="G13" s="43"/>
@@ -17922,10 +17909,10 @@
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="44" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E14" s="44" t="s">
         <v>1076</v>
-      </c>
-      <c r="E14" s="44" t="s">
-        <v>1078</v>
       </c>
       <c r="F14" s="43"/>
       <c r="G14" s="43"/>
@@ -17938,13 +17925,13 @@
         <v>338</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="D15" s="44" t="s">
         <v>771</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
@@ -17957,13 +17944,13 @@
         <v>338</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>773</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="F16" s="43"/>
       <c r="G16" s="43"/>
@@ -17977,10 +17964,10 @@
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="44" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="F17" s="43"/>
       <c r="G17" s="43"/>
@@ -17994,10 +17981,10 @@
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="44" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E18" s="44" t="s">
         <v>1083</v>
-      </c>
-      <c r="E18" s="44" t="s">
-        <v>1085</v>
       </c>
       <c r="F18" s="43"/>
       <c r="G18" s="43"/>
@@ -18011,10 +17998,10 @@
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="44" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="F19" s="43"/>
       <c r="G19" s="43"/>
@@ -18031,7 +18018,7 @@
         <v>877</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="F20" s="43"/>
       <c r="G20" s="43"/>
@@ -18048,7 +18035,7 @@
         <v>766</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43"/>
@@ -18065,7 +18052,7 @@
         <v>766</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="F22" s="43"/>
       <c r="G22" s="43"/>
@@ -18082,7 +18069,7 @@
         <v>764</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="F23" s="43"/>
       <c r="G23" s="43"/>
@@ -18099,7 +18086,7 @@
         <v>764</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="F24" s="43"/>
       <c r="G24" s="43"/>
@@ -18112,13 +18099,13 @@
         <v>389</v>
       </c>
       <c r="C25" s="43" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E25" s="44" t="s">
         <v>1093</v>
-      </c>
-      <c r="D25" s="44" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E25" s="44" t="s">
-        <v>1095</v>
       </c>
       <c r="F25" s="43"/>
       <c r="G25" s="43"/>
@@ -18134,10 +18121,10 @@
         <v>126</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="F26" s="43"/>
       <c r="G26" s="43"/>
@@ -18153,10 +18140,10 @@
         <v>133</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
@@ -18172,10 +18159,10 @@
         <v>119</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="F28" s="43"/>
       <c r="G28" s="43"/>
@@ -18188,13 +18175,13 @@
         <v>338</v>
       </c>
       <c r="C29" s="43" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E29" s="44" t="s">
         <v>1102</v>
-      </c>
-      <c r="D29" s="44" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>1104</v>
       </c>
       <c r="F29" s="43"/>
       <c r="G29" s="43"/>
@@ -18207,13 +18194,13 @@
         <v>338</v>
       </c>
       <c r="C30" s="43" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E30" s="44" t="s">
         <v>1105</v>
-      </c>
-      <c r="D30" s="44" t="s">
-        <v>1106</v>
-      </c>
-      <c r="E30" s="44" t="s">
-        <v>1107</v>
       </c>
       <c r="F30" s="43"/>
       <c r="G30" s="43"/>
@@ -18227,10 +18214,10 @@
       </c>
       <c r="C31" s="43"/>
       <c r="D31" s="44" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F31" s="43"/>
       <c r="G31" s="43"/>
@@ -18247,7 +18234,7 @@
         <v>357</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="F32" s="43"/>
       <c r="G32" s="43"/>
@@ -18261,10 +18248,10 @@
       </c>
       <c r="C33" s="43"/>
       <c r="D33" s="44" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="F33" s="43"/>
       <c r="G33" s="43"/>
@@ -18281,7 +18268,7 @@
         <v>934</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
@@ -18294,13 +18281,13 @@
         <v>362</v>
       </c>
       <c r="C35" s="43" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E35" s="44" t="s">
         <v>1114</v>
-      </c>
-      <c r="D35" s="44" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E35" s="44" t="s">
-        <v>1116</v>
       </c>
       <c r="F35" s="43"/>
       <c r="G35" s="43"/>
@@ -18314,10 +18301,10 @@
       </c>
       <c r="C36" s="43"/>
       <c r="D36" s="44" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="F36" s="43"/>
       <c r="G36" s="43"/>
@@ -18333,10 +18320,10 @@
         <v>129</v>
       </c>
       <c r="D37" s="44" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E37" s="44" t="s">
         <v>1117</v>
-      </c>
-      <c r="E37" s="44" t="s">
-        <v>1119</v>
       </c>
       <c r="F37" s="43"/>
       <c r="G37" s="43"/>
@@ -18350,10 +18337,10 @@
       </c>
       <c r="C38" s="43"/>
       <c r="D38" s="44" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="F38" s="43"/>
       <c r="G38" s="43"/>
@@ -18367,10 +18354,10 @@
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
@@ -18384,10 +18371,10 @@
       </c>
       <c r="C40" s="43"/>
       <c r="D40" s="44" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="F40" s="43"/>
       <c r="G40" s="43"/>
@@ -18401,10 +18388,10 @@
       </c>
       <c r="C41" s="43"/>
       <c r="D41" s="44" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E41" s="44" t="s">
         <v>1124</v>
-      </c>
-      <c r="E41" s="44" t="s">
-        <v>1126</v>
       </c>
       <c r="F41" s="43"/>
       <c r="G41" s="43"/>
@@ -18418,10 +18405,10 @@
       </c>
       <c r="C42" s="43"/>
       <c r="D42" s="44" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="F42" s="43"/>
       <c r="G42" s="43"/>
@@ -18435,10 +18422,10 @@
       </c>
       <c r="C43" s="43"/>
       <c r="D43" s="44" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="F43" s="43"/>
       <c r="G43" s="43"/>
@@ -18452,10 +18439,10 @@
       </c>
       <c r="C44" s="43"/>
       <c r="D44" s="44" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F44" s="43"/>
       <c r="G44" s="43"/>
@@ -18469,10 +18456,10 @@
       </c>
       <c r="C45" s="43"/>
       <c r="D45" s="44" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -18488,10 +18475,10 @@
         <v>411</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="F46" s="43"/>
       <c r="G46" s="43"/>
@@ -18505,10 +18492,10 @@
       </c>
       <c r="C47" s="43"/>
       <c r="D47" s="44" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="F47" s="43"/>
       <c r="G47" s="43"/>
@@ -18522,10 +18509,10 @@
       </c>
       <c r="C48" s="43"/>
       <c r="D48" s="44" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E48" s="50" t="s">
         <v>1135</v>
-      </c>
-      <c r="E48" s="50" t="s">
-        <v>1137</v>
       </c>
       <c r="F48" s="43"/>
       <c r="G48" s="43"/>
@@ -18541,10 +18528,10 @@
         <v>411</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="F49" s="43"/>
       <c r="G49" s="43"/>
@@ -18560,10 +18547,10 @@
         <v>411</v>
       </c>
       <c r="D50" s="44" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E50" s="50" t="s">
         <v>1138</v>
-      </c>
-      <c r="E50" s="50" t="s">
-        <v>1140</v>
       </c>
       <c r="F50" s="43"/>
       <c r="G50" s="43"/>
@@ -18577,10 +18564,10 @@
       </c>
       <c r="C51" s="43"/>
       <c r="D51" s="44" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="F51" s="43"/>
       <c r="G51" s="43"/>
@@ -18594,10 +18581,10 @@
       </c>
       <c r="C52" s="43"/>
       <c r="D52" s="44" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="F52" s="43"/>
       <c r="G52" s="43"/>
@@ -18614,7 +18601,7 @@
         <v>547</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="F53" s="43"/>
       <c r="G53" s="43"/>
@@ -18628,10 +18615,10 @@
       </c>
       <c r="C54" s="43"/>
       <c r="D54" s="44" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="F54" s="43"/>
       <c r="G54" s="43"/>
@@ -18645,10 +18632,10 @@
       </c>
       <c r="C55" s="43"/>
       <c r="D55" s="44" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="F55" s="43"/>
       <c r="G55" s="43"/>
@@ -18665,7 +18652,7 @@
         <v>373</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="F56" s="43"/>
       <c r="G56" s="43"/>
@@ -18682,7 +18669,7 @@
         <v>375</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="F57" s="43"/>
       <c r="G57" s="43"/>
@@ -18696,10 +18683,10 @@
       </c>
       <c r="C58" s="43"/>
       <c r="D58" s="44" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="F58" s="43"/>
       <c r="G58" s="43"/>
@@ -18713,10 +18700,10 @@
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E59" s="44" t="s">
         <v>1150</v>
-      </c>
-      <c r="E59" s="44" t="s">
-        <v>1152</v>
       </c>
       <c r="F59" s="43"/>
       <c r="G59" s="43"/>
@@ -18732,10 +18719,10 @@
         <v>411</v>
       </c>
       <c r="D60" s="44" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="F60" s="43"/>
       <c r="G60" s="43"/>
@@ -18749,10 +18736,10 @@
       </c>
       <c r="C61" s="43"/>
       <c r="D61" s="44" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E61" s="44" t="s">
         <v>1153</v>
-      </c>
-      <c r="E61" s="44" t="s">
-        <v>1155</v>
       </c>
       <c r="F61" s="43"/>
       <c r="G61" s="43"/>
@@ -18766,10 +18753,10 @@
       </c>
       <c r="C62" s="43"/>
       <c r="D62" s="44" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="F62" s="43"/>
       <c r="G62" s="43"/>
@@ -18783,10 +18770,10 @@
       </c>
       <c r="C63" s="43"/>
       <c r="D63" s="44" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="F63" s="43"/>
       <c r="G63" s="43"/>
@@ -18800,10 +18787,10 @@
       </c>
       <c r="C64" s="43"/>
       <c r="D64" s="44" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="F64" s="43"/>
       <c r="G64" s="43"/>
@@ -18817,10 +18804,10 @@
       </c>
       <c r="C65" s="43"/>
       <c r="D65" s="44" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="F65" s="43"/>
       <c r="G65" s="43"/>
@@ -18834,10 +18821,10 @@
       </c>
       <c r="C66" s="43"/>
       <c r="D66" s="44" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="F66" s="43"/>
       <c r="G66" s="43"/>
@@ -18851,10 +18838,10 @@
       </c>
       <c r="C67" s="43"/>
       <c r="D67" s="44" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="F67" s="43"/>
       <c r="G67" s="43"/>
@@ -18868,10 +18855,10 @@
       </c>
       <c r="C68" s="43"/>
       <c r="D68" s="44" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E68" s="44" t="s">
         <v>1164</v>
-      </c>
-      <c r="E68" s="44" t="s">
-        <v>1166</v>
       </c>
       <c r="F68" s="43"/>
       <c r="G68" s="43"/>
@@ -18888,7 +18875,7 @@
         <v>383</v>
       </c>
       <c r="E69" s="49" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="F69" s="43"/>
       <c r="G69" s="43"/>
@@ -18902,10 +18889,10 @@
       </c>
       <c r="C70" s="43"/>
       <c r="D70" s="49" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="E70" s="49" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="F70" s="43"/>
       <c r="G70" s="43"/>
@@ -18919,10 +18906,10 @@
       </c>
       <c r="C71" s="43"/>
       <c r="D71" s="49" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E71" s="49" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="F71" s="43"/>
       <c r="G71" s="43"/>
@@ -18936,10 +18923,10 @@
       </c>
       <c r="C72" s="43"/>
       <c r="D72" s="49" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="E72" s="49" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F72" s="43"/>
       <c r="G72" s="43"/>
@@ -18953,10 +18940,10 @@
       </c>
       <c r="C73" s="43"/>
       <c r="D73" s="49" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="E73" s="49" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="F73" s="43"/>
       <c r="G73" s="43"/>
@@ -18970,10 +18957,10 @@
       </c>
       <c r="C74" s="43"/>
       <c r="D74" s="49" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="E74" s="49" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="F74" s="43"/>
       <c r="G74" s="43"/>
@@ -18987,10 +18974,10 @@
       </c>
       <c r="C75" s="43"/>
       <c r="D75" s="49" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="E75" s="49" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="F75" s="43"/>
       <c r="G75" s="43"/>
@@ -19004,10 +18991,10 @@
       </c>
       <c r="C76" s="43"/>
       <c r="D76" s="49" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E76" s="49" t="s">
         <v>1178</v>
-      </c>
-      <c r="E76" s="49" t="s">
-        <v>1180</v>
       </c>
       <c r="F76" s="43"/>
       <c r="G76" s="43"/>
@@ -19024,7 +19011,7 @@
         <v>446</v>
       </c>
       <c r="E77" s="49" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -19038,10 +19025,10 @@
       </c>
       <c r="C78" s="43"/>
       <c r="D78" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E78" s="49" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="F78" s="43"/>
       <c r="G78" s="43"/>
@@ -19055,10 +19042,10 @@
       </c>
       <c r="C79" s="43"/>
       <c r="D79" s="49" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="E79" s="49" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="F79" s="43"/>
       <c r="G79" s="43"/>
@@ -19072,10 +19059,10 @@
       </c>
       <c r="C80" s="43"/>
       <c r="D80" s="49" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="E80" s="49" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="F80" s="43"/>
       <c r="G80" s="43"/>
@@ -19091,10 +19078,10 @@
         <v>1005</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19105,10 +19092,10 @@
         <v>350</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>1188</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19119,10 +19106,10 @@
         <v>338</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19133,10 +19120,10 @@
         <v>338</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19147,10 +19134,10 @@
         <v>340</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19161,10 +19148,10 @@
         <v>338</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19175,13 +19162,13 @@
         <v>338</v>
       </c>
       <c r="C87" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>1199</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>1200</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19192,10 +19179,10 @@
         <v>338</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19206,10 +19193,10 @@
         <v>338</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19220,10 +19207,10 @@
         <v>338</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19234,10 +19221,10 @@
         <v>354</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19248,9 +19235,23 @@
         <v>350</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="E92" s="1" t="s">
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="46" t="s">
+        <v>354</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D93" s="25" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>1210</v>
       </c>
     </row>
@@ -19517,10 +19518,10 @@
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="43" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F2" s="43"/>
       <c r="G2" s="43"/>
@@ -19534,10 +19535,10 @@
       </c>
       <c r="C3" s="43"/>
       <c r="D3" s="44" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="F3" s="43"/>
       <c r="G3" s="43"/>
@@ -19551,10 +19552,10 @@
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="44" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
@@ -19571,7 +19572,7 @@
         <v>1211</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F5" s="43"/>
       <c r="G5" s="43"/>
@@ -19585,10 +19586,10 @@
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="44" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="43"/>
@@ -19602,10 +19603,10 @@
       </c>
       <c r="C7" s="43"/>
       <c r="D7" s="44" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="F7" s="43"/>
       <c r="G7" s="43"/>
@@ -19619,10 +19620,10 @@
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="44" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="F8" s="43"/>
       <c r="G8" s="43"/>
@@ -19639,7 +19640,7 @@
         <v>1212</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
@@ -19656,7 +19657,7 @@
         <v>1213</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="F10" s="43"/>
       <c r="G10" s="43"/>
@@ -19673,7 +19674,7 @@
         <v>1214</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="F11" s="43"/>
       <c r="G11" s="43"/>
@@ -19687,10 +19688,10 @@
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="44" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
@@ -19704,10 +19705,10 @@
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="44" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="F13" s="43"/>
       <c r="G13" s="43"/>
@@ -19724,7 +19725,7 @@
         <v>1217</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F14" s="43"/>
       <c r="G14" s="43"/>
@@ -19741,7 +19742,7 @@
         <v>1218</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
@@ -19792,7 +19793,7 @@
         <v>1223</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F18" s="43"/>
       <c r="G18" s="43"/>
@@ -19809,7 +19810,7 @@
         <v>1224</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F19" s="43"/>
       <c r="G19" s="43"/>
@@ -19826,7 +19827,7 @@
         <v>1225</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="F20" s="43"/>
       <c r="G20" s="43"/>
@@ -19877,7 +19878,7 @@
         <v>877</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="F23" s="43"/>
       <c r="G23" s="43"/>
@@ -19893,10 +19894,10 @@
         <v>126</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="F24" s="43"/>
       <c r="G24" s="43"/>
@@ -19912,10 +19913,10 @@
         <v>133</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="F25" s="43"/>
       <c r="G25" s="43"/>
@@ -19929,10 +19930,10 @@
       </c>
       <c r="C26" s="43"/>
       <c r="D26" s="44" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="E26" s="49" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="F26" s="43"/>
       <c r="G26" s="43"/>
@@ -19948,10 +19949,10 @@
         <v>119</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
@@ -19968,7 +19969,7 @@
         <v>1234</v>
       </c>
       <c r="E28" s="49" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F28" s="43"/>
       <c r="G28" s="43"/>
@@ -19981,13 +19982,13 @@
         <v>234</v>
       </c>
       <c r="C29" s="43" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E29" s="44" t="s">
         <v>1102</v>
-      </c>
-      <c r="D29" s="44" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>1104</v>
       </c>
       <c r="F29" s="43"/>
       <c r="G29" s="43"/>
@@ -20001,10 +20002,10 @@
       </c>
       <c r="C30" s="43"/>
       <c r="D30" s="44" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F30" s="43"/>
       <c r="G30" s="43"/>
@@ -20019,7 +20020,7 @@
       <c r="C31" s="43"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="F31" s="43"/>
       <c r="G31" s="43"/>
@@ -20036,7 +20037,7 @@
         <v>357</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="F32" s="43"/>
       <c r="G32" s="43"/>
@@ -20050,10 +20051,10 @@
       </c>
       <c r="C33" s="43"/>
       <c r="D33" s="44" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="F33" s="43"/>
       <c r="G33" s="43"/>
@@ -20067,10 +20068,10 @@
       </c>
       <c r="C34" s="43"/>
       <c r="D34" s="44" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
@@ -20084,10 +20085,10 @@
       </c>
       <c r="C35" s="43"/>
       <c r="D35" s="44" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="F35" s="43"/>
       <c r="G35" s="43"/>
@@ -20101,10 +20102,10 @@
       </c>
       <c r="C36" s="43"/>
       <c r="D36" s="44" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="F36" s="43"/>
       <c r="G36" s="43"/>
@@ -20121,7 +20122,7 @@
         <v>1236</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="F37" s="43"/>
       <c r="G37" s="43"/>
@@ -20138,7 +20139,7 @@
         <v>1237</v>
       </c>
       <c r="E38" s="49" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="F38" s="43"/>
       <c r="G38" s="43"/>
@@ -20152,10 +20153,10 @@
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
@@ -20172,7 +20173,7 @@
         <v>1238</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="F40" s="43"/>
       <c r="G40" s="43"/>
@@ -20189,7 +20190,7 @@
         <v>373</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="F41" s="43"/>
       <c r="G41" s="43"/>
@@ -20203,10 +20204,10 @@
       </c>
       <c r="C42" s="43"/>
       <c r="D42" s="49" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="F42" s="43"/>
       <c r="G42" s="43"/>
@@ -20220,10 +20221,10 @@
       </c>
       <c r="C43" s="43"/>
       <c r="D43" s="44" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="F43" s="43"/>
       <c r="G43" s="43"/>
@@ -20237,10 +20238,10 @@
       </c>
       <c r="C44" s="43"/>
       <c r="D44" s="44" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="F44" s="43"/>
       <c r="G44" s="43"/>
@@ -20254,10 +20255,10 @@
       </c>
       <c r="C45" s="43"/>
       <c r="D45" s="44" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -20274,7 +20275,7 @@
         <v>1239</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="F46" s="43"/>
       <c r="G46" s="43"/>
@@ -20291,7 +20292,7 @@
         <v>1240</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="F47" s="43"/>
       <c r="G47" s="43"/>
@@ -20305,10 +20306,10 @@
       </c>
       <c r="C48" s="43"/>
       <c r="D48" s="44" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E48" s="44" t="s">
         <v>1150</v>
-      </c>
-      <c r="E48" s="44" t="s">
-        <v>1152</v>
       </c>
       <c r="F48" s="43"/>
       <c r="G48" s="43"/>
@@ -20322,10 +20323,10 @@
       </c>
       <c r="C49" s="43"/>
       <c r="D49" s="44" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="F49" s="43"/>
       <c r="G49" s="43"/>
@@ -20339,10 +20340,10 @@
       </c>
       <c r="C50" s="43"/>
       <c r="D50" s="44" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E50" s="44" t="s">
         <v>1083</v>
-      </c>
-      <c r="E50" s="44" t="s">
-        <v>1085</v>
       </c>
       <c r="F50" s="43"/>
       <c r="G50" s="43"/>
@@ -20359,7 +20360,7 @@
         <v>1241</v>
       </c>
       <c r="E51" s="49" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="F51" s="43"/>
       <c r="G51" s="43"/>
@@ -20376,7 +20377,7 @@
         <v>1241</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="F52" s="43"/>
       <c r="G52" s="43"/>
@@ -20427,7 +20428,7 @@
         <v>1245</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="F55" s="43"/>
       <c r="G55" s="43"/>
@@ -20444,7 +20445,7 @@
         <v>1245</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="F56" s="43"/>
       <c r="G56" s="43"/>
@@ -20492,10 +20493,10 @@
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="F59" s="43"/>
       <c r="G59" s="43"/>
@@ -20509,10 +20510,10 @@
       </c>
       <c r="C60" s="43"/>
       <c r="D60" s="44" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E60" s="44" t="s">
         <v>1124</v>
-      </c>
-      <c r="E60" s="44" t="s">
-        <v>1126</v>
       </c>
       <c r="F60" s="43"/>
       <c r="G60" s="43"/>
@@ -20526,10 +20527,10 @@
       </c>
       <c r="C61" s="43"/>
       <c r="D61" s="44" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="F61" s="43"/>
       <c r="G61" s="43"/>
@@ -20543,10 +20544,10 @@
       </c>
       <c r="C62" s="43"/>
       <c r="D62" s="44" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E62" s="49" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="F62" s="43"/>
       <c r="G62" s="43"/>
@@ -20559,10 +20560,10 @@
         <v>366</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="E63" s="25" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20573,10 +20574,10 @@
         <v>243</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20587,10 +20588,10 @@
         <v>234</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20604,7 +20605,7 @@
         <v>1249</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20618,7 +20619,7 @@
         <v>1250</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20632,7 +20633,7 @@
         <v>1250</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20643,10 +20644,10 @@
         <v>234</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20657,10 +20658,10 @@
         <v>243</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/SEPIA/SEPIA_config.xlsx
+++ b/SEPIA/SEPIA_config.xlsx
@@ -396,7 +396,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2819" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2829" uniqueCount="1459">
   <si>
     <t xml:space="preserve">Sheet</t>
   </si>
@@ -1952,16 +1952,19 @@
     <t xml:space="preserve">rdmhydcl</t>
   </si>
   <si>
+    <t xml:space="preserve">am</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production losses of ammonia</t>
   </si>
   <si>
-    <t xml:space="preserve">prohydclam</t>
+    <t xml:space="preserve">prohydnh</t>
   </si>
   <si>
     <t xml:space="preserve">Production of ammonia from hydrogen</t>
   </si>
   <si>
-    <t xml:space="preserve">prohydclammt</t>
+    <t xml:space="preserve">proamclammt</t>
   </si>
   <si>
     <t xml:space="preserve">smr</t>
@@ -2915,15 +2918,15 @@
     <t xml:space="preserve">prespaccfaaa</t>
   </si>
   <si>
+    <t xml:space="preserve">rural ground heat pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prerusgr</t>
+  </si>
+  <si>
     <t xml:space="preserve">gr</t>
   </si>
   <si>
-    <t xml:space="preserve">rural ground heat pumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prespaccfta</t>
-  </si>
-  <si>
     <t xml:space="preserve">prespaccftaa</t>
   </si>
   <si>
@@ -3068,7 +3071,7 @@
     <t xml:space="preserve">ammonia for industry</t>
   </si>
   <si>
-    <t xml:space="preserve">prohydclamm</t>
+    <t xml:space="preserve">prohydem</t>
   </si>
   <si>
     <t xml:space="preserve">prescmscfneind</t>
@@ -3561,6 +3564,18 @@
   </si>
   <si>
     <t xml:space="preserve">prebmannfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rural air heat pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prerurair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rural air heat pump ambient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prerurairam</t>
   </si>
   <si>
     <t xml:space="preserve">Process emissions from industry</t>
@@ -6762,7 +6777,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="B1" s="1" t="n">
         <v>2025</v>
@@ -6785,7 +6800,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>10</v>
@@ -6806,12 +6821,12 @@
         <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0</v>
@@ -6832,12 +6847,12 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.6</v>
@@ -6858,12 +6873,12 @@
         <v>0.6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -6884,12 +6899,12 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1.28</v>
@@ -6910,12 +6925,12 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>47</v>
@@ -6936,12 +6951,12 @@
         <v>40</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>20</v>
@@ -6962,12 +6977,12 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -6988,12 +7003,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0</v>
@@ -7014,12 +7029,12 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1389</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0</v>
@@ -7040,12 +7055,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1392</v>
+        <v>1397</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -7066,12 +7081,12 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1393</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>0</v>
@@ -7092,12 +7107,12 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
@@ -7118,12 +7133,12 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>16</v>
@@ -7144,12 +7159,12 @@
         <v>16</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>1399</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>19</v>
@@ -7170,12 +7185,12 @@
         <v>19</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1401</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>31</v>
@@ -7196,12 +7211,12 @@
         <v>20</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -7222,12 +7237,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1405</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -7248,12 +7263,12 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1407</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -7274,12 +7289,12 @@
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>107</v>
@@ -7300,12 +7315,12 @@
         <v>107</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1412</v>
+        <v>1417</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1000</v>
@@ -7326,12 +7341,12 @@
         <v>1000</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1413</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>43</v>
@@ -7352,12 +7367,12 @@
         <v>43</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1415</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1416</v>
+        <v>1421</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -7378,12 +7393,12 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1417</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1418</v>
+        <v>1423</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>68</v>
@@ -7404,12 +7419,12 @@
         <v>68</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1413</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1419</v>
+        <v>1424</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -7430,12 +7445,12 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1420</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -7456,12 +7471,12 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1422</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1423</v>
+        <v>1428</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>0</v>
@@ -7482,12 +7497,12 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1424</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1425</v>
+        <v>1430</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>351</v>
@@ -7508,7 +7523,7 @@
         <v>341</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1413</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7560,7 +7575,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="B1" s="1" t="n">
         <v>2025</v>
@@ -7583,7 +7598,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>6.5</v>
@@ -7604,12 +7619,12 @@
         <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1426</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0</v>
@@ -7630,12 +7645,12 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1427</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0</v>
@@ -7656,12 +7671,12 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1428</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -7682,12 +7697,12 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1.36</v>
@@ -7708,12 +7723,12 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1430</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>38</v>
@@ -7734,12 +7749,12 @@
         <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1431</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>42</v>
@@ -7760,12 +7775,12 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1432</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -7786,12 +7801,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1433</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
@@ -7812,12 +7827,12 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1434</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0</v>
@@ -7838,12 +7853,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1435</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1392</v>
+        <v>1397</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -7864,12 +7879,12 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>9</v>
@@ -7890,12 +7905,12 @@
         <v>8</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1437</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
@@ -7916,12 +7931,12 @@
         <v>8</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>13</v>
@@ -7942,12 +7957,12 @@
         <v>13</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1439</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>0</v>
@@ -7968,12 +7983,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1440</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>60</v>
@@ -7994,12 +8009,12 @@
         <v>60</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1441</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -8020,12 +8035,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -8046,12 +8061,12 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -8072,12 +8087,12 @@
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>12</v>
@@ -8098,12 +8113,12 @@
         <v>12</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1445</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1412</v>
+        <v>1417</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1076</v>
@@ -8124,12 +8139,12 @@
         <v>1000</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1446</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>11</v>
@@ -8150,12 +8165,12 @@
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1447</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1416</v>
+        <v>1421</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -8176,12 +8191,12 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1448</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1418</v>
+        <v>1423</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>40</v>
@@ -8202,12 +8217,12 @@
         <v>40</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1449</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1419</v>
+        <v>1424</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -8228,12 +8243,12 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1450</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -8254,12 +8269,12 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1451</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1423</v>
+        <v>1428</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>2.4</v>
@@ -8280,12 +8295,12 @@
         <v>2.4</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1425</v>
+        <v>1430</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>616</v>
@@ -8306,7 +8321,7 @@
         <v>600</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1453</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -12380,12 +12395,14 @@
       <c r="B55" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="C55" s="43"/>
+      <c r="C55" s="43" t="s">
+        <v>518</v>
+      </c>
       <c r="D55" s="44" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F55" s="43"/>
       <c r="G55" s="43"/>
@@ -12399,10 +12416,10 @@
       </c>
       <c r="C56" s="43"/>
       <c r="D56" s="44" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E56" s="43" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F56" s="43"/>
       <c r="G56" s="43"/>
@@ -12417,16 +12434,16 @@
         <v>hyd_se</v>
       </c>
       <c r="C57" s="43" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E57" s="43" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F57" s="43" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G57" s="43"/>
     </row>
@@ -12440,16 +12457,16 @@
         <v>hyd_se</v>
       </c>
       <c r="C58" s="43" t="s">
+        <v>527</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>528</v>
+      </c>
+      <c r="E58" s="43" t="s">
+        <v>529</v>
+      </c>
+      <c r="F58" s="43" t="s">
         <v>526</v>
-      </c>
-      <c r="D58" s="43" t="s">
-        <v>527</v>
-      </c>
-      <c r="E58" s="43" t="s">
-        <v>528</v>
-      </c>
-      <c r="F58" s="43" t="s">
-        <v>525</v>
       </c>
       <c r="G58" s="43"/>
     </row>
@@ -12461,13 +12478,13 @@
         <v>163</v>
       </c>
       <c r="C59" s="43" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D59" s="43" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E59" s="43" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F59" s="43"/>
       <c r="G59" s="43"/>
@@ -12484,7 +12501,7 @@
         <v>369</v>
       </c>
       <c r="E60" s="43" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F60" s="43"/>
       <c r="G60" s="43"/>
@@ -12500,10 +12517,10 @@
         <v>411</v>
       </c>
       <c r="D61" s="45" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E61" s="43" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F61" s="43"/>
       <c r="G61" s="43"/>
@@ -12517,10 +12534,10 @@
       </c>
       <c r="C62" s="43"/>
       <c r="D62" s="45" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E62" s="45" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F62" s="43"/>
       <c r="G62" s="43"/>
@@ -12536,10 +12553,10 @@
         <v>411</v>
       </c>
       <c r="D63" s="45" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F63" s="43"/>
       <c r="G63" s="43"/>
@@ -12553,10 +12570,10 @@
       </c>
       <c r="C64" s="43"/>
       <c r="D64" s="45" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E64" s="45" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F64" s="43"/>
       <c r="G64" s="43"/>
@@ -12570,10 +12587,10 @@
       </c>
       <c r="C65" s="43"/>
       <c r="D65" s="45" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F65" s="43"/>
       <c r="G65" s="43"/>
@@ -12587,10 +12604,10 @@
       </c>
       <c r="C66" s="43"/>
       <c r="D66" s="45" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F66" s="43"/>
       <c r="G66" s="43"/>
@@ -12604,10 +12621,10 @@
       </c>
       <c r="C67" s="43"/>
       <c r="D67" s="45" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F67" s="43"/>
       <c r="G67" s="43"/>
@@ -12621,10 +12638,10 @@
       </c>
       <c r="C68" s="43"/>
       <c r="D68" s="45" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F68" s="43"/>
       <c r="G68" s="43"/>
@@ -12638,10 +12655,10 @@
       </c>
       <c r="C69" s="43"/>
       <c r="D69" s="45" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F69" s="43"/>
       <c r="G69" s="43"/>
@@ -12654,13 +12671,13 @@
         <v>282</v>
       </c>
       <c r="C70" s="43" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D70" s="45" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E70" s="45" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F70" s="43"/>
       <c r="G70" s="43"/>
@@ -12678,16 +12695,16 @@
         <v>472</v>
       </c>
       <c r="D71" s="43" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E71" s="43" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F71" s="43" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G71" s="43" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12703,16 +12720,16 @@
         <v>472</v>
       </c>
       <c r="D72" s="43" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E72" s="43" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F72" s="43" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G72" s="43" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12728,16 +12745,16 @@
         <v>472</v>
       </c>
       <c r="D73" s="43" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E73" s="43" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F73" s="43" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G73" s="43" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12751,10 +12768,10 @@
         <v>472</v>
       </c>
       <c r="D74" s="44" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E74" s="43" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F74" s="43"/>
       <c r="G74" s="43"/>
@@ -12772,16 +12789,16 @@
         <v>472</v>
       </c>
       <c r="D75" s="43" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E75" s="43" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F75" s="43" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G75" s="43" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12797,16 +12814,16 @@
         <v>472</v>
       </c>
       <c r="D76" s="43" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E76" s="43" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F76" s="43" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G76" s="43" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12818,10 +12835,10 @@
       </c>
       <c r="C77" s="43"/>
       <c r="D77" s="43" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E77" s="43" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -12839,16 +12856,16 @@
         <v>472</v>
       </c>
       <c r="D78" s="43" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E78" s="43" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F78" s="43" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G78" s="43" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12864,16 +12881,16 @@
         <v>472</v>
       </c>
       <c r="D79" s="43" t="s">
+        <v>583</v>
+      </c>
+      <c r="E79" s="43" t="s">
+        <v>584</v>
+      </c>
+      <c r="F79" s="43" t="s">
+        <v>581</v>
+      </c>
+      <c r="G79" s="43" t="s">
         <v>582</v>
-      </c>
-      <c r="E79" s="43" t="s">
-        <v>583</v>
-      </c>
-      <c r="F79" s="43" t="s">
-        <v>580</v>
-      </c>
-      <c r="G79" s="43" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12894,7 +12911,7 @@
         <v>Heat energy output from waste-to-energy CHP plants</v>
       </c>
       <c r="E80" s="43" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F80" s="43"/>
       <c r="G80" s="43"/>
@@ -12917,7 +12934,7 @@
         <v>Heat energy output from waste-to-energy CHP plants</v>
       </c>
       <c r="E81" s="43" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F81" s="43"/>
       <c r="G81" s="43"/>
@@ -12935,16 +12952,16 @@
         <v>472</v>
       </c>
       <c r="D82" s="43" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E82" s="43" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F82" s="43" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G82" s="43" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12960,16 +12977,16 @@
         <v>472</v>
       </c>
       <c r="D83" s="43" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E83" s="43" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F83" s="43" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G83" s="43" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12982,17 +12999,17 @@
         <v>vap_se</v>
       </c>
       <c r="C84" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D84" s="43" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E84" s="43" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F84" s="43"/>
       <c r="G84" s="43" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13005,19 +13022,19 @@
         <v>vap_se</v>
       </c>
       <c r="C85" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D85" s="43" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E85" s="43" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F85" s="43" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G85" s="43" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13038,7 +13055,7 @@
         <v>Heat energy output from household waste incineration</v>
       </c>
       <c r="E86" s="43" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F86" s="43"/>
       <c r="G86" s="43"/>
@@ -13061,7 +13078,7 @@
         <v>Heat energy output from household waste incineration</v>
       </c>
       <c r="E87" s="43" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F87" s="43"/>
       <c r="G87" s="43"/>
@@ -13076,17 +13093,17 @@
         <v>vap_se</v>
       </c>
       <c r="C88" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D88" s="43" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E88" s="43" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F88" s="43"/>
       <c r="G88" s="43" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13099,16 +13116,16 @@
         <v>vap_se</v>
       </c>
       <c r="C89" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D89" s="43" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E89" s="43" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F89" s="43" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G89" s="43" t="s">
         <v>175</v>
@@ -13125,16 +13142,16 @@
       </c>
       <c r="C90" s="43"/>
       <c r="D90" s="43" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E90" s="43" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F90" s="43" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G90" s="43" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13147,16 +13164,16 @@
       </c>
       <c r="C91" s="43"/>
       <c r="D91" s="43" t="s">
+        <v>615</v>
+      </c>
+      <c r="E91" s="43" t="s">
+        <v>616</v>
+      </c>
+      <c r="F91" s="43" t="s">
+        <v>613</v>
+      </c>
+      <c r="G91" s="43" t="s">
         <v>614</v>
-      </c>
-      <c r="E91" s="43" t="s">
-        <v>615</v>
-      </c>
-      <c r="F91" s="43" t="s">
-        <v>612</v>
-      </c>
-      <c r="G91" s="43" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13169,19 +13186,19 @@
         <v>vap_se</v>
       </c>
       <c r="C92" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D92" s="43" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E92" s="43" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F92" s="43" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G92" s="43" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13193,10 +13210,10 @@
       </c>
       <c r="C93" s="43"/>
       <c r="D93" s="43" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E93" s="43" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F93" s="43"/>
       <c r="G93" s="43"/>
@@ -13210,10 +13227,10 @@
       </c>
       <c r="C94" s="43"/>
       <c r="D94" s="43" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E94" s="43" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F94" s="43"/>
       <c r="G94" s="43"/>
@@ -13227,10 +13244,10 @@
       </c>
       <c r="C95" s="43"/>
       <c r="D95" s="43" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E95" s="43" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F95" s="43"/>
       <c r="G95" s="43"/>
@@ -13245,16 +13262,16 @@
         <v>vap_se</v>
       </c>
       <c r="C96" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D96" s="43" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E96" s="43" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F96" s="43" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G96" s="43" t="s">
         <v>172</v>
@@ -13270,66 +13287,65 @@
         <v>vap_se</v>
       </c>
       <c r="C97" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D97" s="43" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E97" s="43" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F97" s="43"/>
       <c r="G97" s="43" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="26" t="str">
-        <f aca="false">NODES!A53</f>
-        <v>pac_pe</v>
+      <c r="A98" s="26" t="s">
+        <v>194</v>
       </c>
       <c r="B98" s="26" t="str">
         <f aca="false">NODES!$A$30</f>
         <v>vap_se</v>
       </c>
       <c r="C98" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D98" s="43" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E98" s="43" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F98" s="43" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G98" s="43" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="26" t="s">
-        <v>194</v>
+        <v>258</v>
       </c>
       <c r="B99" s="26" t="str">
         <f aca="false">NODES!$A$30</f>
         <v>vap_se</v>
       </c>
       <c r="C99" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D99" s="43" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E99" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="F99" s="43" t="s">
+        <v>635</v>
+      </c>
+      <c r="G99" s="43" t="s">
         <v>636</v>
-      </c>
-      <c r="F99" s="43" t="s">
-        <v>634</v>
-      </c>
-      <c r="G99" s="43" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13341,10 +13357,10 @@
       </c>
       <c r="C100" s="43"/>
       <c r="D100" s="44" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E100" s="43" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F100" s="43"/>
       <c r="G100" s="43"/>
@@ -13358,10 +13374,10 @@
       </c>
       <c r="C101" s="43"/>
       <c r="D101" s="44" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E101" s="43" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F101" s="43"/>
       <c r="G101" s="43"/>
@@ -13375,10 +13391,10 @@
       </c>
       <c r="C102" s="43"/>
       <c r="D102" s="44" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E102" s="43" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F102" s="43"/>
       <c r="G102" s="43"/>
@@ -13393,16 +13409,16 @@
         <v>vap_se</v>
       </c>
       <c r="C103" s="43" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D103" s="43" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E103" s="43" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F103" s="43" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G103" s="43" t="s">
         <v>164</v>
@@ -13422,10 +13438,10 @@
         <v>thm</v>
       </c>
       <c r="D104" s="43" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E104" s="44" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F104" s="43"/>
       <c r="G104" s="43"/>
@@ -13444,10 +13460,10 @@
         <v>thm</v>
       </c>
       <c r="D105" s="43" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E105" s="43" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F105" s="43"/>
       <c r="G105" s="43"/>
@@ -13466,10 +13482,10 @@
         <v>thm</v>
       </c>
       <c r="D106" s="43" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E106" s="43" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F106" s="43"/>
       <c r="G106" s="43"/>
@@ -13488,10 +13504,10 @@
         <v>0</v>
       </c>
       <c r="D107" s="43" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E107" s="43" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F107" s="43"/>
       <c r="G107" s="43"/>
@@ -13507,10 +13523,10 @@
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="43" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E108" s="43" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F108" s="43"/>
       <c r="G108" s="43"/>
@@ -13529,10 +13545,10 @@
         <v>thm</v>
       </c>
       <c r="D109" s="43" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E109" s="43" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F109" s="43"/>
       <c r="G109" s="43"/>
@@ -13551,10 +13567,10 @@
         <v>thm</v>
       </c>
       <c r="D110" s="43" t="s">
+        <v>657</v>
+      </c>
+      <c r="E110" s="43" t="s">
         <v>656</v>
-      </c>
-      <c r="E110" s="43" t="s">
-        <v>655</v>
       </c>
       <c r="F110" s="43"/>
       <c r="G110" s="43"/>
@@ -13577,7 +13593,7 @@
         <v>Transformation losses (waste-fired powerplants)</v>
       </c>
       <c r="E111" s="43" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F111" s="43"/>
       <c r="G111" s="43"/>
@@ -13600,7 +13616,7 @@
         <v>Transformation losses (waste-fired powerplants)</v>
       </c>
       <c r="E112" s="43" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F112" s="43"/>
       <c r="G112" s="43"/>
@@ -13619,10 +13635,10 @@
         <v>thm</v>
       </c>
       <c r="D113" s="43" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E113" s="43" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F113" s="43"/>
       <c r="G113" s="43"/>
@@ -13641,10 +13657,10 @@
         <v>chp</v>
       </c>
       <c r="D114" s="43" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E114" s="43" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F114" s="43"/>
       <c r="G114" s="43"/>
@@ -13663,10 +13679,10 @@
         <v>chp</v>
       </c>
       <c r="D115" s="43" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E115" s="43" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F115" s="43"/>
       <c r="G115" s="43"/>
@@ -13682,10 +13698,10 @@
       </c>
       <c r="C116" s="26"/>
       <c r="D116" s="43" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E116" s="43" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F116" s="43"/>
       <c r="G116" s="43"/>
@@ -13701,10 +13717,10 @@
       </c>
       <c r="C117" s="26"/>
       <c r="D117" s="43" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E117" s="43" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F117" s="43"/>
       <c r="G117" s="43"/>
@@ -13720,10 +13736,10 @@
       </c>
       <c r="C118" s="26"/>
       <c r="D118" s="43" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E118" s="43" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F118" s="43"/>
       <c r="G118" s="43"/>
@@ -13742,10 +13758,10 @@
         <v>chp</v>
       </c>
       <c r="D119" s="43" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E119" s="43" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F119" s="43"/>
       <c r="G119" s="43"/>
@@ -13759,10 +13775,10 @@
       </c>
       <c r="C120" s="26"/>
       <c r="D120" s="43" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E120" s="43" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F120" s="43"/>
       <c r="G120" s="43"/>
@@ -13781,10 +13797,10 @@
         <v>chp</v>
       </c>
       <c r="D121" s="43" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E121" s="43" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F121" s="43"/>
       <c r="G121" s="43"/>
@@ -13803,10 +13819,10 @@
         <v>chp</v>
       </c>
       <c r="D122" s="43" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E122" s="43" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F122" s="43"/>
       <c r="G122" s="43"/>
@@ -13829,7 +13845,7 @@
         <v>Transformation losses (waste-to-energy CHP plants)</v>
       </c>
       <c r="E123" s="43" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F123" s="43"/>
       <c r="G123" s="43"/>
@@ -13852,7 +13868,7 @@
         <v>Transformation losses (waste-to-energy CHP plants)</v>
       </c>
       <c r="E124" s="43" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F124" s="43"/>
       <c r="G124" s="43"/>
@@ -13871,27 +13887,27 @@
         <v>chp</v>
       </c>
       <c r="D125" s="43" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E125" s="43" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F125" s="43"/>
       <c r="G125" s="43"/>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="26" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B126" s="26" t="s">
         <v>282</v>
       </c>
       <c r="C126" s="26"/>
       <c r="D126" s="43" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E126" s="43" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F126" s="43"/>
       <c r="G126" s="43"/>
@@ -13910,10 +13926,10 @@
         <v>chp</v>
       </c>
       <c r="D127" s="43" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E127" s="43" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F127" s="43"/>
       <c r="G127" s="43"/>
@@ -13932,10 +13948,10 @@
         <v>rr</v>
       </c>
       <c r="D128" s="43" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E128" s="43" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F128" s="43"/>
       <c r="G128" s="43"/>
@@ -13954,10 +13970,10 @@
         <v>smr</v>
       </c>
       <c r="D129" s="43" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E129" s="43" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F129" s="43"/>
       <c r="G129" s="43"/>
@@ -13976,10 +13992,10 @@
         <v>smrc</v>
       </c>
       <c r="D130" s="43" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E130" s="43" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F130" s="43"/>
       <c r="G130" s="43"/>
@@ -13998,10 +14014,10 @@
         <v>rch</v>
       </c>
       <c r="D131" s="43" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E131" s="43" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F131" s="43"/>
       <c r="G131" s="43"/>
@@ -14020,10 +14036,10 @@
         <v>rch</v>
       </c>
       <c r="D132" s="43" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E132" s="43" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F132" s="43"/>
       <c r="G132" s="43"/>
@@ -14046,7 +14062,7 @@
         <v>Transformation losses (household waste incineration)</v>
       </c>
       <c r="E133" s="43" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F133" s="43"/>
       <c r="G133" s="43"/>
@@ -14069,7 +14085,7 @@
         <v>Transformation losses (household waste incineration)</v>
       </c>
       <c r="E134" s="43" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F134" s="43"/>
       <c r="G134" s="43"/>
@@ -14088,10 +14104,10 @@
         <v>rch</v>
       </c>
       <c r="D135" s="43" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E135" s="43" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F135" s="43"/>
       <c r="G135" s="43"/>
@@ -14110,10 +14126,10 @@
         <v>rch</v>
       </c>
       <c r="D136" s="43" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E136" s="43" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F136" s="43"/>
       <c r="G136" s="43"/>
@@ -14128,10 +14144,10 @@
       </c>
       <c r="C137" s="26"/>
       <c r="D137" s="43" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E137" s="43" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F137" s="43"/>
       <c r="G137" s="43"/>
@@ -14149,10 +14165,10 @@
         <v>rch</v>
       </c>
       <c r="D138" s="43" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E138" s="43" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F138" s="43"/>
       <c r="G138" s="43"/>
@@ -14166,13 +14182,13 @@
         <v>per</v>
       </c>
       <c r="C139" s="26" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D139" s="43" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E139" s="43" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F139" s="43"/>
       <c r="G139" s="43"/>
@@ -14187,10 +14203,10 @@
       </c>
       <c r="C140" s="26"/>
       <c r="D140" s="43" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E140" s="43" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F140" s="43"/>
       <c r="G140" s="43"/>
@@ -14205,10 +14221,10 @@
       </c>
       <c r="C141" s="26"/>
       <c r="D141" s="43" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E141" s="43" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F141" s="43"/>
       <c r="G141" s="43"/>
@@ -14223,10 +14239,10 @@
       </c>
       <c r="C142" s="26"/>
       <c r="D142" s="43" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E142" s="43" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F142" s="43"/>
       <c r="G142" s="43"/>
@@ -14241,10 +14257,10 @@
       </c>
       <c r="C143" s="26"/>
       <c r="D143" s="43" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E143" s="43" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F143" s="43"/>
       <c r="G143" s="43"/>
@@ -14262,10 +14278,10 @@
         <v>rch</v>
       </c>
       <c r="D144" s="43" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E144" s="43" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F144" s="43"/>
       <c r="G144" s="43"/>
@@ -14279,13 +14295,13 @@
         <v>per</v>
       </c>
       <c r="C145" s="26" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D145" s="43" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E145" s="43" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F145" s="43"/>
       <c r="G145" s="43"/>
@@ -14299,13 +14315,13 @@
         <v>per</v>
       </c>
       <c r="C146" s="26" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D146" s="43" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E146" s="43" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F146" s="43"/>
       <c r="G146" s="43"/>
@@ -14319,13 +14335,13 @@
         <v>per</v>
       </c>
       <c r="C147" s="26" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D147" s="43" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E147" s="43" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F147" s="43"/>
       <c r="G147" s="43"/>
@@ -14344,10 +14360,10 @@
         <v>rch</v>
       </c>
       <c r="D148" s="43" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E148" s="43" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F148" s="43"/>
       <c r="G148" s="43"/>
@@ -14366,10 +14382,10 @@
         <v>rch</v>
       </c>
       <c r="D149" s="43" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E149" s="43" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F149" s="43"/>
       <c r="G149" s="43"/>
@@ -14377,7 +14393,7 @@
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="26" t="str">
         <f aca="false">A98</f>
-        <v>pac_pe</v>
+        <v>elc_se</v>
       </c>
       <c r="B150" s="26" t="str">
         <f aca="false">NODES!$A$62</f>
@@ -14388,10 +14404,10 @@
         <v>rch</v>
       </c>
       <c r="D150" s="43" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E150" s="43" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F150" s="43"/>
       <c r="G150" s="43"/>
@@ -14410,10 +14426,10 @@
         <v>rch</v>
       </c>
       <c r="D151" s="43" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E151" s="43" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F151" s="43"/>
       <c r="G151" s="43"/>
@@ -14429,10 +14445,10 @@
       </c>
       <c r="C152" s="43"/>
       <c r="D152" s="43" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E152" s="43" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F152" s="43"/>
       <c r="G152" s="43"/>
@@ -14448,10 +14464,10 @@
       </c>
       <c r="C153" s="43"/>
       <c r="D153" s="43" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E153" s="43" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F153" s="43"/>
       <c r="G153" s="43"/>
@@ -14467,10 +14483,10 @@
       </c>
       <c r="C154" s="43"/>
       <c r="D154" s="43" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E154" s="43" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F154" s="43"/>
       <c r="G154" s="43"/>
@@ -14486,10 +14502,10 @@
       </c>
       <c r="C155" s="43"/>
       <c r="D155" s="43" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E155" s="43" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F155" s="43"/>
       <c r="G155" s="43"/>
@@ -14505,10 +14521,10 @@
       </c>
       <c r="C156" s="43"/>
       <c r="D156" s="43" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E156" s="43" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F156" s="43"/>
       <c r="G156" s="43"/>
@@ -14524,10 +14540,10 @@
       </c>
       <c r="C157" s="43"/>
       <c r="D157" s="43" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E157" s="43" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F157" s="43"/>
       <c r="G157" s="43"/>
@@ -14543,10 +14559,10 @@
       </c>
       <c r="C158" s="43"/>
       <c r="D158" s="43" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E158" s="43" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F158" s="43"/>
       <c r="G158" s="43"/>
@@ -14562,10 +14578,10 @@
       </c>
       <c r="C159" s="43"/>
       <c r="D159" s="43" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E159" s="43" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F159" s="43"/>
       <c r="G159" s="43"/>
@@ -14581,10 +14597,10 @@
       </c>
       <c r="C160" s="43"/>
       <c r="D160" s="43" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E160" s="43" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F160" s="43"/>
       <c r="G160" s="43"/>
@@ -14600,10 +14616,10 @@
       </c>
       <c r="C161" s="43"/>
       <c r="D161" s="43" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E161" s="43" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F161" s="43"/>
       <c r="G161" s="43"/>
@@ -14619,10 +14635,10 @@
       </c>
       <c r="C162" s="43"/>
       <c r="D162" s="43" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E162" s="43" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F162" s="43"/>
       <c r="G162" s="43"/>
@@ -14638,10 +14654,10 @@
       </c>
       <c r="C163" s="43"/>
       <c r="D163" s="43" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E163" s="43" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F163" s="43"/>
       <c r="G163" s="43"/>
@@ -14657,10 +14673,10 @@
       </c>
       <c r="C164" s="43"/>
       <c r="D164" s="43" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E164" s="43" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F164" s="43"/>
       <c r="G164" s="43"/>
@@ -14676,10 +14692,10 @@
       </c>
       <c r="C165" s="43"/>
       <c r="D165" s="43" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E165" s="43" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F165" s="43"/>
       <c r="G165" s="43"/>
@@ -14695,10 +14711,10 @@
       </c>
       <c r="C166" s="43"/>
       <c r="D166" s="43" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E166" s="43" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F166" s="43"/>
       <c r="G166" s="43"/>
@@ -14713,10 +14729,10 @@
       </c>
       <c r="C167" s="26"/>
       <c r="D167" s="43" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E167" s="43" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F167" s="43"/>
       <c r="G167" s="43"/>
@@ -14735,10 +14751,10 @@
         <v>btl</v>
       </c>
       <c r="D168" s="43" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E168" s="43" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F168" s="43"/>
       <c r="G168" s="43"/>
@@ -14752,10 +14768,10 @@
       </c>
       <c r="C169" s="26"/>
       <c r="D169" s="43" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E169" s="43" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F169" s="43"/>
       <c r="G169" s="43"/>
@@ -14769,10 +14785,10 @@
       </c>
       <c r="C170" s="26"/>
       <c r="D170" s="43" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E170" s="43" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F170" s="43"/>
       <c r="G170" s="43"/>
@@ -14789,7 +14805,7 @@
       <c r="C171" s="43"/>
       <c r="D171" s="43"/>
       <c r="E171" s="43" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F171" s="43"/>
       <c r="G171" s="43"/>
@@ -14803,10 +14819,10 @@
       </c>
       <c r="C172" s="43"/>
       <c r="D172" s="43" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E172" s="43" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F172" s="43"/>
       <c r="G172" s="43"/>
@@ -14820,10 +14836,10 @@
       </c>
       <c r="C173" s="43"/>
       <c r="D173" s="43" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E173" s="43" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F173" s="43"/>
       <c r="G173" s="43"/>
@@ -14837,10 +14853,10 @@
       </c>
       <c r="C174" s="43"/>
       <c r="D174" s="43" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E174" s="43" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F174" s="43"/>
       <c r="G174" s="43"/>
@@ -14854,10 +14870,10 @@
       </c>
       <c r="C175" s="43"/>
       <c r="D175" s="43" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E175" s="43" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F175" s="43"/>
       <c r="G175" s="43"/>
@@ -14871,10 +14887,10 @@
       </c>
       <c r="C176" s="43"/>
       <c r="D176" s="44" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E176" s="43" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F176" s="43"/>
       <c r="G176" s="43"/>
@@ -14888,10 +14904,10 @@
       </c>
       <c r="C177" s="43"/>
       <c r="D177" s="44" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E177" s="43" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F177" s="43"/>
       <c r="G177" s="43"/>
@@ -14905,10 +14921,10 @@
       </c>
       <c r="C178" s="43"/>
       <c r="D178" s="44" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E178" s="43" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F178" s="43"/>
       <c r="G178" s="43"/>
@@ -14922,10 +14938,10 @@
       </c>
       <c r="C179" s="43"/>
       <c r="D179" s="44" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E179" s="43" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F179" s="43"/>
       <c r="G179" s="43"/>
@@ -14939,10 +14955,10 @@
       </c>
       <c r="C180" s="43"/>
       <c r="D180" s="44" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E180" s="43" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F180" s="43"/>
       <c r="G180" s="43"/>
@@ -14956,10 +14972,10 @@
       </c>
       <c r="C181" s="43"/>
       <c r="D181" s="44" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E181" s="43" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F181" s="43"/>
       <c r="G181" s="43"/>
@@ -14973,10 +14989,10 @@
       </c>
       <c r="C182" s="43"/>
       <c r="D182" s="44" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E182" s="43" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F182" s="43"/>
       <c r="G182" s="43"/>
@@ -14990,10 +15006,10 @@
       </c>
       <c r="C183" s="43"/>
       <c r="D183" s="44" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E183" s="43" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F183" s="43"/>
       <c r="G183" s="43"/>
@@ -15008,13 +15024,13 @@
         <v>res</v>
       </c>
       <c r="C184" s="43" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D184" s="43" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E184" s="43" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F184" s="43"/>
       <c r="G184" s="43"/>
@@ -15030,10 +15046,10 @@
         <v>115</v>
       </c>
       <c r="D185" s="44" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E185" s="44" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F185" s="43"/>
       <c r="G185" s="43"/>
@@ -15047,10 +15063,10 @@
       </c>
       <c r="C186" s="43"/>
       <c r="D186" s="43" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E186" s="43" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F186" s="43"/>
       <c r="G186" s="43"/>
@@ -15064,10 +15080,10 @@
       </c>
       <c r="C187" s="43"/>
       <c r="D187" s="43" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E187" s="43" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F187" s="43"/>
       <c r="G187" s="43"/>
@@ -15081,10 +15097,10 @@
       </c>
       <c r="C188" s="43"/>
       <c r="D188" s="43" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E188" s="43" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F188" s="43"/>
       <c r="G188" s="43"/>
@@ -15098,10 +15114,10 @@
       </c>
       <c r="C189" s="43"/>
       <c r="D189" s="43" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E189" s="43" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F189" s="43"/>
       <c r="G189" s="43"/>
@@ -15115,10 +15131,10 @@
       </c>
       <c r="C190" s="43"/>
       <c r="D190" s="43" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E190" s="43" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F190" s="43"/>
       <c r="G190" s="43"/>
@@ -15132,10 +15148,10 @@
       </c>
       <c r="C191" s="43"/>
       <c r="D191" s="43" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E191" s="43" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F191" s="43"/>
       <c r="G191" s="43"/>
@@ -15149,10 +15165,10 @@
       </c>
       <c r="C192" s="43"/>
       <c r="D192" s="43" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E192" s="43" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F192" s="43"/>
       <c r="G192" s="43"/>
@@ -15166,10 +15182,10 @@
       </c>
       <c r="C193" s="43"/>
       <c r="D193" s="43" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E193" s="43" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F193" s="43"/>
       <c r="G193" s="43"/>
@@ -15182,13 +15198,13 @@
         <v>110</v>
       </c>
       <c r="C194" s="43" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D194" s="43" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E194" s="43" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F194" s="43"/>
       <c r="G194" s="43"/>
@@ -15201,13 +15217,13 @@
         <v>110</v>
       </c>
       <c r="C195" s="43" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D195" s="43" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E195" s="43" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F195" s="43"/>
       <c r="G195" s="43"/>
@@ -15220,13 +15236,13 @@
         <v>110</v>
       </c>
       <c r="C196" s="43" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D196" s="43" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E196" s="43" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F196" s="43"/>
       <c r="G196" s="43"/>
@@ -15239,13 +15255,13 @@
         <v>110</v>
       </c>
       <c r="C197" s="43" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D197" s="43" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E197" s="43" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F197" s="43"/>
       <c r="G197" s="43"/>
@@ -15258,13 +15274,13 @@
         <v>110</v>
       </c>
       <c r="C198" s="43" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D198" s="43" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E198" s="43" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F198" s="43"/>
       <c r="G198" s="43"/>
@@ -15277,13 +15293,13 @@
         <v>110</v>
       </c>
       <c r="C199" s="43" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D199" s="43" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E199" s="43" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F199" s="43"/>
       <c r="G199" s="43"/>
@@ -15296,13 +15312,13 @@
         <v>110</v>
       </c>
       <c r="C200" s="43" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D200" s="43" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E200" s="43" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F200" s="43"/>
       <c r="G200" s="43"/>
@@ -15315,13 +15331,13 @@
         <v>110</v>
       </c>
       <c r="C201" s="43" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D201" s="43" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E201" s="43" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F201" s="43"/>
       <c r="G201" s="43"/>
@@ -15335,10 +15351,10 @@
       </c>
       <c r="C202" s="43"/>
       <c r="D202" s="43" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E202" s="43" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F202" s="43"/>
       <c r="G202" s="43"/>
@@ -15352,10 +15368,10 @@
       </c>
       <c r="C203" s="43"/>
       <c r="D203" s="43" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E203" s="43" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F203" s="43"/>
       <c r="G203" s="43"/>
@@ -15369,10 +15385,10 @@
       </c>
       <c r="C204" s="43"/>
       <c r="D204" s="43" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E204" s="43" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F204" s="43"/>
       <c r="G204" s="43"/>
@@ -15386,10 +15402,10 @@
       </c>
       <c r="C205" s="43"/>
       <c r="D205" s="43" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E205" s="43" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F205" s="43"/>
       <c r="G205" s="43"/>
@@ -15403,10 +15419,10 @@
       </c>
       <c r="C206" s="43"/>
       <c r="D206" s="43" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E206" s="43" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F206" s="43"/>
       <c r="G206" s="43"/>
@@ -15420,10 +15436,10 @@
       </c>
       <c r="C207" s="43"/>
       <c r="D207" s="43" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E207" s="43" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F207" s="43"/>
       <c r="G207" s="43"/>
@@ -15437,10 +15453,10 @@
       </c>
       <c r="C208" s="43"/>
       <c r="D208" s="44" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E208" s="43" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F208" s="43"/>
       <c r="G208" s="43"/>
@@ -15454,10 +15470,10 @@
       </c>
       <c r="C209" s="43"/>
       <c r="D209" s="44" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E209" s="43" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F209" s="43"/>
       <c r="G209" s="43"/>
@@ -15471,10 +15487,10 @@
       </c>
       <c r="C210" s="43"/>
       <c r="D210" s="44" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E210" s="43" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F210" s="43"/>
       <c r="G210" s="43"/>
@@ -15488,24 +15504,22 @@
       </c>
       <c r="C211" s="43"/>
       <c r="D211" s="44" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E211" s="43" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F211" s="43"/>
       <c r="G211" s="43"/>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="26" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="B212" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="C212" s="43" t="s">
-        <v>839</v>
-      </c>
+      <c r="C212" s="43"/>
       <c r="D212" s="44" t="s">
         <v>840</v>
       </c>
@@ -15517,51 +15531,53 @@
     </row>
     <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="26" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="B213" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="C213" s="43"/>
+      <c r="C213" s="44" t="s">
+        <v>842</v>
+      </c>
       <c r="D213" s="44" t="s">
         <v>840</v>
       </c>
       <c r="E213" s="43" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F213" s="43"/>
       <c r="G213" s="43"/>
     </row>
     <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="26" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="B214" s="26" t="s">
         <v>110</v>
       </c>
       <c r="C214" s="43"/>
       <c r="D214" s="44" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E214" s="43" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F214" s="43"/>
       <c r="G214" s="43"/>
     </row>
     <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="26" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="B215" s="26" t="s">
         <v>110</v>
       </c>
       <c r="C215" s="43"/>
       <c r="D215" s="44" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E215" s="43" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F215" s="43"/>
       <c r="G215" s="43"/>
@@ -15578,7 +15594,7 @@
       <c r="C216" s="43"/>
       <c r="D216" s="43"/>
       <c r="E216" s="43" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F216" s="43"/>
       <c r="G216" s="43"/>
@@ -15595,7 +15611,7 @@
       <c r="C217" s="43"/>
       <c r="D217" s="43"/>
       <c r="E217" s="43" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F217" s="43"/>
       <c r="G217" s="43"/>
@@ -15612,7 +15628,7 @@
       <c r="C218" s="43"/>
       <c r="D218" s="43"/>
       <c r="E218" s="43" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F218" s="43"/>
       <c r="G218" s="43"/>
@@ -15629,7 +15645,7 @@
       <c r="C219" s="43"/>
       <c r="D219" s="43"/>
       <c r="E219" s="43" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F219" s="43"/>
       <c r="G219" s="43"/>
@@ -15646,7 +15662,7 @@
       <c r="C220" s="43"/>
       <c r="D220" s="43"/>
       <c r="E220" s="43" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F220" s="43"/>
       <c r="G220" s="43"/>
@@ -15663,7 +15679,7 @@
       <c r="C221" s="43"/>
       <c r="D221" s="43"/>
       <c r="E221" s="43" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F221" s="43"/>
       <c r="G221" s="43"/>
@@ -15680,7 +15696,7 @@
       <c r="C222" s="43"/>
       <c r="D222" s="43"/>
       <c r="E222" s="43" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F222" s="43"/>
       <c r="G222" s="43"/>
@@ -15697,7 +15713,7 @@
       <c r="C223" s="43"/>
       <c r="D223" s="43"/>
       <c r="E223" s="43" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F223" s="43"/>
       <c r="G223" s="43"/>
@@ -15714,7 +15730,7 @@
       <c r="C224" s="43"/>
       <c r="D224" s="43"/>
       <c r="E224" s="43" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F224" s="43"/>
       <c r="G224" s="43"/>
@@ -15729,10 +15745,10 @@
       </c>
       <c r="C225" s="43"/>
       <c r="D225" s="43" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E225" s="43" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F225" s="43"/>
       <c r="G225" s="43"/>
@@ -15749,7 +15765,7 @@
       <c r="C226" s="43"/>
       <c r="D226" s="43"/>
       <c r="E226" s="43" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F226" s="43"/>
       <c r="G226" s="43"/>
@@ -15764,10 +15780,10 @@
       </c>
       <c r="C227" s="43"/>
       <c r="D227" s="43" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E227" s="43" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F227" s="43"/>
       <c r="G227" s="43"/>
@@ -15782,10 +15798,10 @@
       </c>
       <c r="C228" s="43"/>
       <c r="D228" s="43" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E228" s="43" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="F228" s="43"/>
       <c r="G228" s="43"/>
@@ -15800,10 +15816,10 @@
       </c>
       <c r="C229" s="43"/>
       <c r="D229" s="43" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E229" s="43" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F229" s="43"/>
       <c r="G229" s="43"/>
@@ -15818,10 +15834,10 @@
       </c>
       <c r="C230" s="43"/>
       <c r="D230" s="43" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E230" s="43" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F230" s="43"/>
       <c r="G230" s="43"/>
@@ -15836,10 +15852,10 @@
       </c>
       <c r="C231" s="43"/>
       <c r="D231" s="43" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E231" s="43" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F231" s="43"/>
       <c r="G231" s="43"/>
@@ -15853,10 +15869,10 @@
       </c>
       <c r="C232" s="43"/>
       <c r="D232" s="43" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E232" s="43" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F232" s="43"/>
       <c r="G232" s="43"/>
@@ -15873,7 +15889,7 @@
       <c r="C233" s="43"/>
       <c r="D233" s="43"/>
       <c r="E233" s="43" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F233" s="43"/>
       <c r="G233" s="43"/>
@@ -15888,10 +15904,10 @@
       </c>
       <c r="C234" s="43"/>
       <c r="D234" s="43" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E234" s="43" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F234" s="43"/>
       <c r="G234" s="43"/>
@@ -15905,10 +15921,10 @@
       </c>
       <c r="C235" s="43"/>
       <c r="D235" s="44" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E235" s="44" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F235" s="43"/>
       <c r="G235" s="43"/>
@@ -15924,10 +15940,10 @@
       </c>
       <c r="C236" s="43"/>
       <c r="D236" s="43" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E236" s="43" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F236" s="43"/>
       <c r="G236" s="43"/>
@@ -15942,10 +15958,10 @@
       </c>
       <c r="C237" s="43"/>
       <c r="D237" s="43" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E237" s="43" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F237" s="43"/>
       <c r="G237" s="43"/>
@@ -15959,10 +15975,10 @@
       </c>
       <c r="C238" s="43"/>
       <c r="D238" s="43" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E238" s="44" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F238" s="43"/>
       <c r="G238" s="43"/>
@@ -15978,10 +15994,10 @@
       </c>
       <c r="C239" s="43"/>
       <c r="D239" s="43" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E239" s="43" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F239" s="43"/>
       <c r="G239" s="43"/>
@@ -15998,7 +16014,7 @@
       <c r="C240" s="43"/>
       <c r="D240" s="43"/>
       <c r="E240" s="43" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F240" s="43"/>
       <c r="G240" s="43"/>
@@ -16013,10 +16029,10 @@
       </c>
       <c r="C241" s="43"/>
       <c r="D241" s="43" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E241" s="43" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F241" s="43"/>
       <c r="G241" s="43"/>
@@ -16033,7 +16049,7 @@
       <c r="C242" s="43"/>
       <c r="D242" s="43"/>
       <c r="E242" s="43" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F242" s="43"/>
       <c r="G242" s="43"/>
@@ -16048,10 +16064,10 @@
       </c>
       <c r="C243" s="43"/>
       <c r="D243" s="43" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E243" s="43" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F243" s="43"/>
       <c r="G243" s="43"/>
@@ -16065,10 +16081,10 @@
       </c>
       <c r="C244" s="43"/>
       <c r="D244" s="43" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E244" s="43" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F244" s="43"/>
       <c r="G244" s="43"/>
@@ -16085,7 +16101,7 @@
       <c r="C245" s="43"/>
       <c r="D245" s="43"/>
       <c r="E245" s="43" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F245" s="43"/>
       <c r="G245" s="43"/>
@@ -16102,7 +16118,7 @@
       <c r="C246" s="43"/>
       <c r="D246" s="43"/>
       <c r="E246" s="43" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F246" s="43"/>
       <c r="G246" s="43"/>
@@ -16118,10 +16134,10 @@
       </c>
       <c r="C247" s="43"/>
       <c r="D247" s="43" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E247" s="43" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F247" s="43"/>
       <c r="G247" s="43"/>
@@ -16136,10 +16152,10 @@
       </c>
       <c r="C248" s="43"/>
       <c r="D248" s="43" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E248" s="43" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F248" s="43"/>
       <c r="G248" s="43"/>
@@ -16156,7 +16172,7 @@
       <c r="C249" s="43"/>
       <c r="D249" s="43"/>
       <c r="E249" s="43" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F249" s="43"/>
       <c r="G249" s="43"/>
@@ -16171,10 +16187,10 @@
       </c>
       <c r="C250" s="43"/>
       <c r="D250" s="43" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E250" s="43" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F250" s="43"/>
       <c r="G250" s="43"/>
@@ -16191,7 +16207,7 @@
       <c r="C251" s="43"/>
       <c r="D251" s="43"/>
       <c r="E251" s="43" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F251" s="43"/>
       <c r="G251" s="43"/>
@@ -16208,7 +16224,7 @@
       <c r="C252" s="43"/>
       <c r="D252" s="43"/>
       <c r="E252" s="43" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="F252" s="43"/>
       <c r="G252" s="43"/>
@@ -16225,7 +16241,7 @@
       <c r="C253" s="43"/>
       <c r="D253" s="43"/>
       <c r="E253" s="43" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F253" s="43"/>
       <c r="G253" s="43"/>
@@ -16242,7 +16258,7 @@
       <c r="C254" s="43"/>
       <c r="D254" s="43"/>
       <c r="E254" s="43" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F254" s="43"/>
       <c r="G254" s="43"/>
@@ -16259,7 +16275,7 @@
       <c r="C255" s="43"/>
       <c r="D255" s="43"/>
       <c r="E255" s="43" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F255" s="43"/>
       <c r="G255" s="43"/>
@@ -16276,7 +16292,7 @@
       <c r="C256" s="43"/>
       <c r="D256" s="43"/>
       <c r="E256" s="43" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F256" s="43"/>
       <c r="G256" s="43"/>
@@ -16293,7 +16309,7 @@
       <c r="C257" s="43"/>
       <c r="D257" s="43"/>
       <c r="E257" s="43" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F257" s="43"/>
       <c r="G257" s="43"/>
@@ -16308,10 +16324,10 @@
       </c>
       <c r="C258" s="43"/>
       <c r="D258" s="43" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E258" s="43" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F258" s="43"/>
       <c r="G258" s="43"/>
@@ -16327,10 +16343,10 @@
       </c>
       <c r="C259" s="43"/>
       <c r="D259" s="43" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E259" s="43" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F259" s="43"/>
       <c r="G259" s="43"/>
@@ -16344,10 +16360,10 @@
       </c>
       <c r="C260" s="43"/>
       <c r="D260" s="43" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E260" s="43" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F260" s="43"/>
       <c r="G260" s="43"/>
@@ -16361,10 +16377,10 @@
       </c>
       <c r="C261" s="43"/>
       <c r="D261" s="43" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E261" s="43" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F261" s="43"/>
       <c r="G261" s="43"/>
@@ -16381,7 +16397,7 @@
       <c r="C262" s="43"/>
       <c r="D262" s="43"/>
       <c r="E262" s="43" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F262" s="43"/>
       <c r="G262" s="43"/>
@@ -16395,10 +16411,10 @@
       </c>
       <c r="C263" s="43"/>
       <c r="D263" s="43" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E263" s="43" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F263" s="43"/>
       <c r="G263" s="43"/>
@@ -16412,10 +16428,10 @@
       </c>
       <c r="C264" s="43"/>
       <c r="D264" s="43" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E264" s="43" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F264" s="43"/>
       <c r="G264" s="43"/>
@@ -16429,10 +16445,10 @@
       </c>
       <c r="C265" s="43"/>
       <c r="D265" s="43" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E265" s="43" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F265" s="43"/>
       <c r="G265" s="43"/>
@@ -16446,10 +16462,10 @@
       </c>
       <c r="C266" s="43"/>
       <c r="D266" s="44" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E266" s="44" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F266" s="43"/>
       <c r="G266" s="43"/>
@@ -16463,10 +16479,10 @@
       </c>
       <c r="C267" s="43"/>
       <c r="D267" s="44" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E267" s="44" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F267" s="43"/>
       <c r="G267" s="43"/>
@@ -16480,10 +16496,10 @@
       </c>
       <c r="C268" s="43"/>
       <c r="D268" s="44" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E268" s="44" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F268" s="43"/>
       <c r="G268" s="43"/>
@@ -16497,10 +16513,10 @@
       </c>
       <c r="C269" s="43"/>
       <c r="D269" s="44" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E269" s="44" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F269" s="43"/>
       <c r="G269" s="43"/>
@@ -16514,10 +16530,10 @@
       </c>
       <c r="C270" s="43"/>
       <c r="D270" s="44" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E270" s="44" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F270" s="43"/>
       <c r="G270" s="43"/>
@@ -16531,10 +16547,10 @@
       </c>
       <c r="C271" s="43"/>
       <c r="D271" s="44" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E271" s="44" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F271" s="43"/>
       <c r="G271" s="43"/>
@@ -16548,10 +16564,10 @@
       </c>
       <c r="C272" s="43"/>
       <c r="D272" s="44" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E272" s="44" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F272" s="43"/>
       <c r="G272" s="43"/>
@@ -16565,10 +16581,10 @@
       </c>
       <c r="C273" s="43"/>
       <c r="D273" s="44" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="E273" s="44" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F273" s="43"/>
       <c r="G273" s="43"/>
@@ -16583,7 +16599,7 @@
       <c r="C274" s="43"/>
       <c r="D274" s="44"/>
       <c r="E274" s="44" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F274" s="43"/>
       <c r="G274" s="43"/>
@@ -16598,7 +16614,7 @@
       <c r="C275" s="43"/>
       <c r="D275" s="44"/>
       <c r="E275" s="44" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F275" s="43"/>
       <c r="G275" s="43"/>
@@ -16612,10 +16628,10 @@
       </c>
       <c r="C276" s="43"/>
       <c r="D276" s="44" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="E276" s="44" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F276" s="43"/>
       <c r="G276" s="43"/>
@@ -16629,10 +16645,10 @@
       </c>
       <c r="C277" s="43"/>
       <c r="D277" s="44" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E277" s="44" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F277" s="43"/>
       <c r="G277" s="43"/>
@@ -16646,10 +16662,10 @@
       </c>
       <c r="C278" s="43"/>
       <c r="D278" s="44" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E278" s="44" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F278" s="43"/>
       <c r="G278" s="43"/>
@@ -16663,10 +16679,10 @@
       </c>
       <c r="C279" s="43"/>
       <c r="D279" s="44" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E279" s="44" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F279" s="43"/>
       <c r="G279" s="43"/>
@@ -16681,7 +16697,7 @@
       <c r="C280" s="43"/>
       <c r="D280" s="44"/>
       <c r="E280" s="44" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F280" s="43"/>
       <c r="G280" s="43"/>
@@ -16696,7 +16712,7 @@
       <c r="C281" s="43"/>
       <c r="D281" s="44"/>
       <c r="E281" s="44" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F281" s="43"/>
       <c r="G281" s="43"/>
@@ -16711,7 +16727,7 @@
       <c r="C282" s="43"/>
       <c r="D282" s="44"/>
       <c r="E282" s="44" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F282" s="43"/>
       <c r="G282" s="43"/>
@@ -16726,7 +16742,7 @@
       <c r="C283" s="43"/>
       <c r="D283" s="44"/>
       <c r="E283" s="44" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F283" s="43"/>
       <c r="G283" s="43"/>
@@ -16741,7 +16757,7 @@
       <c r="C284" s="43"/>
       <c r="D284" s="44"/>
       <c r="E284" s="44" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F284" s="43"/>
       <c r="G284" s="43"/>
@@ -16756,7 +16772,7 @@
       <c r="C285" s="43"/>
       <c r="D285" s="44"/>
       <c r="E285" s="44" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F285" s="43"/>
       <c r="G285" s="43"/>
@@ -16771,7 +16787,7 @@
       <c r="C286" s="43"/>
       <c r="D286" s="44"/>
       <c r="E286" s="44" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F286" s="43"/>
       <c r="G286" s="43"/>
@@ -16786,7 +16802,7 @@
       <c r="C287" s="43"/>
       <c r="D287" s="44"/>
       <c r="E287" s="44" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F287" s="43"/>
       <c r="G287" s="43"/>
@@ -16801,7 +16817,7 @@
       <c r="C288" s="43"/>
       <c r="D288" s="44"/>
       <c r="E288" s="44" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F288" s="43"/>
       <c r="G288" s="43"/>
@@ -16816,7 +16832,7 @@
       <c r="C289" s="43"/>
       <c r="D289" s="44"/>
       <c r="E289" s="44" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F289" s="43"/>
       <c r="G289" s="43"/>
@@ -16831,7 +16847,7 @@
       <c r="C290" s="43"/>
       <c r="D290" s="44"/>
       <c r="E290" s="44" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F290" s="43"/>
       <c r="G290" s="43"/>
@@ -16846,7 +16862,7 @@
       <c r="C291" s="43"/>
       <c r="D291" s="44"/>
       <c r="E291" s="44" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F291" s="43"/>
       <c r="G291" s="43"/>
@@ -16861,7 +16877,7 @@
       <c r="C292" s="43"/>
       <c r="D292" s="44"/>
       <c r="E292" s="44" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F292" s="43"/>
       <c r="G292" s="43"/>
@@ -16876,7 +16892,7 @@
       <c r="C293" s="43"/>
       <c r="D293" s="44"/>
       <c r="E293" s="44" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F293" s="43"/>
       <c r="G293" s="43"/>
@@ -16891,7 +16907,7 @@
       <c r="C294" s="43"/>
       <c r="D294" s="44"/>
       <c r="E294" s="44" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F294" s="43"/>
       <c r="G294" s="43"/>
@@ -16906,7 +16922,7 @@
       <c r="C295" s="43"/>
       <c r="D295" s="44"/>
       <c r="E295" s="44" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F295" s="43"/>
       <c r="G295" s="43"/>
@@ -16920,10 +16936,10 @@
       </c>
       <c r="C296" s="43"/>
       <c r="D296" s="44" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E296" s="44" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F296" s="43"/>
       <c r="G296" s="43"/>
@@ -16937,10 +16953,10 @@
       </c>
       <c r="C297" s="43"/>
       <c r="D297" s="44" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E297" s="44" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F297" s="43"/>
       <c r="G297" s="43"/>
@@ -16954,10 +16970,10 @@
       </c>
       <c r="C298" s="43"/>
       <c r="D298" s="44" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E298" s="44" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F298" s="43"/>
       <c r="G298" s="43"/>
@@ -16972,7 +16988,7 @@
       <c r="C299" s="43"/>
       <c r="D299" s="44"/>
       <c r="E299" s="44" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F299" s="43"/>
       <c r="G299" s="43"/>
@@ -16986,10 +17002,10 @@
       </c>
       <c r="C300" s="43"/>
       <c r="D300" s="44" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="E300" s="44" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F300" s="43"/>
       <c r="G300" s="43"/>
@@ -17004,7 +17020,7 @@
       <c r="C301" s="43"/>
       <c r="D301" s="44"/>
       <c r="E301" s="44" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F301" s="43"/>
       <c r="G301" s="43"/>
@@ -17018,10 +17034,10 @@
       </c>
       <c r="C302" s="43"/>
       <c r="D302" s="44" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E302" s="44" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F302" s="43"/>
       <c r="G302" s="43"/>
@@ -17035,10 +17051,10 @@
       </c>
       <c r="C303" s="43"/>
       <c r="D303" s="44" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E303" s="44" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F303" s="43"/>
       <c r="G303" s="43"/>
@@ -17054,10 +17070,10 @@
         <v>411</v>
       </c>
       <c r="D304" s="44" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E304" s="44" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F304" s="43"/>
       <c r="G304" s="43"/>
@@ -17073,10 +17089,10 @@
         <v>411</v>
       </c>
       <c r="D305" s="44" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E305" s="44" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F305" s="43"/>
       <c r="G305" s="43"/>
@@ -17090,10 +17106,10 @@
       </c>
       <c r="C306" s="43"/>
       <c r="D306" s="44" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E306" s="44" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F306" s="43"/>
       <c r="G306" s="43"/>
@@ -17107,10 +17123,10 @@
       </c>
       <c r="C307" s="43"/>
       <c r="D307" s="44" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="E307" s="44" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F307" s="43"/>
       <c r="G307" s="43"/>
@@ -17124,10 +17140,10 @@
       </c>
       <c r="C308" s="43"/>
       <c r="D308" s="44" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E308" s="44" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F308" s="43"/>
       <c r="G308" s="43"/>
@@ -17142,7 +17158,7 @@
       <c r="C309" s="43"/>
       <c r="D309" s="44"/>
       <c r="E309" s="44" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F309" s="43"/>
       <c r="G309" s="43"/>
@@ -17156,10 +17172,10 @@
       </c>
       <c r="C310" s="43"/>
       <c r="D310" s="44" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E310" s="44" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F310" s="43"/>
       <c r="G310" s="43"/>
@@ -17173,10 +17189,10 @@
       </c>
       <c r="C311" s="43"/>
       <c r="D311" s="44" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E311" s="44" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F311" s="43"/>
       <c r="G311" s="43"/>
@@ -17190,10 +17206,10 @@
       </c>
       <c r="C312" s="43"/>
       <c r="D312" s="44" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E312" s="44" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F312" s="43"/>
       <c r="G312" s="43"/>
@@ -17207,10 +17223,10 @@
       </c>
       <c r="C313" s="43"/>
       <c r="D313" s="44" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E313" s="44" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F313" s="43"/>
       <c r="G313" s="43"/>
@@ -17224,10 +17240,10 @@
       </c>
       <c r="C314" s="43"/>
       <c r="D314" s="44" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E314" s="44" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F314" s="43"/>
       <c r="G314" s="43"/>
@@ -17241,10 +17257,10 @@
       </c>
       <c r="C315" s="43"/>
       <c r="D315" s="44" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E315" s="44" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F315" s="43"/>
       <c r="G315" s="43"/>
@@ -17258,10 +17274,10 @@
       </c>
       <c r="C316" s="43"/>
       <c r="D316" s="44" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E316" s="44" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F316" s="43"/>
       <c r="G316" s="43"/>
@@ -17274,10 +17290,10 @@
         <v>129</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17288,13 +17304,13 @@
         <v>156</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17305,10 +17321,10 @@
         <v>208</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17319,10 +17335,10 @@
         <v>201</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17333,10 +17349,10 @@
         <v>201</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17347,10 +17363,10 @@
         <v>201</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17361,13 +17377,13 @@
         <v>282</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17378,10 +17394,10 @@
         <v>282</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17392,10 +17408,10 @@
         <v>282</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17406,10 +17422,10 @@
         <v>201</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17420,10 +17436,10 @@
         <v>282</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17434,10 +17450,10 @@
         <v>282</v>
       </c>
       <c r="D328" s="25" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17448,10 +17464,10 @@
         <v>196</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17462,13 +17478,13 @@
         <v>156</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17479,10 +17495,10 @@
         <v>282</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17493,10 +17509,10 @@
         <v>196</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17507,10 +17523,10 @@
         <v>196</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17521,10 +17537,10 @@
         <v>196</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17535,10 +17551,10 @@
         <v>196</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17549,10 +17565,10 @@
         <v>196</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17563,10 +17579,10 @@
         <v>196</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17577,10 +17593,10 @@
         <v>282</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17591,10 +17607,10 @@
         <v>201</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17605,10 +17621,10 @@
         <v>186</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17619,10 +17635,10 @@
         <v>282</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17633,10 +17649,38 @@
         <v>189</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A343" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A344" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>1059</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -17705,10 +17749,10 @@
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="43" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="F2" s="43"/>
       <c r="G2" s="43"/>
@@ -17722,10 +17766,10 @@
       </c>
       <c r="C3" s="43"/>
       <c r="D3" s="44" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="F3" s="43"/>
       <c r="G3" s="43"/>
@@ -17739,10 +17783,10 @@
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="44" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
@@ -17756,10 +17800,10 @@
       </c>
       <c r="C5" s="43"/>
       <c r="D5" s="44" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="F5" s="43"/>
       <c r="G5" s="43"/>
@@ -17773,10 +17817,10 @@
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="44" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="43"/>
@@ -17790,10 +17834,10 @@
       </c>
       <c r="C7" s="43"/>
       <c r="D7" s="44" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="F7" s="43"/>
       <c r="G7" s="43"/>
@@ -17807,10 +17851,10 @@
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="44" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="F8" s="43"/>
       <c r="G8" s="43"/>
@@ -17824,10 +17868,10 @@
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="44" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
@@ -17841,10 +17885,10 @@
       </c>
       <c r="C10" s="43"/>
       <c r="D10" s="44" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="F10" s="43"/>
       <c r="G10" s="43"/>
@@ -17858,10 +17902,10 @@
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="44" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="F11" s="43"/>
       <c r="G11" s="43"/>
@@ -17875,10 +17919,10 @@
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="44" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
@@ -17892,10 +17936,10 @@
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="44" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="F13" s="43"/>
       <c r="G13" s="43"/>
@@ -17909,10 +17953,10 @@
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="44" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="F14" s="43"/>
       <c r="G14" s="43"/>
@@ -17925,13 +17969,13 @@
         <v>338</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
@@ -17944,13 +17988,13 @@
         <v>338</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="F16" s="43"/>
       <c r="G16" s="43"/>
@@ -17964,10 +18008,10 @@
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="44" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="F17" s="43"/>
       <c r="G17" s="43"/>
@@ -17981,10 +18025,10 @@
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="44" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="F18" s="43"/>
       <c r="G18" s="43"/>
@@ -17998,10 +18042,10 @@
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="44" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="F19" s="43"/>
       <c r="G19" s="43"/>
@@ -18015,10 +18059,10 @@
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="F20" s="43"/>
       <c r="G20" s="43"/>
@@ -18032,10 +18076,10 @@
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="44" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43"/>
@@ -18049,10 +18093,10 @@
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="44" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="F22" s="43"/>
       <c r="G22" s="43"/>
@@ -18066,10 +18110,10 @@
       </c>
       <c r="C23" s="43"/>
       <c r="D23" s="44" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="F23" s="43"/>
       <c r="G23" s="43"/>
@@ -18083,10 +18127,10 @@
       </c>
       <c r="C24" s="43"/>
       <c r="D24" s="44" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="F24" s="43"/>
       <c r="G24" s="43"/>
@@ -18099,13 +18143,13 @@
         <v>389</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="F25" s="43"/>
       <c r="G25" s="43"/>
@@ -18121,10 +18165,10 @@
         <v>126</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="F26" s="43"/>
       <c r="G26" s="43"/>
@@ -18140,10 +18184,10 @@
         <v>133</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
@@ -18159,10 +18203,10 @@
         <v>119</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="F28" s="43"/>
       <c r="G28" s="43"/>
@@ -18175,13 +18219,13 @@
         <v>338</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="F29" s="43"/>
       <c r="G29" s="43"/>
@@ -18194,13 +18238,13 @@
         <v>338</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="F30" s="43"/>
       <c r="G30" s="43"/>
@@ -18214,10 +18258,10 @@
       </c>
       <c r="C31" s="43"/>
       <c r="D31" s="44" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="F31" s="43"/>
       <c r="G31" s="43"/>
@@ -18234,7 +18278,7 @@
         <v>357</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="F32" s="43"/>
       <c r="G32" s="43"/>
@@ -18248,10 +18292,10 @@
       </c>
       <c r="C33" s="43"/>
       <c r="D33" s="44" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="F33" s="43"/>
       <c r="G33" s="43"/>
@@ -18265,10 +18309,10 @@
       </c>
       <c r="C34" s="43"/>
       <c r="D34" s="44" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
@@ -18281,13 +18325,13 @@
         <v>362</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="F35" s="43"/>
       <c r="G35" s="43"/>
@@ -18301,10 +18345,10 @@
       </c>
       <c r="C36" s="43"/>
       <c r="D36" s="44" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="F36" s="43"/>
       <c r="G36" s="43"/>
@@ -18320,10 +18364,10 @@
         <v>129</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="F37" s="43"/>
       <c r="G37" s="43"/>
@@ -18337,10 +18381,10 @@
       </c>
       <c r="C38" s="43"/>
       <c r="D38" s="44" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="F38" s="43"/>
       <c r="G38" s="43"/>
@@ -18354,10 +18398,10 @@
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
@@ -18371,10 +18415,10 @@
       </c>
       <c r="C40" s="43"/>
       <c r="D40" s="44" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="F40" s="43"/>
       <c r="G40" s="43"/>
@@ -18388,10 +18432,10 @@
       </c>
       <c r="C41" s="43"/>
       <c r="D41" s="44" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="F41" s="43"/>
       <c r="G41" s="43"/>
@@ -18405,10 +18449,10 @@
       </c>
       <c r="C42" s="43"/>
       <c r="D42" s="44" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="F42" s="43"/>
       <c r="G42" s="43"/>
@@ -18422,10 +18466,10 @@
       </c>
       <c r="C43" s="43"/>
       <c r="D43" s="44" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="F43" s="43"/>
       <c r="G43" s="43"/>
@@ -18439,10 +18483,10 @@
       </c>
       <c r="C44" s="43"/>
       <c r="D44" s="44" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="F44" s="43"/>
       <c r="G44" s="43"/>
@@ -18456,10 +18500,10 @@
       </c>
       <c r="C45" s="43"/>
       <c r="D45" s="44" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -18475,10 +18519,10 @@
         <v>411</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="F46" s="43"/>
       <c r="G46" s="43"/>
@@ -18492,10 +18536,10 @@
       </c>
       <c r="C47" s="43"/>
       <c r="D47" s="44" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="F47" s="43"/>
       <c r="G47" s="43"/>
@@ -18509,10 +18553,10 @@
       </c>
       <c r="C48" s="43"/>
       <c r="D48" s="44" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="F48" s="43"/>
       <c r="G48" s="43"/>
@@ -18528,10 +18572,10 @@
         <v>411</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="F49" s="43"/>
       <c r="G49" s="43"/>
@@ -18547,10 +18591,10 @@
         <v>411</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="E50" s="50" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="F50" s="43"/>
       <c r="G50" s="43"/>
@@ -18564,10 +18608,10 @@
       </c>
       <c r="C51" s="43"/>
       <c r="D51" s="44" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="F51" s="43"/>
       <c r="G51" s="43"/>
@@ -18581,10 +18625,10 @@
       </c>
       <c r="C52" s="43"/>
       <c r="D52" s="44" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="E52" s="50" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="F52" s="43"/>
       <c r="G52" s="43"/>
@@ -18598,10 +18642,10 @@
       </c>
       <c r="C53" s="43"/>
       <c r="D53" s="44" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E53" s="50" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="F53" s="43"/>
       <c r="G53" s="43"/>
@@ -18615,10 +18659,10 @@
       </c>
       <c r="C54" s="43"/>
       <c r="D54" s="44" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="F54" s="43"/>
       <c r="G54" s="43"/>
@@ -18632,10 +18676,10 @@
       </c>
       <c r="C55" s="43"/>
       <c r="D55" s="44" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="F55" s="43"/>
       <c r="G55" s="43"/>
@@ -18652,7 +18696,7 @@
         <v>373</v>
       </c>
       <c r="E56" s="50" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="F56" s="43"/>
       <c r="G56" s="43"/>
@@ -18669,7 +18713,7 @@
         <v>375</v>
       </c>
       <c r="E57" s="50" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="F57" s="43"/>
       <c r="G57" s="43"/>
@@ -18683,10 +18727,10 @@
       </c>
       <c r="C58" s="43"/>
       <c r="D58" s="44" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="F58" s="43"/>
       <c r="G58" s="43"/>
@@ -18700,10 +18744,10 @@
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="F59" s="43"/>
       <c r="G59" s="43"/>
@@ -18719,10 +18763,10 @@
         <v>411</v>
       </c>
       <c r="D60" s="44" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="F60" s="43"/>
       <c r="G60" s="43"/>
@@ -18736,10 +18780,10 @@
       </c>
       <c r="C61" s="43"/>
       <c r="D61" s="44" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="F61" s="43"/>
       <c r="G61" s="43"/>
@@ -18753,10 +18797,10 @@
       </c>
       <c r="C62" s="43"/>
       <c r="D62" s="44" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="F62" s="43"/>
       <c r="G62" s="43"/>
@@ -18770,10 +18814,10 @@
       </c>
       <c r="C63" s="43"/>
       <c r="D63" s="44" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="F63" s="43"/>
       <c r="G63" s="43"/>
@@ -18787,10 +18831,10 @@
       </c>
       <c r="C64" s="43"/>
       <c r="D64" s="44" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="F64" s="43"/>
       <c r="G64" s="43"/>
@@ -18804,10 +18848,10 @@
       </c>
       <c r="C65" s="43"/>
       <c r="D65" s="44" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="E65" s="44" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="F65" s="43"/>
       <c r="G65" s="43"/>
@@ -18821,10 +18865,10 @@
       </c>
       <c r="C66" s="43"/>
       <c r="D66" s="44" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="F66" s="43"/>
       <c r="G66" s="43"/>
@@ -18838,10 +18882,10 @@
       </c>
       <c r="C67" s="43"/>
       <c r="D67" s="44" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="E67" s="44" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="F67" s="43"/>
       <c r="G67" s="43"/>
@@ -18855,10 +18899,10 @@
       </c>
       <c r="C68" s="43"/>
       <c r="D68" s="44" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="F68" s="43"/>
       <c r="G68" s="43"/>
@@ -18875,7 +18919,7 @@
         <v>383</v>
       </c>
       <c r="E69" s="49" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="F69" s="43"/>
       <c r="G69" s="43"/>
@@ -18889,10 +18933,10 @@
       </c>
       <c r="C70" s="43"/>
       <c r="D70" s="49" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="E70" s="49" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="F70" s="43"/>
       <c r="G70" s="43"/>
@@ -18906,10 +18950,10 @@
       </c>
       <c r="C71" s="43"/>
       <c r="D71" s="49" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="E71" s="49" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="F71" s="43"/>
       <c r="G71" s="43"/>
@@ -18923,10 +18967,10 @@
       </c>
       <c r="C72" s="43"/>
       <c r="D72" s="49" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="E72" s="49" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="F72" s="43"/>
       <c r="G72" s="43"/>
@@ -18940,10 +18984,10 @@
       </c>
       <c r="C73" s="43"/>
       <c r="D73" s="49" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="E73" s="49" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="F73" s="43"/>
       <c r="G73" s="43"/>
@@ -18957,10 +19001,10 @@
       </c>
       <c r="C74" s="43"/>
       <c r="D74" s="49" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="E74" s="49" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="F74" s="43"/>
       <c r="G74" s="43"/>
@@ -18974,10 +19018,10 @@
       </c>
       <c r="C75" s="43"/>
       <c r="D75" s="49" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="E75" s="49" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="F75" s="43"/>
       <c r="G75" s="43"/>
@@ -18991,10 +19035,10 @@
       </c>
       <c r="C76" s="43"/>
       <c r="D76" s="49" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="E76" s="49" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="F76" s="43"/>
       <c r="G76" s="43"/>
@@ -19011,7 +19055,7 @@
         <v>446</v>
       </c>
       <c r="E77" s="49" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -19025,10 +19069,10 @@
       </c>
       <c r="C78" s="43"/>
       <c r="D78" s="49" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="E78" s="49" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="F78" s="43"/>
       <c r="G78" s="43"/>
@@ -19042,10 +19086,10 @@
       </c>
       <c r="C79" s="43"/>
       <c r="D79" s="49" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="E79" s="49" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="F79" s="43"/>
       <c r="G79" s="43"/>
@@ -19059,10 +19103,10 @@
       </c>
       <c r="C80" s="43"/>
       <c r="D80" s="49" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="E80" s="49" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="F80" s="43"/>
       <c r="G80" s="43"/>
@@ -19075,13 +19119,13 @@
         <v>348</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19092,10 +19136,10 @@
         <v>350</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19106,10 +19150,10 @@
         <v>338</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19120,10 +19164,10 @@
         <v>338</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19134,10 +19178,10 @@
         <v>340</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19148,10 +19192,10 @@
         <v>338</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19162,13 +19206,13 @@
         <v>338</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19179,10 +19223,10 @@
         <v>338</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19193,10 +19237,10 @@
         <v>338</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19207,10 +19251,10 @@
         <v>338</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19221,10 +19265,10 @@
         <v>354</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19235,10 +19279,10 @@
         <v>350</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19249,10 +19293,10 @@
         <v>340</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="1048377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -19518,10 +19562,10 @@
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="43" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="F2" s="43"/>
       <c r="G2" s="43"/>
@@ -19535,10 +19579,10 @@
       </c>
       <c r="C3" s="43"/>
       <c r="D3" s="44" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="F3" s="43"/>
       <c r="G3" s="43"/>
@@ -19552,10 +19596,10 @@
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="44" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
@@ -19569,10 +19613,10 @@
       </c>
       <c r="C5" s="43"/>
       <c r="D5" s="44" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="F5" s="43"/>
       <c r="G5" s="43"/>
@@ -19586,10 +19630,10 @@
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="44" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="43"/>
@@ -19603,10 +19647,10 @@
       </c>
       <c r="C7" s="43"/>
       <c r="D7" s="44" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="F7" s="43"/>
       <c r="G7" s="43"/>
@@ -19620,10 +19664,10 @@
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="44" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="F8" s="43"/>
       <c r="G8" s="43"/>
@@ -19637,10 +19681,10 @@
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="44" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="F9" s="43"/>
       <c r="G9" s="43"/>
@@ -19654,10 +19698,10 @@
       </c>
       <c r="C10" s="43"/>
       <c r="D10" s="44" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="F10" s="43"/>
       <c r="G10" s="43"/>
@@ -19671,112 +19715,112 @@
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="44" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="F11" s="43"/>
       <c r="G11" s="43"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="44" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="F12" s="43"/>
       <c r="G12" s="43"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="44" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="F13" s="43"/>
       <c r="G13" s="43"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="44" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="F14" s="43"/>
       <c r="G14" s="43"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="44" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="F15" s="43"/>
       <c r="G15" s="43"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="44" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="F16" s="43"/>
       <c r="G16" s="43"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="44" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="F17" s="43"/>
       <c r="G17" s="43"/>
@@ -19790,102 +19834,102 @@
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="44" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="F18" s="43"/>
       <c r="G18" s="43"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="44" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="F19" s="43"/>
       <c r="G19" s="43"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="F20" s="43"/>
       <c r="G20" s="43"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="44" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="F21" s="43"/>
       <c r="G21" s="43"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="44" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="F22" s="43"/>
       <c r="G22" s="43"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C23" s="43"/>
       <c r="D23" s="44" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="F23" s="43"/>
       <c r="G23" s="43"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>234</v>
@@ -19894,17 +19938,17 @@
         <v>126</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="F24" s="43"/>
       <c r="G24" s="43"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="48" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>234</v>
@@ -19913,34 +19957,34 @@
         <v>133</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="F25" s="43"/>
       <c r="G25" s="43"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C26" s="43"/>
       <c r="D26" s="44" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="E26" s="49" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="F26" s="43"/>
       <c r="G26" s="43"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>234</v>
@@ -19949,70 +19993,70 @@
         <v>119</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="48" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C28" s="43"/>
       <c r="D28" s="44" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="E28" s="49" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="F28" s="43"/>
       <c r="G28" s="43"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="48" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="F29" s="43"/>
       <c r="G29" s="43"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="48" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>243</v>
       </c>
       <c r="C30" s="43"/>
       <c r="D30" s="44" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="F30" s="43"/>
       <c r="G30" s="43"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="48" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>243</v>
@@ -20020,7 +20064,7 @@
       <c r="C31" s="43"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="F31" s="43"/>
       <c r="G31" s="43"/>
@@ -20037,41 +20081,41 @@
         <v>357</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="F32" s="43"/>
       <c r="G32" s="43"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="48" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C33" s="43"/>
       <c r="D33" s="44" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="F33" s="43"/>
       <c r="G33" s="43"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="48" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C34" s="43"/>
       <c r="D34" s="44" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
@@ -20085,10 +20129,10 @@
       </c>
       <c r="C35" s="43"/>
       <c r="D35" s="44" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="F35" s="43"/>
       <c r="G35" s="43"/>
@@ -20102,10 +20146,10 @@
       </c>
       <c r="C36" s="43"/>
       <c r="D36" s="44" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="F36" s="43"/>
       <c r="G36" s="43"/>
@@ -20119,10 +20163,10 @@
       </c>
       <c r="C37" s="43"/>
       <c r="D37" s="44" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="F37" s="43"/>
       <c r="G37" s="43"/>
@@ -20136,10 +20180,10 @@
       </c>
       <c r="C38" s="43"/>
       <c r="D38" s="44" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="E38" s="49" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="F38" s="43"/>
       <c r="G38" s="43"/>
@@ -20153,10 +20197,10 @@
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="F39" s="43"/>
       <c r="G39" s="43"/>
@@ -20170,10 +20214,10 @@
       </c>
       <c r="C40" s="43"/>
       <c r="D40" s="44" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="F40" s="43"/>
       <c r="G40" s="43"/>
@@ -20190,7 +20234,7 @@
         <v>373</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="F41" s="43"/>
       <c r="G41" s="43"/>
@@ -20204,10 +20248,10 @@
       </c>
       <c r="C42" s="43"/>
       <c r="D42" s="49" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="E42" s="44" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="F42" s="43"/>
       <c r="G42" s="43"/>
@@ -20221,10 +20265,10 @@
       </c>
       <c r="C43" s="43"/>
       <c r="D43" s="44" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="F43" s="43"/>
       <c r="G43" s="43"/>
@@ -20238,10 +20282,10 @@
       </c>
       <c r="C44" s="43"/>
       <c r="D44" s="44" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="E44" s="50" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="F44" s="43"/>
       <c r="G44" s="43"/>
@@ -20255,10 +20299,10 @@
       </c>
       <c r="C45" s="43"/>
       <c r="D45" s="44" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -20272,10 +20316,10 @@
       </c>
       <c r="C46" s="43"/>
       <c r="D46" s="44" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="E46" s="50" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="F46" s="43"/>
       <c r="G46" s="43"/>
@@ -20289,10 +20333,10 @@
       </c>
       <c r="C47" s="43"/>
       <c r="D47" s="44" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="E47" s="44" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="F47" s="43"/>
       <c r="G47" s="43"/>
@@ -20306,27 +20350,27 @@
       </c>
       <c r="C48" s="43"/>
       <c r="D48" s="44" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="F48" s="43"/>
       <c r="G48" s="43"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="48" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C49" s="43"/>
       <c r="D49" s="44" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="E49" s="44" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="F49" s="43"/>
       <c r="G49" s="43"/>
@@ -20340,27 +20384,27 @@
       </c>
       <c r="C50" s="43"/>
       <c r="D50" s="44" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="E50" s="44" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="F50" s="43"/>
       <c r="G50" s="43"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C51" s="43"/>
       <c r="D51" s="44" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="E51" s="49" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="F51" s="43"/>
       <c r="G51" s="43"/>
@@ -20374,27 +20418,27 @@
       </c>
       <c r="C52" s="43"/>
       <c r="D52" s="44" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="F52" s="43"/>
       <c r="G52" s="43"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C53" s="43"/>
       <c r="D53" s="44" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="F53" s="43"/>
       <c r="G53" s="43"/>
@@ -20408,27 +20452,27 @@
       </c>
       <c r="C54" s="43"/>
       <c r="D54" s="44" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="E54" s="44" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="F54" s="43"/>
       <c r="G54" s="43"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C55" s="43"/>
       <c r="D55" s="44" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="F55" s="43"/>
       <c r="G55" s="43"/>
@@ -20442,27 +20486,27 @@
       </c>
       <c r="C56" s="43"/>
       <c r="D56" s="44" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="F56" s="43"/>
       <c r="G56" s="43"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="48" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C57" s="43"/>
       <c r="D57" s="44" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="F57" s="43"/>
       <c r="G57" s="43"/>
@@ -20476,27 +20520,27 @@
       </c>
       <c r="C58" s="43"/>
       <c r="D58" s="44" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="F58" s="43"/>
       <c r="G58" s="43"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="48" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>350</v>
       </c>
       <c r="C59" s="43"/>
       <c r="D59" s="44" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="F59" s="43"/>
       <c r="G59" s="43"/>
@@ -20510,10 +20554,10 @@
       </c>
       <c r="C60" s="43"/>
       <c r="D60" s="44" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="E60" s="44" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="F60" s="43"/>
       <c r="G60" s="43"/>
@@ -20527,10 +20571,10 @@
       </c>
       <c r="C61" s="43"/>
       <c r="D61" s="44" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="F61" s="43"/>
       <c r="G61" s="43"/>
@@ -20544,10 +20588,10 @@
       </c>
       <c r="C62" s="43"/>
       <c r="D62" s="44" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="E62" s="49" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="F62" s="43"/>
       <c r="G62" s="43"/>
@@ -20560,38 +20604,38 @@
         <v>366</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="E63" s="25" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="46" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="46" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>234</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20602,10 +20646,10 @@
         <v>234</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20616,10 +20660,10 @@
         <v>387</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20630,24 +20674,24 @@
         <v>387</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="48" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B69" s="52" t="s">
         <v>234</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20658,10 +20702,10 @@
         <v>243</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -20713,563 +20757,563 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D2" s="55" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D3" s="55" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>1258</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="D4" s="55" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E4" s="56" t="s">
         <v>1259</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>1258</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="E9" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="E11" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="E12" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="E13" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D15" s="55" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E15" s="58" t="s">
         <v>1283</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="E17" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D20" s="55" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="B21" s="60" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="C21" s="54" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="E21" s="56" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D22" s="55" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C23" s="54" t="s">
         <v>1302</v>
       </c>
-      <c r="B23" s="53" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>1297</v>
-      </c>
       <c r="D23" s="55" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="E23" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="C24" s="54" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D24" s="55" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="B26" s="62" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="B27" s="62" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="E27" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="B28" s="62" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="B29" s="62" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D29" s="63" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="E29" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="B30" s="62" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D30" s="63" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="B31" s="62" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D31" s="63" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="E31" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="B33" s="59" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="C33" s="57" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="E33" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="B34" s="59" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="C34" s="57" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="D34" s="55" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
   </sheetData>
@@ -21323,274 +21367,274 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="55" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="D3" s="55" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="E3" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="C4" s="54"/>
       <c r="D4" s="55" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="C5" s="54"/>
       <c r="D5" s="55" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="E5" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="C6" s="54"/>
       <c r="D6" s="55" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C7" s="54"/>
       <c r="D7" s="55" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="E7" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="C8" s="54"/>
       <c r="D8" s="55" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="55" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="C10" s="54"/>
       <c r="D10" s="55" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="C11" s="54"/>
       <c r="D11" s="55" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="E11" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="C12" s="54"/>
       <c r="D12" s="55" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="55" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="E13" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="C14" s="54"/>
       <c r="D14" s="55" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="C15" s="54"/>
       <c r="D15" s="55" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="E15" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="55" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="C17" s="54"/>
       <c r="D17" s="55" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="C18" s="54"/>
       <c r="D18" s="55" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="B19" s="53" t="s">
-        <v>1370</v>
+        <v>1375</v>
       </c>
       <c r="C19" s="54"/>
       <c r="D19" s="55" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
   </sheetData>

--- a/SEPIA/SEPIA_config.xlsx
+++ b/SEPIA/SEPIA_config.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="1" state="visible" r:id="rId3"/>
@@ -396,7 +396,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="1440">
   <si>
     <t xml:space="preserve">Sheet</t>
   </si>
@@ -1403,25 +1403,7 @@
     <t xml:space="preserve">co_ghg</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">carbon </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> vent</t>
-    </r>
+    <t xml:space="preserve">carbon  vent</t>
   </si>
   <si>
     <t xml:space="preserve">lufnes_ghg</t>
@@ -3435,15 +3417,6 @@
   </si>
   <si>
     <t xml:space="preserve">prehvvap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hbt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home battery charger losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home battery discharger losses</t>
   </si>
   <si>
     <t xml:space="preserve">electricity to H2 compression</t>
@@ -4967,7 +4940,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5034,12 +5007,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -5532,7 +5499,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5552,7 +5519,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5560,11 +5531,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5572,7 +5539,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5588,11 +5555,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5600,7 +5567,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -5624,11 +5591,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -6757,7 +6724,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="B1" s="1" t="n">
         <v>2025</v>
@@ -6780,7 +6747,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>10</v>
@@ -6801,12 +6768,12 @@
         <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0</v>
@@ -6827,12 +6794,12 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.6</v>
@@ -6853,12 +6820,12 @@
         <v>0.6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -6879,12 +6846,12 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1.28</v>
@@ -6905,12 +6872,12 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>47</v>
@@ -6931,12 +6898,12 @@
         <v>40</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>20</v>
@@ -6957,12 +6924,12 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -6983,12 +6950,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0</v>
@@ -7009,12 +6976,12 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0</v>
@@ -7035,12 +7002,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -7061,12 +7028,12 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>0</v>
@@ -7087,12 +7054,12 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
@@ -7113,12 +7080,12 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>16</v>
@@ -7139,12 +7106,12 @@
         <v>16</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>19</v>
@@ -7165,12 +7132,12 @@
         <v>19</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>31</v>
@@ -7191,12 +7158,12 @@
         <v>20</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -7217,12 +7184,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -7243,12 +7210,12 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -7269,12 +7236,12 @@
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>107</v>
@@ -7295,12 +7262,12 @@
         <v>107</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1000</v>
@@ -7321,12 +7288,12 @@
         <v>1000</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>43</v>
@@ -7347,12 +7314,12 @@
         <v>43</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -7373,12 +7340,12 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>68</v>
@@ -7399,12 +7366,12 @@
         <v>68</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -7425,12 +7392,12 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -7451,12 +7418,12 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>0</v>
@@ -7477,12 +7444,12 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>351</v>
@@ -7503,7 +7470,7 @@
         <v>341</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7555,7 +7522,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="B1" s="1" t="n">
         <v>2025</v>
@@ -7578,7 +7545,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>6.5</v>
@@ -7599,12 +7566,12 @@
         <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0</v>
@@ -7625,12 +7592,12 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0</v>
@@ -7651,12 +7618,12 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -7677,12 +7644,12 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1.36</v>
@@ -7703,12 +7670,12 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>38</v>
@@ -7729,12 +7696,12 @@
         <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>42</v>
@@ -7755,12 +7722,12 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -7781,12 +7748,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
@@ -7807,12 +7774,12 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0</v>
@@ -7833,12 +7800,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -7859,12 +7826,12 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>9</v>
@@ -7885,12 +7852,12 @@
         <v>8</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>8</v>
@@ -7911,12 +7878,12 @@
         <v>8</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>13</v>
@@ -7937,12 +7904,12 @@
         <v>13</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>0</v>
@@ -7963,12 +7930,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>60</v>
@@ -7989,12 +7956,12 @@
         <v>60</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -8015,12 +7982,12 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -8041,12 +8008,12 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -8067,12 +8034,12 @@
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>12</v>
@@ -8093,12 +8060,12 @@
         <v>12</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1076</v>
@@ -8119,12 +8086,12 @@
         <v>1000</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>11</v>
@@ -8145,12 +8112,12 @@
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -8171,12 +8138,12 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>40</v>
@@ -8197,12 +8164,12 @@
         <v>40</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -8223,12 +8190,12 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -8249,12 +8216,12 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>2.4</v>
@@ -8275,12 +8242,12 @@
         <v>2.4</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>616</v>
@@ -8301,7 +8268,7 @@
         <v>600</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -10785,13 +10752,15 @@
       <c r="A85" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B85" s="41" t="s">
+      <c r="B85" s="25" t="s">
         <v>298</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D85" s="32"/>
+      <c r="D85" s="41" t="s">
+        <v>231</v>
+      </c>
       <c r="S85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17103,75 +17072,72 @@
         <v>193</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C309" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D309" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="D309" s="1" t="s">
+      <c r="E309" s="1" t="s">
         <v>1008</v>
-      </c>
-      <c r="E309" s="1" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D310" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>1009</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>976</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="B311" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E311" s="1" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A312" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D311" s="1" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E311" s="1" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="1" t="s">
+      <c r="D312" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E312" s="1" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A313" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E312" s="1" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B313" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="D313" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17182,10 +17148,10 @@
         <v>196</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17196,94 +17162,94 @@
         <v>196</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A316" s="1" t="s">
+      <c r="A316" s="25" t="s">
         <v>393</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>196</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>393</v>
+        <v>193</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>196</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A318" s="25" t="s">
-        <v>393</v>
+      <c r="A318" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>196</v>
+        <v>282</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>282</v>
+        <v>185</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>201</v>
+        <v>282</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17291,71 +17257,45 @@
         <v>238</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A325" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D325" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="E325" s="1" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A326" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E326" s="1" t="s">
-        <v>1041</v>
-      </c>
-    </row>
+    </row>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -17440,10 +17380,10 @@
       </c>
       <c r="C2" s="44"/>
       <c r="D2" s="44" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
@@ -17457,10 +17397,10 @@
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="45" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
@@ -17474,10 +17414,10 @@
       </c>
       <c r="C4" s="44"/>
       <c r="D4" s="45" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
@@ -17491,10 +17431,10 @@
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="45" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
@@ -17508,10 +17448,10 @@
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="45" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -17525,10 +17465,10 @@
       </c>
       <c r="C7" s="44"/>
       <c r="D7" s="45" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
@@ -17542,10 +17482,10 @@
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="45" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
@@ -17559,10 +17499,10 @@
       </c>
       <c r="C9" s="44"/>
       <c r="D9" s="45" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F9" s="44"/>
       <c r="G9" s="44"/>
@@ -17576,10 +17516,10 @@
       </c>
       <c r="C10" s="44"/>
       <c r="D10" s="45" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F10" s="44"/>
       <c r="G10" s="44"/>
@@ -17596,7 +17536,7 @@
         <v>760</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="F11" s="44"/>
       <c r="G11" s="44"/>
@@ -17613,7 +17553,7 @@
         <v>758</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="44"/>
@@ -17627,10 +17567,10 @@
       </c>
       <c r="C13" s="44"/>
       <c r="D13" s="45" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="44"/>
@@ -17644,10 +17584,10 @@
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="45" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="44"/>
@@ -17660,13 +17600,13 @@
         <v>340</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="D15" s="45" t="s">
         <v>749</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="44"/>
@@ -17679,13 +17619,13 @@
         <v>340</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D16" s="45" t="s">
         <v>751</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="F16" s="44"/>
       <c r="G16" s="44"/>
@@ -17699,10 +17639,10 @@
       </c>
       <c r="C17" s="44"/>
       <c r="D17" s="45" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="44"/>
@@ -17716,10 +17656,10 @@
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="45" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F18" s="44"/>
       <c r="G18" s="44"/>
@@ -17733,10 +17673,10 @@
       </c>
       <c r="C19" s="44"/>
       <c r="D19" s="45" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F19" s="44"/>
       <c r="G19" s="44"/>
@@ -17753,7 +17693,7 @@
         <v>855</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="F20" s="44"/>
       <c r="G20" s="44"/>
@@ -17770,7 +17710,7 @@
         <v>744</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44"/>
@@ -17787,7 +17727,7 @@
         <v>744</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="F22" s="44"/>
       <c r="G22" s="44"/>
@@ -17804,7 +17744,7 @@
         <v>742</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="F23" s="44"/>
       <c r="G23" s="44"/>
@@ -17821,7 +17761,7 @@
         <v>742</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="F24" s="44"/>
       <c r="G24" s="44"/>
@@ -17834,13 +17774,13 @@
         <v>391</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="D25" s="45" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="F25" s="44"/>
       <c r="G25" s="44"/>
@@ -17856,10 +17796,10 @@
         <v>126</v>
       </c>
       <c r="D26" s="45" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="F26" s="44"/>
       <c r="G26" s="44"/>
@@ -17875,10 +17815,10 @@
         <v>133</v>
       </c>
       <c r="D27" s="45" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="F27" s="44"/>
       <c r="G27" s="44"/>
@@ -17894,10 +17834,10 @@
         <v>119</v>
       </c>
       <c r="D28" s="45" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="F28" s="44"/>
       <c r="G28" s="44"/>
@@ -17910,13 +17850,13 @@
         <v>340</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="D29" s="45" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="F29" s="44"/>
       <c r="G29" s="44"/>
@@ -17929,13 +17869,13 @@
         <v>340</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="D30" s="45" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="F30" s="44"/>
       <c r="G30" s="44"/>
@@ -17949,10 +17889,10 @@
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="45" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="F31" s="44"/>
       <c r="G31" s="44"/>
@@ -17969,7 +17909,7 @@
         <v>359</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="F32" s="44"/>
       <c r="G32" s="44"/>
@@ -17983,10 +17923,10 @@
       </c>
       <c r="C33" s="44"/>
       <c r="D33" s="45" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="F33" s="44"/>
       <c r="G33" s="44"/>
@@ -18003,7 +17943,7 @@
         <v>913</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="F34" s="44"/>
       <c r="G34" s="44"/>
@@ -18016,13 +17956,13 @@
         <v>364</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="D35" s="45" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="F35" s="44"/>
       <c r="G35" s="44"/>
@@ -18036,10 +17976,10 @@
       </c>
       <c r="C36" s="44"/>
       <c r="D36" s="45" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="F36" s="44"/>
       <c r="G36" s="44"/>
@@ -18055,10 +17995,10 @@
         <v>129</v>
       </c>
       <c r="D37" s="45" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="F37" s="44"/>
       <c r="G37" s="44"/>
@@ -18072,10 +18012,10 @@
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="45" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="F38" s="44"/>
       <c r="G38" s="44"/>
@@ -18089,10 +18029,10 @@
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="45" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="E39" s="45" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="F39" s="44"/>
       <c r="G39" s="44"/>
@@ -18106,10 +18046,10 @@
       </c>
       <c r="C40" s="44"/>
       <c r="D40" s="45" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="E40" s="45" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="F40" s="44"/>
       <c r="G40" s="44"/>
@@ -18123,10 +18063,10 @@
       </c>
       <c r="C41" s="44"/>
       <c r="D41" s="45" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="E41" s="45" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="F41" s="44"/>
       <c r="G41" s="44"/>
@@ -18140,10 +18080,10 @@
       </c>
       <c r="C42" s="44"/>
       <c r="D42" s="45" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="F42" s="44"/>
       <c r="G42" s="44"/>
@@ -18157,10 +18097,10 @@
       </c>
       <c r="C43" s="44"/>
       <c r="D43" s="45" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="F43" s="44"/>
       <c r="G43" s="44"/>
@@ -18174,10 +18114,10 @@
       </c>
       <c r="C44" s="44"/>
       <c r="D44" s="45" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="F44" s="44"/>
       <c r="G44" s="44"/>
@@ -18191,10 +18131,10 @@
       </c>
       <c r="C45" s="44"/>
       <c r="D45" s="45" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="F45" s="44"/>
       <c r="G45" s="44"/>
@@ -18210,10 +18150,10 @@
         <v>413</v>
       </c>
       <c r="D46" s="45" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E46" s="51" t="s">
         <v>1116</v>
-      </c>
-      <c r="E46" s="51" t="s">
-        <v>1119</v>
       </c>
       <c r="F46" s="44"/>
       <c r="G46" s="44"/>
@@ -18227,10 +18167,10 @@
       </c>
       <c r="C47" s="44"/>
       <c r="D47" s="45" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="F47" s="44"/>
       <c r="G47" s="44"/>
@@ -18244,10 +18184,10 @@
       </c>
       <c r="C48" s="44"/>
       <c r="D48" s="45" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E48" s="51" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="F48" s="44"/>
       <c r="G48" s="44"/>
@@ -18263,10 +18203,10 @@
         <v>413</v>
       </c>
       <c r="D49" s="45" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="F49" s="44"/>
       <c r="G49" s="44"/>
@@ -18282,10 +18222,10 @@
         <v>413</v>
       </c>
       <c r="D50" s="45" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="E50" s="51" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="F50" s="44"/>
       <c r="G50" s="44"/>
@@ -18299,10 +18239,10 @@
       </c>
       <c r="C51" s="44"/>
       <c r="D51" s="45" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E51" s="51" t="s">
         <v>1123</v>
-      </c>
-      <c r="E51" s="51" t="s">
-        <v>1126</v>
       </c>
       <c r="F51" s="44"/>
       <c r="G51" s="44"/>
@@ -18316,10 +18256,10 @@
       </c>
       <c r="C52" s="44"/>
       <c r="D52" s="45" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="E52" s="51" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="F52" s="44"/>
       <c r="G52" s="44"/>
@@ -18336,7 +18276,7 @@
         <v>551</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="F53" s="44"/>
       <c r="G53" s="44"/>
@@ -18350,10 +18290,10 @@
       </c>
       <c r="C54" s="44"/>
       <c r="D54" s="45" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="E54" s="51" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="F54" s="44"/>
       <c r="G54" s="44"/>
@@ -18367,10 +18307,10 @@
       </c>
       <c r="C55" s="44"/>
       <c r="D55" s="45" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F55" s="44"/>
       <c r="G55" s="44"/>
@@ -18387,7 +18327,7 @@
         <v>375</v>
       </c>
       <c r="E56" s="51" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="F56" s="44"/>
       <c r="G56" s="44"/>
@@ -18404,7 +18344,7 @@
         <v>377</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="F57" s="44"/>
       <c r="G57" s="44"/>
@@ -18418,10 +18358,10 @@
       </c>
       <c r="C58" s="44"/>
       <c r="D58" s="45" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="F58" s="44"/>
       <c r="G58" s="44"/>
@@ -18435,10 +18375,10 @@
       </c>
       <c r="C59" s="44"/>
       <c r="D59" s="45" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="E59" s="45" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="F59" s="44"/>
       <c r="G59" s="44"/>
@@ -18454,10 +18394,10 @@
         <v>413</v>
       </c>
       <c r="D60" s="45" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="F60" s="44"/>
       <c r="G60" s="44"/>
@@ -18471,10 +18411,10 @@
       </c>
       <c r="C61" s="44"/>
       <c r="D61" s="45" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="F61" s="44"/>
       <c r="G61" s="44"/>
@@ -18488,10 +18428,10 @@
       </c>
       <c r="C62" s="44"/>
       <c r="D62" s="45" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E62" s="45" t="s">
         <v>1138</v>
-      </c>
-      <c r="E62" s="45" t="s">
-        <v>1141</v>
       </c>
       <c r="F62" s="44"/>
       <c r="G62" s="44"/>
@@ -18505,10 +18445,10 @@
       </c>
       <c r="C63" s="44"/>
       <c r="D63" s="45" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="E63" s="45" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="F63" s="44"/>
       <c r="G63" s="44"/>
@@ -18522,10 +18462,10 @@
       </c>
       <c r="C64" s="44"/>
       <c r="D64" s="45" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="E64" s="45" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F64" s="44"/>
       <c r="G64" s="44"/>
@@ -18539,10 +18479,10 @@
       </c>
       <c r="C65" s="44"/>
       <c r="D65" s="45" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="E65" s="45" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="F65" s="44"/>
       <c r="G65" s="44"/>
@@ -18556,10 +18496,10 @@
       </c>
       <c r="C66" s="44"/>
       <c r="D66" s="45" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="F66" s="44"/>
       <c r="G66" s="44"/>
@@ -18573,10 +18513,10 @@
       </c>
       <c r="C67" s="44"/>
       <c r="D67" s="45" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="F67" s="44"/>
       <c r="G67" s="44"/>
@@ -18590,10 +18530,10 @@
       </c>
       <c r="C68" s="44"/>
       <c r="D68" s="45" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="F68" s="44"/>
       <c r="G68" s="44"/>
@@ -18610,7 +18550,7 @@
         <v>385</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="F69" s="44"/>
       <c r="G69" s="44"/>
@@ -18624,10 +18564,10 @@
       </c>
       <c r="C70" s="44"/>
       <c r="D70" s="50" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F70" s="44"/>
       <c r="G70" s="44"/>
@@ -18641,10 +18581,10 @@
       </c>
       <c r="C71" s="44"/>
       <c r="D71" s="50" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="F71" s="44"/>
       <c r="G71" s="44"/>
@@ -18658,10 +18598,10 @@
       </c>
       <c r="C72" s="44"/>
       <c r="D72" s="50" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="E72" s="50" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="F72" s="44"/>
       <c r="G72" s="44"/>
@@ -18675,10 +18615,10 @@
       </c>
       <c r="C73" s="44"/>
       <c r="D73" s="50" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="E73" s="50" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="F73" s="44"/>
       <c r="G73" s="44"/>
@@ -18692,10 +18632,10 @@
       </c>
       <c r="C74" s="44"/>
       <c r="D74" s="50" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="E74" s="50" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="F74" s="44"/>
       <c r="G74" s="44"/>
@@ -18709,10 +18649,10 @@
       </c>
       <c r="C75" s="44"/>
       <c r="D75" s="50" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="E75" s="50" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="F75" s="44"/>
       <c r="G75" s="44"/>
@@ -18726,10 +18666,10 @@
       </c>
       <c r="C76" s="44"/>
       <c r="D76" s="50" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="E76" s="50" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="F76" s="44"/>
       <c r="G76" s="44"/>
@@ -18746,7 +18686,7 @@
         <v>448</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="F77" s="44"/>
       <c r="G77" s="44"/>
@@ -18760,10 +18700,10 @@
       </c>
       <c r="C78" s="44"/>
       <c r="D78" s="50" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="E78" s="50" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="F78" s="44"/>
       <c r="G78" s="44"/>
@@ -18777,10 +18717,10 @@
       </c>
       <c r="C79" s="44"/>
       <c r="D79" s="50" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="E79" s="50" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="F79" s="44"/>
       <c r="G79" s="44"/>
@@ -18794,10 +18734,10 @@
       </c>
       <c r="C80" s="44"/>
       <c r="D80" s="50" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="E80" s="50" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="F80" s="44"/>
       <c r="G80" s="44"/>
@@ -18813,10 +18753,10 @@
         <v>986</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18827,10 +18767,10 @@
         <v>352</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18841,10 +18781,10 @@
         <v>340</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18855,10 +18795,10 @@
         <v>340</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18869,10 +18809,10 @@
         <v>342</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18883,10 +18823,10 @@
         <v>340</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18897,13 +18837,13 @@
         <v>340</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18914,10 +18854,10 @@
         <v>340</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18928,10 +18868,10 @@
         <v>340</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18942,10 +18882,10 @@
         <v>340</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18956,10 +18896,10 @@
         <v>356</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18970,10 +18910,10 @@
         <v>352</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18984,10 +18924,10 @@
         <v>342</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18998,10 +18938,10 @@
         <v>340</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="1048377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -19267,10 +19207,10 @@
       </c>
       <c r="C2" s="44"/>
       <c r="D2" s="44" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
@@ -19284,10 +19224,10 @@
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="45" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
@@ -19301,10 +19241,10 @@
       </c>
       <c r="C4" s="44"/>
       <c r="D4" s="45" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
@@ -19318,10 +19258,10 @@
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="45" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
@@ -19335,10 +19275,10 @@
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="45" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -19352,10 +19292,10 @@
       </c>
       <c r="C7" s="44"/>
       <c r="D7" s="45" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="E7" s="50" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
@@ -19369,10 +19309,10 @@
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="45" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="E8" s="50" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
@@ -19386,10 +19326,10 @@
       </c>
       <c r="C9" s="44"/>
       <c r="D9" s="45" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="F9" s="44"/>
       <c r="G9" s="44"/>
@@ -19403,10 +19343,10 @@
       </c>
       <c r="C10" s="44"/>
       <c r="D10" s="45" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="F10" s="44"/>
       <c r="G10" s="44"/>
@@ -19420,112 +19360,112 @@
       </c>
       <c r="C11" s="44"/>
       <c r="D11" s="45" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="F11" s="44"/>
       <c r="G11" s="44"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C12" s="44"/>
       <c r="D12" s="45" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="44"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C13" s="44"/>
       <c r="D13" s="45" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="44"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="45" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="44"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C15" s="44"/>
       <c r="D15" s="45" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="44"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="45" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="F16" s="44"/>
       <c r="G16" s="44"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C17" s="44"/>
       <c r="D17" s="45" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="44"/>
@@ -19539,85 +19479,85 @@
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="45" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="F18" s="44"/>
       <c r="G18" s="44"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C19" s="44"/>
       <c r="D19" s="45" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="F19" s="44"/>
       <c r="G19" s="44"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C20" s="44"/>
       <c r="D20" s="45" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="F20" s="44"/>
       <c r="G20" s="44"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="45" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C22" s="44"/>
       <c r="D22" s="45" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="F22" s="44"/>
       <c r="G22" s="44"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>236</v>
@@ -19627,14 +19567,14 @@
         <v>855</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="F23" s="44"/>
       <c r="G23" s="44"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>234</v>
@@ -19643,17 +19583,17 @@
         <v>126</v>
       </c>
       <c r="D24" s="45" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="F24" s="44"/>
       <c r="G24" s="44"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>234</v>
@@ -19662,34 +19602,34 @@
         <v>133</v>
       </c>
       <c r="D25" s="45" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="F25" s="44"/>
       <c r="G25" s="44"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C26" s="44"/>
       <c r="D26" s="45" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="F26" s="44"/>
       <c r="G26" s="44"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>234</v>
@@ -19698,70 +19638,70 @@
         <v>119</v>
       </c>
       <c r="D27" s="45" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="F27" s="44"/>
       <c r="G27" s="44"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C28" s="44"/>
       <c r="D28" s="45" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="F28" s="44"/>
       <c r="G28" s="44"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="D29" s="45" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="F29" s="44"/>
       <c r="G29" s="44"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>243</v>
       </c>
       <c r="C30" s="44"/>
       <c r="D30" s="45" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="E30" s="45" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="F30" s="44"/>
       <c r="G30" s="44"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>243</v>
@@ -19769,7 +19709,7 @@
       <c r="C31" s="44"/>
       <c r="D31" s="45"/>
       <c r="E31" s="45" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="F31" s="44"/>
       <c r="G31" s="44"/>
@@ -19786,41 +19726,41 @@
         <v>359</v>
       </c>
       <c r="E32" s="45" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="F32" s="44"/>
       <c r="G32" s="44"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>236</v>
       </c>
       <c r="C33" s="44"/>
       <c r="D33" s="45" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="E33" s="45" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="F33" s="44"/>
       <c r="G33" s="44"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>234</v>
       </c>
       <c r="C34" s="44"/>
       <c r="D34" s="45" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="E34" s="45" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="F34" s="44"/>
       <c r="G34" s="44"/>
@@ -19834,10 +19774,10 @@
       </c>
       <c r="C35" s="44"/>
       <c r="D35" s="45" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="E35" s="45" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="F35" s="44"/>
       <c r="G35" s="44"/>
@@ -19851,10 +19791,10 @@
       </c>
       <c r="C36" s="44"/>
       <c r="D36" s="45" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="F36" s="44"/>
       <c r="G36" s="44"/>
@@ -19868,10 +19808,10 @@
       </c>
       <c r="C37" s="44"/>
       <c r="D37" s="45" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="F37" s="44"/>
       <c r="G37" s="44"/>
@@ -19885,10 +19825,10 @@
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="45" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="E38" s="50" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="F38" s="44"/>
       <c r="G38" s="44"/>
@@ -19902,10 +19842,10 @@
       </c>
       <c r="C39" s="44"/>
       <c r="D39" s="45" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="F39" s="44"/>
       <c r="G39" s="44"/>
@@ -19919,10 +19859,10 @@
       </c>
       <c r="C40" s="44"/>
       <c r="D40" s="45" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="F40" s="44"/>
       <c r="G40" s="44"/>
@@ -19939,7 +19879,7 @@
         <v>375</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="F41" s="44"/>
       <c r="G41" s="44"/>
@@ -19953,10 +19893,10 @@
       </c>
       <c r="C42" s="44"/>
       <c r="D42" s="50" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="E42" s="45" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="F42" s="44"/>
       <c r="G42" s="44"/>
@@ -19970,10 +19910,10 @@
       </c>
       <c r="C43" s="44"/>
       <c r="D43" s="45" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="F43" s="44"/>
       <c r="G43" s="44"/>
@@ -19987,10 +19927,10 @@
       </c>
       <c r="C44" s="44"/>
       <c r="D44" s="45" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E44" s="51" t="s">
         <v>1116</v>
-      </c>
-      <c r="E44" s="51" t="s">
-        <v>1119</v>
       </c>
       <c r="F44" s="44"/>
       <c r="G44" s="44"/>
@@ -20004,10 +19944,10 @@
       </c>
       <c r="C45" s="44"/>
       <c r="D45" s="45" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E45" s="45" t="s">
         <v>1138</v>
-      </c>
-      <c r="E45" s="45" t="s">
-        <v>1141</v>
       </c>
       <c r="F45" s="44"/>
       <c r="G45" s="44"/>
@@ -20021,10 +19961,10 @@
       </c>
       <c r="C46" s="44"/>
       <c r="D46" s="45" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="E46" s="51" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F46" s="44"/>
       <c r="G46" s="44"/>
@@ -20038,10 +19978,10 @@
       </c>
       <c r="C47" s="44"/>
       <c r="D47" s="45" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="E47" s="45" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="F47" s="44"/>
       <c r="G47" s="44"/>
@@ -20055,27 +19995,27 @@
       </c>
       <c r="C48" s="44"/>
       <c r="D48" s="45" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="E48" s="45" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="F48" s="44"/>
       <c r="G48" s="44"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>352</v>
       </c>
       <c r="C49" s="44"/>
       <c r="D49" s="45" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E49" s="45" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F49" s="44"/>
       <c r="G49" s="44"/>
@@ -20089,27 +20029,27 @@
       </c>
       <c r="C50" s="44"/>
       <c r="D50" s="45" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E50" s="45" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F50" s="44"/>
       <c r="G50" s="44"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>352</v>
       </c>
       <c r="C51" s="44"/>
       <c r="D51" s="45" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="F51" s="44"/>
       <c r="G51" s="44"/>
@@ -20123,27 +20063,27 @@
       </c>
       <c r="C52" s="44"/>
       <c r="D52" s="45" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="F52" s="44"/>
       <c r="G52" s="44"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>352</v>
       </c>
       <c r="C53" s="44"/>
       <c r="D53" s="45" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="E53" s="45" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="F53" s="44"/>
       <c r="G53" s="44"/>
@@ -20157,27 +20097,27 @@
       </c>
       <c r="C54" s="44"/>
       <c r="D54" s="45" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="E54" s="45" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="F54" s="44"/>
       <c r="G54" s="44"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>352</v>
       </c>
       <c r="C55" s="44"/>
       <c r="D55" s="45" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="F55" s="44"/>
       <c r="G55" s="44"/>
@@ -20191,27 +20131,27 @@
       </c>
       <c r="C56" s="44"/>
       <c r="D56" s="45" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="F56" s="44"/>
       <c r="G56" s="44"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>352</v>
       </c>
       <c r="C57" s="44"/>
       <c r="D57" s="45" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="F57" s="44"/>
       <c r="G57" s="44"/>
@@ -20225,27 +20165,27 @@
       </c>
       <c r="C58" s="44"/>
       <c r="D58" s="45" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="F58" s="44"/>
       <c r="G58" s="44"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>352</v>
       </c>
       <c r="C59" s="44"/>
       <c r="D59" s="45" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="E59" s="45" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="F59" s="44"/>
       <c r="G59" s="44"/>
@@ -20259,10 +20199,10 @@
       </c>
       <c r="C60" s="44"/>
       <c r="D60" s="45" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="F60" s="44"/>
       <c r="G60" s="44"/>
@@ -20276,10 +20216,10 @@
       </c>
       <c r="C61" s="44"/>
       <c r="D61" s="45" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="F61" s="44"/>
       <c r="G61" s="44"/>
@@ -20293,10 +20233,10 @@
       </c>
       <c r="C62" s="44"/>
       <c r="D62" s="45" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="F62" s="44"/>
       <c r="G62" s="44"/>
@@ -20309,38 +20249,38 @@
         <v>368</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="E63" s="25" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="47" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="47" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>234</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20351,10 +20291,10 @@
         <v>234</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20365,10 +20305,10 @@
         <v>389</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20379,24 +20319,24 @@
         <v>389</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="49" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B69" s="53" t="s">
         <v>234</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20407,10 +20347,10 @@
         <v>243</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20421,10 +20361,10 @@
         <v>334</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="E71" s="41" t="s">
-        <v>1199</v>
+        <v>1195</v>
+      </c>
+      <c r="E71" s="25" t="s">
+        <v>1196</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -20476,563 +20416,563 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E2" s="57" t="s">
         <v>1240</v>
-      </c>
-      <c r="B2" s="54" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C2" s="55" t="s">
-        <v>1242</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="C5" s="55" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D5" s="56" t="s">
         <v>1246</v>
       </c>
-      <c r="D5" s="56" t="s">
-        <v>1249</v>
-      </c>
       <c r="E5" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="E7" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="E8" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="E9" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="E10" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="E12" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="E13" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="E15" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="E17" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B18" s="54" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="E18" s="57" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="B19" s="60" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="E19" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="B20" s="54" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="E20" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D21" s="56" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E21" s="57" t="s">
         <v>1284</v>
-      </c>
-      <c r="B21" s="61" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E21" s="57" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="B22" s="62" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="B23" s="54" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="B24" s="54" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B25" s="54" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="E25" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D26" s="64" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="C27" s="65" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D27" s="64" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="E27" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="B28" s="63" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="C28" s="65" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D28" s="64" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="E28" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="B29" s="63" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D29" s="64" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="E29" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B30" s="63" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D31" s="64" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="E31" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="B32" s="54" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="E32" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D33" s="64" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="E33" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="B34" s="60" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="E34" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
@@ -21086,274 +21026,274 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="C2" s="55"/>
       <c r="D2" s="56" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="E2" s="66" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="C4" s="55"/>
       <c r="D4" s="56" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="E4" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="C5" s="55"/>
       <c r="D5" s="56" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="C6" s="55"/>
       <c r="D6" s="56" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="56" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="56" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="56" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="E9" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="C10" s="55"/>
       <c r="D10" s="56" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="C11" s="55"/>
       <c r="D11" s="56" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="E11" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="56" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="C13" s="55"/>
       <c r="D13" s="56" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="E13" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="C14" s="55"/>
       <c r="D14" s="56" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="C15" s="55"/>
       <c r="D15" s="56" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="E15" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="C16" s="55"/>
       <c r="D16" s="56" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="C17" s="55"/>
       <c r="D17" s="56" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="B18" s="54" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="C18" s="55"/>
       <c r="D18" s="56" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C19" s="55"/>
       <c r="D19" s="56" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="E19" s="59" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
